--- a/NAP mock data.xlsx
+++ b/NAP mock data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="333">
   <si>
     <t>Year</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>Impact of recent deviations in how we think market will expand</t>
-  </si>
-  <si>
-    <t>2024 to 43</t>
   </si>
   <si>
     <t>Table 1</t>
@@ -986,12 +983,18 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Source</t>
+  </si>
+  <si>
     <t>Market CAGR</t>
   </si>
   <si>
     <t>Monitor</t>
   </si>
   <si>
+    <t>Forian claims</t>
+  </si>
+  <si>
     <t>Diagnosis rate</t>
   </si>
   <si>
@@ -1013,6 +1016,9 @@
     <t>Access</t>
   </si>
   <si>
+    <t>MMIT Formulary Coverage Data</t>
+  </si>
+  <si>
     <t>Fulfilment</t>
   </si>
   <si>
@@ -1074,9 +1080,6 @@
   </si>
   <si>
     <t>Illustrative claims-based view; replace values as the ongoing claims feed becomes available.</t>
-  </si>
-  <si>
-    <t>Source</t>
   </si>
   <si>
     <t>Illustrative claims data</t>
@@ -2006,13 +2009,13 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C4" s="3">
-        <v>68040350.404194</v>
+        <v>70276510.1282979</v>
       </c>
       <c r="D4" s="3">
-        <v>68040350.404194</v>
+        <v>70776510.1282979</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
@@ -2020,14 +2023,14 @@
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
-        <f t="shared" ref="B5:B8" si="0">B4+1</f>
-        <v>2025</v>
+        <f>B4+1</f>
+        <v>2027</v>
       </c>
       <c r="C5" s="3">
-        <v>69197036.3610653</v>
+        <v>71500000.1305315</v>
       </c>
       <c r="D5" s="3">
-        <v>69197036.3610653</v>
+        <v>72300000.1305315</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
@@ -2035,14 +2038,14 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
-        <f t="shared" si="0"/>
-        <v>2026</v>
+        <f>B5+1</f>
+        <v>2028</v>
       </c>
       <c r="C6" s="3">
-        <v>70276510.1282979</v>
+        <v>72939400.1331593</v>
       </c>
       <c r="D6" s="3">
-        <v>70776510.1282979</v>
+        <v>73839400.1331593</v>
       </c>
       <c r="F6" t="s">
         <v>6</v>
@@ -2050,14 +2053,14 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
-        <f t="shared" si="0"/>
-        <v>2027</v>
+        <f>B6+1</f>
+        <v>2029</v>
       </c>
       <c r="C7" s="3">
-        <v>71500000.1305315</v>
+        <v>74483147.8735519</v>
       </c>
       <c r="D7" s="3">
-        <v>72300000.1305315</v>
+        <v>75483147.8735519</v>
       </c>
       <c r="F7" t="s">
         <v>7</v>
@@ -2065,208 +2068,186 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>2028</v>
+        <f>B7+1</f>
+        <v>2030</v>
       </c>
       <c r="C8" s="3">
-        <v>72939400.1331593</v>
+        <v>76045549.3195225</v>
       </c>
       <c r="D8" s="3">
-        <v>73839400.1331593</v>
+        <v>77045549.3195225</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <f>B8+1</f>
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="C9" s="3">
-        <v>74483147.8735519</v>
+        <v>77584100.0617359</v>
       </c>
       <c r="D9" s="3">
-        <v>75483147.8735519</v>
+        <v>78584100.0617359</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
-        <f t="shared" ref="B10:B23" si="1">B9+1</f>
-        <v>2030</v>
+        <f>B9+1</f>
+        <v>2032</v>
       </c>
       <c r="C10" s="3">
-        <v>76045549.3195225</v>
+        <v>79078001.4307763</v>
       </c>
       <c r="D10" s="3">
-        <v>77045549.3195225</v>
+        <v>80278001.4307763</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
-        <f t="shared" si="1"/>
-        <v>2031</v>
+        <f>B10+1</f>
+        <v>2033</v>
       </c>
       <c r="C11" s="3">
-        <v>77584100.0617359</v>
+        <v>80517404.8384735</v>
       </c>
       <c r="D11" s="3">
-        <v>78584100.0617359</v>
+        <v>82017404.8384735</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
-        <f t="shared" si="1"/>
-        <v>2032</v>
+        <f>B11+1</f>
+        <v>2034</v>
       </c>
       <c r="C12" s="3">
-        <v>79078001.4307763</v>
+        <v>81904630.2507732</v>
       </c>
       <c r="D12" s="3">
-        <v>80278001.4307763</v>
+        <v>83704630.2507732</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
-        <f t="shared" si="1"/>
-        <v>2033</v>
+        <f>B12+1</f>
+        <v>2035</v>
       </c>
       <c r="C13" s="3">
-        <v>80517404.8384735</v>
+        <v>83242203.0826524</v>
       </c>
       <c r="D13" s="3">
-        <v>82017404.8384735</v>
+        <v>85542203.0826524</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
-        <f t="shared" si="1"/>
-        <v>2034</v>
+        <f>B13+1</f>
+        <v>2036</v>
       </c>
       <c r="C14" s="3">
-        <v>81904630.2507732</v>
+        <v>84528479.8723046</v>
       </c>
       <c r="D14" s="3">
-        <v>83704630.2507732</v>
+        <v>87328479.8723046</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
-        <f t="shared" si="1"/>
-        <v>2035</v>
+        <f>B14+1</f>
+        <v>2037</v>
       </c>
       <c r="C15" s="3">
-        <v>83242203.0826524</v>
+        <v>85765943.3481735</v>
       </c>
       <c r="D15" s="3">
-        <v>85542203.0826524</v>
+        <v>89065943.3481735</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
-        <f t="shared" si="1"/>
-        <v>2036</v>
+        <f>B15+1</f>
+        <v>2038</v>
       </c>
       <c r="C16" s="3">
-        <v>84528479.8723046</v>
+        <v>86956956.0746462</v>
       </c>
       <c r="D16" s="3">
-        <v>87328479.8723046</v>
+        <v>91056956.0746462</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
-        <f t="shared" si="1"/>
-        <v>2037</v>
+        <f>B16+1</f>
+        <v>2039</v>
       </c>
       <c r="C17" s="3">
-        <v>85765943.3481735</v>
+        <v>88103766.2679935</v>
       </c>
       <c r="D17" s="3">
-        <v>89065943.3481735</v>
+        <v>92903766.2679935</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
-        <f t="shared" si="1"/>
-        <v>2038</v>
+        <f>B17+1</f>
+        <v>2040</v>
       </c>
       <c r="C18" s="3">
-        <v>86956956.0746462</v>
+        <v>89208513.3308187</v>
       </c>
       <c r="D18" s="3">
-        <v>91056956.0746462</v>
+        <v>94808513.3308187</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
-        <f t="shared" si="1"/>
-        <v>2039</v>
+        <f>B18+1</f>
+        <v>2041</v>
       </c>
       <c r="C19" s="3">
-        <v>88103766.2679935</v>
+        <v>90269246.9147585</v>
       </c>
       <c r="D19" s="3">
-        <v>92903766.2679935</v>
+        <v>96869246.9147585</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
-        <f t="shared" si="1"/>
-        <v>2040</v>
+        <f>B19+1</f>
+        <v>2042</v>
       </c>
       <c r="C20" s="3">
-        <v>89208513.3308187</v>
+        <v>91288097.272191</v>
       </c>
       <c r="D20" s="3">
-        <v>94808513.3308187</v>
+        <v>98688097.272191</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
-        <f t="shared" si="1"/>
-        <v>2041</v>
+        <f>B20+1</f>
+        <v>2043</v>
       </c>
       <c r="C21" s="3">
-        <v>90269246.9147585</v>
+        <v>92267091.5512792</v>
       </c>
       <c r="D21" s="3">
-        <v>96869246.9147585</v>
+        <v>100667091.551279</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="1">
-        <f t="shared" si="1"/>
-        <v>2042</v>
-      </c>
-      <c r="C22" s="3">
-        <v>91288097.272191</v>
-      </c>
-      <c r="D22" s="3">
-        <v>98688097.272191</v>
-      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="1">
-        <f t="shared" si="1"/>
-        <v>2043</v>
-      </c>
-      <c r="C23" s="3">
-        <v>92267091.5512792</v>
-      </c>
-      <c r="D23" s="3">
-        <v>100667091.551279</v>
-      </c>
-    </row>
+      <c r="B23" s="1"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25"/>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="4" t="str">
-        <f>"CAGR: "&amp;ROUND(_xlfn.RRI(COUNTA(B4:B23)-1,C4,C23)*100,1)&amp;"%"</f>
-        <v>CAGR: 1.6%</v>
-      </c>
-      <c r="D25" s="4" t="str">
-        <f>"CAGR: "&amp;ROUND(_xlfn.RRI(COUNTA(B4:B23)-1,D4,D23)*100,1)&amp;"%"</f>
-        <v>CAGR: 2.1%</v>
-      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2287,20 +2268,20 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="7">
         <f>SUM(C13:C18)</f>
@@ -2309,7 +2290,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C19:C24)</f>
@@ -2318,7 +2299,7 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="7">
         <f>SUM(C25:C26)</f>
@@ -2327,28 +2308,28 @@
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G11" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>18</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="14">
         <v>0.104</v>
@@ -2357,7 +2338,7 @@
         <v>0.095</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H13" s="16">
         <v>52020.991983967935</v>
@@ -2369,7 +2350,7 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="18">
         <v>0.111</v>
@@ -2378,19 +2359,19 @@
         <v>0.115</v>
       </c>
       <c r="G14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H14" s="16">
         <v>184603.98549179515</v>
       </c>
       <c r="I14" s="4">
-        <f t="shared" si="0"/>
+        <f>H14/SUM($H$13:$H$26)</f>
         <v>0.04021670924443566</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="18">
         <v>0.077</v>
@@ -2399,19 +2380,19 @@
         <v>0.082</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H15" s="16">
         <v>25191.390497401633</v>
       </c>
       <c r="I15" s="4">
-        <f t="shared" si="0"/>
+        <f>H15/SUM($H$13:$H$26)</f>
         <v>0.005488044174117084</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" s="21">
         <v>0.009</v>
@@ -2420,19 +2401,19 @@
         <v>0.009</v>
       </c>
       <c r="G16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H16" s="16">
         <v>2973.8975501113587</v>
       </c>
       <c r="I16" s="4">
-        <f t="shared" si="0"/>
+        <f>H16/SUM($H$13:$H$26)</f>
         <v>0.0006478753574953763</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="21">
         <v>0.016</v>
@@ -2441,19 +2422,19 @@
         <v>0.016</v>
       </c>
       <c r="G17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H17" s="16">
         <v>9836.87374749499</v>
       </c>
       <c r="I17" s="4">
-        <f t="shared" si="0"/>
+        <f>H17/SUM($H$13:$H$26)</f>
         <v>0.002143001898487242</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="24">
         <v>0.033</v>
@@ -2462,19 +2443,19 @@
         <v>0.035</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H18" s="16">
         <v>633852.8607292289</v>
       </c>
       <c r="I18" s="4">
-        <f t="shared" si="0"/>
+        <f>H18/SUM($H$13:$H$26)</f>
         <v>0.13808735567539607</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="27">
         <v>0.096</v>
@@ -2483,19 +2464,19 @@
         <v>0.091</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H19" s="16">
         <v>11962.021509296392</v>
       </c>
       <c r="I19" s="4">
-        <f t="shared" si="0"/>
+        <f>H19/SUM($H$13:$H$26)</f>
         <v>0.0026059737536730486</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="30">
         <v>0.015</v>
@@ -2504,19 +2485,19 @@
         <v>0.014</v>
       </c>
       <c r="G20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H20" s="16">
         <v>3892.316806416332</v>
       </c>
       <c r="I20" s="4">
-        <f t="shared" si="0"/>
+        <f>H20/SUM($H$13:$H$26)</f>
         <v>0.0008479566292886637</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="30">
         <v>0.061</v>
@@ -2525,19 +2506,19 @@
         <v>0.064</v>
       </c>
       <c r="G21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H21" s="16">
         <v>367854.14234905096</v>
       </c>
       <c r="I21" s="4">
-        <f t="shared" si="0"/>
+        <f>H21/SUM($H$13:$H$26)</f>
         <v>0.08013848155987159</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="30">
         <v>0.011</v>
@@ -2546,19 +2527,19 @@
         <v>0.012</v>
       </c>
       <c r="G22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H22" s="16">
         <v>6675.824547600314</v>
       </c>
       <c r="I22" s="4">
-        <f t="shared" si="0"/>
+        <f>H22/SUM($H$13:$H$26)</f>
         <v>0.00145435481299314</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="30">
         <v>0.077</v>
@@ -2567,19 +2548,19 @@
         <v>0.068</v>
       </c>
       <c r="G23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H23" s="16">
         <v>2276.6577498033043</v>
       </c>
       <c r="I23" s="4">
-        <f t="shared" si="0"/>
+        <f>H23/SUM($H$13:$H$26)</f>
         <v>0.0004959789060296322</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="33">
         <v>0.036</v>
@@ -2588,19 +2569,19 @@
         <v>0.035</v>
       </c>
       <c r="G24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H24" s="16">
         <v>253346.03703783272</v>
       </c>
       <c r="I24" s="4">
-        <f t="shared" si="0"/>
+        <f>H24/SUM($H$13:$H$26)</f>
         <v>0.05519243738230881</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" s="36">
         <v>0.256</v>
@@ -2609,20 +2590,20 @@
         <v>0.27</v>
       </c>
       <c r="G25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H25" s="16">
         <f>SUM(H31:H33)</f>
         <v>1624067</v>
       </c>
       <c r="I25" s="4">
-        <f t="shared" si="0"/>
+        <f>H25/SUM($H$13:$H$26)</f>
         <v>0.35380942702012164</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" s="39">
         <v>0.098</v>
@@ -2632,20 +2613,20 @@
         <v>0.09399999999999975</v>
       </c>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H26" s="16">
         <f>SUM(H34:H36)</f>
         <v>1411677</v>
       </c>
       <c r="I26" s="4">
-        <f t="shared" si="0"/>
+        <f>H26/SUM($H$13:$H$26)</f>
         <v>0.3075394244864801</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" s="42">
         <f>SUM(C13:C26)</f>
@@ -2669,7 +2650,7 @@
     </row>
     <row r="31" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H31" s="16">
         <v>113118</v>
@@ -2677,7 +2658,7 @@
     </row>
     <row r="32" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H32" s="16">
         <v>1301493</v>
@@ -2685,7 +2666,7 @@
     </row>
     <row r="33" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H33" s="16">
         <v>209456</v>
@@ -2693,7 +2674,7 @@
     </row>
     <row r="34" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H34" s="16">
         <v>79616</v>
@@ -2701,7 +2682,7 @@
     </row>
     <row r="35" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H35" s="16">
         <v>1046324</v>
@@ -2709,7 +2690,7 @@
     </row>
     <row r="36" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H36" s="16">
         <v>285737</v>
@@ -2717,7 +2698,7 @@
     </row>
     <row r="37" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H37" s="16">
         <v>25600.42778390298</v>
@@ -2725,7 +2706,7 @@
     </row>
     <row r="38" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H38" s="16">
         <v>133075.57221609703</v>
@@ -2733,7 +2714,7 @@
     </row>
     <row r="39" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H39" s="16">
         <v>40414.10333531864</v>
@@ -2741,7 +2722,7 @@
     </row>
     <row r="40" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H40" s="16">
         <v>47766.896664681364</v>
@@ -2766,45 +2747,45 @@
   <sheetData>
     <row r="3" ht="57.599998474121094" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="E3" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="H3" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="54" t="s">
         <v>129</v>
       </c>
-      <c r="H3" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="54" t="s">
+      <c r="J3" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="J3" s="54" t="s">
+      <c r="K3" s="54" t="s">
         <v>131</v>
       </c>
-      <c r="K3" s="54" t="s">
+      <c r="L3" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="L3" s="54" t="s">
+      <c r="M3" s="54" t="s">
         <v>133</v>
-      </c>
-      <c r="M3" s="54" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="55">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="C4" s="56">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="D4" s="57">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="E4" s="56">
         <v>0.04</v>
@@ -2830,13 +2811,13 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="55">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="C5" s="56">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D5" s="57">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="E5" s="56">
         <v>0.04</v>
@@ -2862,13 +2843,13 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="55">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="C6" s="56">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="D6" s="57">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="E6" s="56">
         <v>0.04</v>
@@ -2894,13 +2875,13 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="55">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="C7" s="56">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D7" s="57">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="E7" s="56">
         <v>0.04</v>
@@ -2926,13 +2907,13 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="55">
-        <v>46296</v>
+        <v>46327</v>
       </c>
       <c r="C8" s="56">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="D8" s="57">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="E8" s="56">
         <v>0.04</v>
@@ -2958,13 +2939,13 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="55">
-        <v>46327</v>
+        <v>46357</v>
       </c>
       <c r="C9" s="56">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="D9" s="57">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="E9" s="56">
         <v>0.04</v>
@@ -2989,34 +2970,26 @@
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="55">
-        <v>46357</v>
-      </c>
-      <c r="C10" s="64">
-        <v>0.16</v>
-      </c>
-      <c r="D10" s="64">
-        <v>0.8</v>
-      </c>
-      <c r="E10" s="64">
-        <v>0.04</v>
-      </c>
+      <c r="B10" s="55"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
     </row>
     <row r="13" ht="57.599998474121094" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="54" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="54" t="s">
         <v>135</v>
       </c>
-      <c r="D13" s="54" t="s">
+      <c r="E13" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="E13" s="54" t="s">
+      <c r="F13" s="54" t="s">
         <v>137</v>
-      </c>
-      <c r="F13" s="54" t="s">
-        <v>138</v>
       </c>
       <c r="G13" s="54"/>
       <c r="H13" s="54"/>
@@ -3027,16 +3000,16 @@
         <v>46204</v>
       </c>
       <c r="C14" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="61" t="s">
         <v>139</v>
-      </c>
-      <c r="D14" s="61" t="s">
-        <v>140</v>
       </c>
       <c r="E14" s="59">
         <v>8200</v>
       </c>
       <c r="F14" s="61" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G14" s="60"/>
       <c r="H14" s="60"/>
@@ -3047,7 +3020,7 @@
         <v>46235</v>
       </c>
       <c r="C15" s="61" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D15" s="66">
         <v>0.01</v>
@@ -3056,7 +3029,7 @@
         <v>8450</v>
       </c>
       <c r="F15" s="61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G15" s="60"/>
       <c r="H15" s="60"/>
@@ -3067,7 +3040,7 @@
         <v>46266</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D16" s="66">
         <v>0.01</v>
@@ -3076,7 +3049,7 @@
         <v>8750</v>
       </c>
       <c r="F16" s="61" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G16" s="60"/>
       <c r="H16" s="60"/>
@@ -3087,7 +3060,7 @@
         <v>46296</v>
       </c>
       <c r="C17" s="61" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D17" s="66">
         <v>0.015</v>
@@ -3096,7 +3069,7 @@
         <v>9050</v>
       </c>
       <c r="F17" s="61" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G17" s="60"/>
       <c r="H17" s="60"/>
@@ -3107,7 +3080,7 @@
         <v>46327</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D18" s="66">
         <v>0.019</v>
@@ -3116,7 +3089,7 @@
         <v>9400</v>
       </c>
       <c r="F18" s="61" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G18" s="60"/>
       <c r="H18" s="60"/>
@@ -3127,7 +3100,7 @@
         <v>46357</v>
       </c>
       <c r="C19" s="54" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D19" s="66">
         <v>0.019</v>
@@ -3136,7 +3109,7 @@
         <v>9800</v>
       </c>
       <c r="F19" s="54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G19" s="63"/>
       <c r="H19" s="63"/>
@@ -3149,30 +3122,36 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:G10"/>
+  <dimension ref="B3:H10"/>
   <sheetFormatPr defaultRowHeight="14.399999618530273" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <cols>
+    <col min="8" max="8" width="30" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" ht="28.799999237060547" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" ht="28.799999237060547" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
+        <v>293</v>
+      </c>
+      <c r="C3" s="53" t="s">
         <v>294</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="D3" s="53" t="s">
         <v>295</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="E3" s="53" t="s">
         <v>296</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="F3" s="53" t="s">
         <v>297</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="G3" s="53" t="s">
         <v>298</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="H3" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="4" ht="28.799999237060547" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" ht="28.799999237060547" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="69" t="s">
         <v>300</v>
       </c>
@@ -3191,10 +3170,13 @@
       <c r="G4" s="69" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="5" ht="28.799999237060547" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" ht="28.799999237060547" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="69" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C5" s="70">
         <v>0.806</v>
@@ -3209,12 +3191,15 @@
         <v>0.81</v>
       </c>
       <c r="G5" s="69" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="6" ht="28.799999237060547" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+      <c r="H5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" ht="28.799999237060547" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="69" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C6" s="70">
         <v>0.807</v>
@@ -3231,13 +3216,16 @@
       <c r="G6" s="69" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="7" ht="28.799999237060547" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" ht="28.799999237060547" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="69" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D7" s="69">
         <v>8.2</v>
@@ -3249,12 +3237,15 @@
         <v>7.3</v>
       </c>
       <c r="G7" s="69" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+      <c r="H7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="69" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C8" s="56">
         <v>0.41</v>
@@ -3271,10 +3262,13 @@
       <c r="G8" s="69" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="9" ht="28.799999237060547" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H8" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="9" ht="28.799999237060547" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="69" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C9" s="56">
         <v>0.9</v>
@@ -3289,27 +3283,33 @@
         <v>0.87</v>
       </c>
       <c r="G9" s="69" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="10" ht="28.799999237060547" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+      <c r="H9" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="10" ht="28.799999237060547" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="69" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C10" s="56">
         <v>0.84</v>
       </c>
       <c r="D10" s="69" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E10" s="69" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F10" s="56">
         <v>0.83</v>
       </c>
       <c r="G10" s="69" t="s">
-        <v>303</v>
+        <v>304</v>
+      </c>
+      <c r="H10" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -3337,40 +3337,40 @@
   <sheetData>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="D3" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="E3" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="F3" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="G3" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="45" t="s">
+      <c r="H3" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="I3" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="45" t="s">
+      <c r="J3" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="J3" s="47" t="s">
+      <c r="K3" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="K3" s="48" t="s">
+      <c r="N3" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="N3" s="49" t="s">
+      <c r="O3" s="49" t="s">
         <v>69</v>
-      </c>
-      <c r="O3" s="49" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
@@ -3403,10 +3403,10 @@
         <v>0.019</v>
       </c>
       <c r="L4" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="M4" s="48" t="s">
         <v>71</v>
-      </c>
-      <c r="M4" s="48" t="s">
-        <v>72</v>
       </c>
       <c r="N4" s="16">
         <f>'LLT Product Mix'!B10*J4*1000000</f>
@@ -3616,7 +3616,7 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" s="51">
         <v>0.14106942814008797</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11" s="51">
         <v>0.16899362276834914</v>
@@ -3670,7 +3670,7 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" s="51">
         <v>0.18086951250960706</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" s="51">
         <v>0.23207708077500677</v>
@@ -3724,7 +3724,7 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" s="51">
         <v>0.21015208408946234</v>
@@ -3751,7 +3751,7 @@
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="51">
         <v>0.20633277488869373</v>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16" s="51">
         <v>0.2432575679919738</v>
@@ -3805,7 +3805,7 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C17" s="51">
         <v>0.23764030096933392</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C18" s="51">
         <v>0.24834877921903614</v>
@@ -3861,7 +3861,7 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C19" s="51">
         <v>0.2878858356907664</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C20" s="51">
         <v>0.315575827396339</v>
@@ -3919,7 +3919,7 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" s="51">
         <v>0.36625733986616116</v>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C22" s="51">
         <v>0.39845123393113063</v>
@@ -3977,7 +3977,7 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" s="51">
         <v>0.41844495728496567</v>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C24" s="51">
         <v>0.44069783806227414</v>
@@ -4035,7 +4035,7 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C25" s="51">
         <v>0.49721640798987476</v>
@@ -4064,7 +4064,7 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C26" s="51">
         <v>0.4587206537436371</v>
@@ -4093,7 +4093,7 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C27" s="51">
         <v>0.4594737062181282</v>
@@ -4122,7 +4122,7 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C28" s="51">
         <v>0.5508993209919991</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C29" s="51">
         <v>0.5074384647847622</v>
@@ -4180,7 +4180,7 @@
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C30" s="51">
         <v>0.5345447507445569</v>
@@ -4209,7 +4209,7 @@
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C31" s="51">
         <v>0.5799296740397282</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C32" s="51">
         <v>0.5805241891511685</v>
@@ -4267,7 +4267,7 @@
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33" s="51">
         <v>0.6592235774183274</v>
@@ -4296,7 +4296,7 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C34" s="51">
         <v>0.6418313080672801</v>
@@ -4325,7 +4325,7 @@
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C35" s="51">
         <v>0.6702635428816812</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C36" s="51">
         <v>0.6850255332548407</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C37" s="51">
         <v>0.7499069490833696</v>
@@ -4412,7 +4412,7 @@
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C38" s="51">
         <v>0.6485439241437253</v>
@@ -4441,7 +4441,7 @@
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C39" s="51">
         <v>0.6201333080606493</v>
@@ -4470,7 +4470,7 @@
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C40" s="51">
         <v>0.7136199085541801</v>
@@ -4499,7 +4499,7 @@
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C41" s="51">
         <v>0.6749115701165789</v>
@@ -4528,7 +4528,7 @@
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C42" s="51">
         <v>0.7288899391134795</v>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C43" s="51">
         <v>0.7433600766137501</v>
@@ -4586,7 +4586,7 @@
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C44" s="51">
         <v>0.7285044050715153</v>
@@ -4615,7 +4615,7 @@
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C45" s="51">
         <v>0.7945820573667</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C46" s="51">
         <v>0.7445527099585185</v>
@@ -4673,7 +4673,7 @@
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C47" s="51">
         <v>0.8220630680027965</v>
@@ -4702,7 +4702,7 @@
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C48" s="51">
         <v>0.8224269833134358</v>
@@ -4731,7 +4731,7 @@
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C49" s="51">
         <v>0.8721536684830657</v>
@@ -4760,7 +4760,7 @@
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C50" s="51">
         <v>0.8316329597360431</v>
@@ -4789,7 +4789,7 @@
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C51" s="51">
         <v>0.7798056545059904</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C52" s="51">
         <v>0.8598018172960398</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C53" s="51">
         <v>0.81316424548195</v>
@@ -4876,7 +4876,7 @@
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C54" s="51">
         <v>0.878199846649862</v>
@@ -4905,7 +4905,7 @@
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C55" s="51">
         <v>0.895634128359383</v>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C56" s="51">
         <v>0.8777353376501311</v>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C57" s="51">
         <v>0.9573487072395004</v>
@@ -4992,7 +4992,7 @@
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C58" s="51">
         <v>0.897071067414625</v>
@@ -5021,7 +5021,7 @@
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C59" s="51">
         <v>0.9904590823885333</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C60" s="51">
         <v>0.9908975441546343</v>
@@ -5079,7 +5079,7 @@
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C61" s="51">
         <v>0.9937017428763146</v>
@@ -5108,7 +5108,7 @@
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C62" s="51">
         <v>0.9986435273612461</v>
@@ -5137,7 +5137,7 @@
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C63" s="51">
         <v>1</v>
@@ -5215,32 +5215,32 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="67" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1" s="67" t="s">
         <v>152</v>
-      </c>
-      <c r="G1" s="67" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="3" spans="2:190" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D3" t="s">
         <v>154</v>
-      </c>
-      <c r="D3" t="s">
-        <v>155</v>
       </c>
       <c r="E3" s="65"/>
       <c r="F3" s="65"/>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I3" s="65" t="s">
         <v>156</v>
-      </c>
-      <c r="I3" s="65" t="s">
-        <v>157</v>
       </c>
       <c r="J3" s="65"/>
       <c r="K3" s="65"/>
@@ -5436,7 +5436,7 @@
         <v>755.3537766726711</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H4" s="51">
         <v>1</v>
@@ -5457,7 +5457,7 @@
         <v>7363.051608239055</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H5" s="51">
         <v>0.901351518911394</v>
@@ -5478,7 +5478,7 @@
         <v>16720.76739495377</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H6" s="51">
         <v>0.8188694670127475</v>
@@ -5499,7 +5499,7 @@
         <v>17203.5768849056</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H7" s="51">
         <v>0.7302873968132739</v>
@@ -5520,7 +5520,7 @@
         <v>20342.227664131788</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H8" s="51">
         <v>0.6509164769434985</v>
@@ -5541,7 +5541,7 @@
         <v>21780.412287401174</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H9" s="51">
         <v>0.5824549749858094</v>
@@ -5558,7 +5558,7 @@
         <v>17982.960788772907</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H10" s="51">
         <v>0.557878163361794</v>
@@ -5572,7 +5572,7 @@
         <v>21680.969498555165</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H11" s="51">
         <v>0.5367591461398546</v>
@@ -5586,7 +5586,7 @@
         <v>22262.124739157378</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H12" s="51">
         <v>0.5164894592233565</v>
@@ -5600,7 +5600,7 @@
         <v>24010.098480228906</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H13" s="51">
         <v>0.4983590995890034</v>
@@ -5614,7 +5614,7 @@
         <v>24577.43744758986</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H14" s="51">
         <v>0.48131960314016</v>
@@ -5628,7 +5628,7 @@
         <v>25250.57493014599</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H15" s="51">
         <v>0.46640327524352176</v>
@@ -5642,7 +5642,7 @@
         <v>25981.313510541717</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H16" s="51">
         <v>0.45375317406651494</v>
@@ -5656,7 +5656,7 @@
         <v>26590.062958108236</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H17" s="51">
         <v>0.44178850750555915</v>
@@ -5670,7 +5670,7 @@
         <v>27149.503654956992</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H18" s="51">
         <v>0.4302469671706629</v>
@@ -5684,7 +5684,7 @@
         <v>27723.50591838969</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H19" s="51">
         <v>0.419644705745174</v>
@@ -5698,7 +5698,7 @@
         <v>28278.54261980982</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H20" s="51">
         <v>0.4086786453757704</v>
@@ -5712,7 +5712,7 @@
         <v>28948.388153367734</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H21" s="51">
         <v>0.3983849387457999</v>
@@ -5726,7 +5726,7 @@
         <v>29542.7321240539</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H22" s="51">
         <v>0.390417774804375</v>
@@ -5740,7 +5740,7 @@
         <v>30063.291329528372</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H23" s="51">
         <v>0.3832313803262805</v>
@@ -5754,7 +5754,7 @@
         <v>30587.474062057372</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H24" s="51">
         <v>0.3757842163848556</v>
@@ -5768,7 +5768,7 @@
         <v>31081.90939352426</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H25" s="51">
         <v>0.37058903579461955</v>
@@ -5782,7 +5782,7 @@
         <v>31650.37938929695</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H26" s="51">
         <v>0.3636618718531946</v>
@@ -5796,7 +5796,7 @@
         <v>32300.717743710742</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H27" s="51">
         <v>0.35846669126295855</v>
@@ -5810,7 +5810,7 @@
         <v>33008.55488362522</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H28" s="51">
         <v>0.35327151067272244</v>
@@ -5824,7 +5824,7 @@
         <v>33512.319467426336</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H29" s="51">
         <v>0.3480763300824864</v>
@@ -5838,7 +5838,7 @@
         <v>34098.10152128227</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H30" s="51">
         <v>0.3428811494922503</v>
@@ -5852,7 +5852,7 @@
         <v>34607.118970474345</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H31" s="51">
         <v>0.33768596890201424</v>
@@ -5866,7 +5866,7 @@
         <v>35195.935314008966</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H32" s="51">
         <v>0.33422277166296704</v>
@@ -5880,7 +5880,7 @@
         <v>35771.833111260006</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H33" s="51">
         <v>0.32902759107273094</v>
@@ -5894,7 +5894,7 @@
         <v>36310.991018905865</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H34" s="51">
         <v>0.3255643938336837</v>
@@ -5908,7 +5908,7 @@
         <v>36873.35095607688</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H35" s="51">
         <v>0.322100427131306</v>
@@ -5922,7 +5922,7 @@
         <v>37307.01455063151</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H36" s="51">
         <v>0.3186372298922588</v>
@@ -5936,7 +5936,7 @@
         <v>37773.23609035687</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H37" s="51">
         <v>0.31517403265321153</v>
@@ -5950,7 +5950,7 @@
         <v>38350.945645873675</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H38" s="51">
         <v>0.3117100659508339</v>
@@ -5964,7 +5964,7 @@
         <v>39192.504612957564</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H39" s="51">
         <v>0.30824686871178664</v>
@@ -5978,7 +5978,7 @@
         <v>40177.80199605892</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H40" s="51">
         <v>0.30478367147273944</v>
@@ -5992,7 +5992,7 @@
         <v>40653.313122332496</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H41" s="51">
         <v>0.3030516881215506</v>
@@ -6006,7 +6006,7 @@
         <v>41230.91050471592</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H42" s="51">
         <v>0.29958849088250333</v>
@@ -6020,7 +6020,7 @@
         <v>41750.06402680537</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H43" s="51">
         <v>0.29785650753131454</v>
@@ -6034,7 +6034,7 @@
         <v>42402.03493617121</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H44" s="51">
         <v>0.2943933102922673</v>
@@ -6048,7 +6048,7 @@
         <v>42948.81780920555</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H45" s="51">
         <v>0.29266132694107844</v>
@@ -6062,7 +6062,7 @@
         <v>43107.15232725287</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H46" s="51">
         <v>0.2909301130532201</v>
@@ -6076,7 +6076,7 @@
         <v>43323.72661174839</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H47" s="51">
         <v>0.28746614635084244</v>
@@ -6090,7 +6090,7 @@
         <v>43379.713254110735</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H48" s="51">
         <v>0.285734932462984</v>
@@ -6104,7 +6104,7 @@
         <v>43452.67660587634</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H49" s="51">
         <v>0.28400294911179513</v>
@@ -6118,7 +6118,7 @@
         <v>43476.48632219695</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H50" s="51">
         <v>0.2822709657606063</v>
@@ -6132,7 +6132,7 @@
         <v>43609.07701202549</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H51" s="51">
         <v>0.28053975187274793</v>
@@ -6146,7 +6146,7 @@
         <v>43818.725496274834</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H52" s="51">
         <v>0.2788077685215591</v>
@@ -6160,7 +6160,7 @@
         <v>43695.03769421823</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H53" s="51">
         <v>0.27707578517037024</v>
@@ -6174,7 +6174,7 @@
         <v>43653.22830820949</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H54" s="51">
         <v>0.2753445712825119</v>
@@ -6188,7 +6188,7 @@
         <v>43555.4243740708</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H55" s="51">
         <v>0.273612587931323</v>
@@ -6202,7 +6202,7 @@
         <v>43560.5015501366</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H56" s="51">
         <v>0.2718806045801342</v>
@@ -6216,7 +6216,7 @@
         <v>43565.63924255693</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H57" s="51">
         <v>0.2718806045801342</v>
@@ -6230,7 +6230,7 @@
         <v>43440.26477604743</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H58" s="51">
         <v>0.2701493906922758</v>
@@ -6244,7 +6244,7 @@
         <v>43361.37985636941</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H59" s="51">
         <v>0.26841740734108693</v>
@@ -6258,7 +6258,7 @@
         <v>43235.870826385544</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H60" s="51">
         <v>0.2666854239898981</v>
@@ -6272,7 +6272,7 @@
         <v>43110.361796401674</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H61" s="51">
         <v>0.2666854239898981</v>
@@ -6286,7 +6286,7 @@
         <v>43047.85734887935</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H62" s="51">
         <v>0.26495421010203973</v>
@@ -6300,7 +6300,7 @@
         <v>43056.38509853063</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H63" s="51">
         <v>0.2632222267508509</v>
@@ -6314,7 +6314,7 @@
         <v>43110.84674156823</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H64" s="51">
         <v>0.2632222267508509</v>
@@ -6328,7 +6328,7 @@
         <v>43111.30243550642</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H65" s="51">
         <v>0.261490243399662</v>
@@ -6342,7 +6342,7 @@
         <v>43161.08417370434</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H66" s="51">
         <v>0.261490243399662</v>
@@ -6356,7 +6356,7 @@
         <v>43177.32344859251</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H67" s="51">
         <v>0.25975902951180363</v>
@@ -6370,7 +6370,7 @@
         <v>43227.587870865435</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H68" s="51">
         <v>0.2580270461606148</v>
@@ -6384,7 +6384,7 @@
         <v>43306.574820151465</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H69" s="51">
         <v>0.2580270461606148</v>
@@ -6398,7 +6398,7 @@
         <v>43306.574820151465</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H70" s="51">
         <v>0.25629506280942593</v>
@@ -6412,7 +6412,7 @@
         <v>43334.954963298725</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H71" s="51">
         <v>0.25629506280942593</v>
@@ -6426,7 +6426,7 @@
         <v>43334.954963298725</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H72" s="51">
         <v>0.2545638489215676</v>
@@ -6440,7 +6440,7 @@
         <v>43334.954963298725</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H73" s="51">
         <v>0.2545638489215676</v>
@@ -6454,7 +6454,7 @@
         <v>43325.00078598156</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H74" s="51">
         <v>0.25283186557037873</v>
@@ -6468,7 +6468,7 @@
         <v>43241.01695159193</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H75" s="51">
         <v>0.25283186557037873</v>
@@ -6482,7 +6482,7 @@
         <v>43127.68497133806</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H76" s="51">
         <v>0.2510998822191899</v>
@@ -6496,7 +6496,7 @@
         <v>43127.39870741521</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H77" s="51">
         <v>0.2510998822191899</v>
@@ -6510,7 +6510,7 @@
         <v>43096.12614820737</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H78" s="51">
         <v>0.24936866833133148</v>
@@ -6524,7 +6524,7 @@
         <v>43085.924742956835</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H79" s="51">
         <v>0.24936866833133148</v>
@@ -6538,7 +6538,7 @@
         <v>43054.34896480041</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H80" s="51">
         <v>0.24763668498014263</v>
@@ -6552,7 +6552,7 @@
         <v>43004.72988484032</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H81" s="51">
         <v>0.24763668498014263</v>
@@ -6566,7 +6566,7 @@
         <v>43004.72988484032</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H82" s="51">
         <v>0.24590470162895378</v>
@@ -6580,7 +6580,7 @@
         <v>42986.90166632028</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H83" s="51">
         <v>0.24590470162895378</v>
@@ -6594,7 +6594,7 @@
         <v>42986.90166632028</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H84" s="51">
         <v>0.24590470162895378</v>
@@ -6608,7 +6608,7 @@
         <v>42986.90166632028</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H85" s="51">
         <v>0.24417348774109537</v>
@@ -6622,7 +6622,7 @@
         <v>42990.88827713235</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H86" s="51">
         <v>0.24417348774109537</v>
@@ -6636,7 +6636,7 @@
         <v>43024.52348891821</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H87" s="51">
         <v>0.24244150438990655</v>
@@ -6650,7 +6650,7 @@
         <v>43069.91252343484</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H88" s="51">
         <v>0.24244150438990655</v>
@@ -6664,7 +6664,7 @@
         <v>43070.02717106604</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H89" s="51">
         <v>0.24070952103871773</v>
@@ -6678,7 +6678,7 @@
         <v>43082.551714148474</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H90" s="51">
         <v>0.24070952103871773</v>
@@ -6692,7 +6692,7 @@
         <v>43086.63733882385</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H91" s="51">
         <v>0.24070952103871773</v>
@@ -6706,7 +6706,7 @@
         <v>43099.28331996193</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H92" s="51">
         <v>0.23897830715085933</v>
@@ -6720,7 +6720,7 @@
         <v>43119.15557603605</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H93" s="51">
         <v>0.23897830715085933</v>
@@ -6734,7 +6734,7 @@
         <v>43119.15557603605</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H94" s="51">
         <v>0.23724632379967048</v>
@@ -6748,7 +6748,7 @@
         <v>43126.29571092087</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H95" s="51">
         <v>0.23724632379967048</v>
@@ -6762,7 +6762,7 @@
         <v>43126.29571092087</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H96" s="51">
         <v>0.23724632379967048</v>
@@ -6776,7 +6776,7 @@
         <v>43126.29571092087</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H97" s="51">
         <v>0.23551434044848166</v>
@@ -6790,7 +6790,7 @@
         <v>43132.51471737827</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H98" s="51">
         <v>0.23551434044848166</v>
@@ -6804,7 +6804,7 @@
         <v>43184.98474998307</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H99" s="51">
         <v>0.23551434044848166</v>
@@ -6818,7 +6818,7 @@
         <v>43255.79043231832</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H100" s="51">
         <v>0.23378312656062325</v>
@@ -6832,7 +6832,7 @@
         <v>43255.96927956285</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H101" s="51">
         <v>0.23378312656062325</v>
@@ -6846,7 +6846,7 @@
         <v>43275.507232470045</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H102" s="51">
         <v>0.23378312656062325</v>
@@ -6860,7 +6860,7 @@
         <v>43281.88069791135</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H103" s="51">
         <v>0.2320511432094344</v>
@@ -6874,7 +6874,7 @@
         <v>43301.608090943955</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H104" s="51">
         <v>0.2320511432094344</v>
@@ -6888,7 +6888,7 @@
         <v>43332.608279995206</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H105" s="51">
         <v>0.2320511432094344</v>
@@ -6902,7 +6902,7 @@
         <v>43332.608279995206</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H106" s="51">
         <v>0.23031915985824558</v>
@@ -6916,7 +6916,7 @@
         <v>43343.74669983315</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H107" s="51">
         <v>0.23031915985824558</v>
@@ -6930,7 +6930,7 @@
         <v>43343.74669983315</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H108" s="51">
         <v>0.23031915985824558</v>
@@ -6944,7 +6944,7 @@
         <v>43343.74669983315</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H109" s="51">
         <v>0.22858794597038715</v>
@@ -6958,7 +6958,7 @@
         <v>43349.71145932787</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H110" s="51">
         <v>0.22858794597038715</v>
@@ -6972,7 +6972,7 @@
         <v>43400.03639906094</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H111" s="51">
         <v>0.22858794597038715</v>
@@ -6986,7 +6986,7 @@
         <v>43467.94738594975</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H112" s="51">
         <v>0.22685596261919833</v>
@@ -7000,7 +7000,7 @@
         <v>43468.11892151692</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H113" s="51">
         <v>0.22685596261919833</v>
@@ -7014,7 +7014,7 @@
         <v>43486.8581189931</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H114" s="51">
         <v>0.22685596261919833</v>
@@ -7028,7 +7028,7 @@
         <v>43492.97102284129</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H115" s="51">
         <v>0.22512397926800948</v>
@@ -7042,7 +7042,7 @@
         <v>43511.89191570472</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H116" s="51">
         <v>0.22512397926800948</v>
@@ -7056,7 +7056,7 @@
         <v>43541.62474734727</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H117" s="51">
         <v>0.22512397926800948</v>
@@ -7070,7 +7070,7 @@
         <v>43541.62474734727</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H118" s="51">
         <v>0.2233927653801511</v>
@@ -7084,7 +7084,7 @@
         <v>43552.30780354599</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H119" s="51">
         <v>0.2233927653801511</v>
@@ -7098,7 +7098,7 @@
         <v>43552.30780354599</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H120" s="51">
         <v>0.2233927653801511</v>
@@ -7112,7 +7112,7 @@
         <v>43552.30780354599</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H121" s="51">
         <v>0.22166078202896228</v>
@@ -7126,7 +7126,7 @@
         <v>43558.059639988765</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H122" s="51">
         <v>0.22166078202896228</v>
@@ -7140,7 +7140,7 @@
         <v>43606.58813851299</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H123" s="51">
         <v>0.22166078202896228</v>
@@ -7154,7 +7154,7 @@
         <v>43672.07491792083</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H124" s="51">
         <v>0.2199287986777734</v>
@@ -7168,7 +7168,7 @@
         <v>43672.24033021068</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H125" s="51">
         <v>0.2199287986777734</v>
@@ -7182,7 +7182,7 @@
         <v>43690.310597594835</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H126" s="51">
         <v>0.2199287986777734</v>
@@ -7196,7 +7196,7 @@
         <v>43696.20529010612</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H127" s="51">
         <v>0.21819758478991505</v>
@@ -7210,7 +7210,7 @@
         <v>43714.45076692677</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H128" s="51">
         <v>0.21819758478991505</v>
@@ -7224,7 +7224,7 @@
         <v>43743.12223050208</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H129" s="51">
         <v>0.21819758478991505</v>
@@ -7238,7 +7238,7 @@
         <v>43743.12223050208</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H130" s="51">
         <v>0.2164656014387262</v>
@@ -7252,7 +7252,7 @@
         <v>43753.42393537692</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H131" s="51">
         <v>0.2164656014387262</v>
@@ -7266,7 +7266,7 @@
         <v>43753.42393537692</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H132" s="51">
         <v>0.2164656014387262</v>
@@ -7280,7 +7280,7 @@
         <v>43753.42393537692</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H133" s="51">
         <v>0.21473361808753735</v>
@@ -7294,7 +7294,7 @@
         <v>43758.99492786032</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H134" s="51">
         <v>0.21473361808753735</v>
@@ -7308,7 +7308,7 @@
         <v>43805.99763789895</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H135" s="51">
         <v>0.21473361808753735</v>
@@ -7322,7 +7322,7 @@
         <v>43869.42544212688</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H136" s="51">
         <v>0.21473361808753735</v>
@@ -7336,7 +7336,7 @@
         <v>43869.58565367542</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H137" s="51">
         <v>0.21300240419967897</v>
@@ -7350,7 +7350,7 @@
         <v>43887.08777230687</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H138" s="51">
         <v>0.21300240419967897</v>
@@ -7364,7 +7364,7 @@
         <v>43892.79712930947</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H139" s="51">
         <v>0.21300240419967897</v>
@@ -7378,7 +7378,7 @@
         <v>43910.468948603215</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H140" s="51">
         <v>0.21127042084849015</v>
@@ -7392,7 +7392,7 @@
         <v>43938.238950350555</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H141" s="51">
         <v>0.21127042084849015</v>
@@ -7406,7 +7406,7 @@
         <v>43938.238950350555</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H142" s="51">
         <v>0.21127042084849015</v>
@@ -7420,7 +7420,7 @@
         <v>43948.216758481045</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H143" s="51">
         <v>0.20953843749730128</v>
@@ -7434,7 +7434,7 @@
         <v>43948.216758481045</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H144" s="51">
         <v>0.20953843749730128</v>
@@ -7448,7 +7448,7 @@
         <v>43948.216758481045</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H145" s="51">
         <v>0.20953843749730128</v>
@@ -7462,7 +7462,7 @@
         <v>43953.63230343142</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H146" s="51">
         <v>0.20953843749730128</v>
@@ -7476,7 +7476,7 @@
         <v>43999.32349575703</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H147" s="51">
         <v>0.2078072236094429</v>
@@ -7490,7 +7490,7 @@
         <v>44060.9814724862</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H148" s="51">
         <v>0.2078072236094429</v>
@@ -7504,7 +7504,7 @@
         <v>44061.13721364817</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H149" s="51">
         <v>0.2078072236094429</v>
@@ -7518,7 +7518,7 @@
         <v>44078.150970255796</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H150" s="51">
         <v>0.20607524025825408</v>
@@ -7532,7 +7532,7 @@
         <v>44083.70101893697</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H151" s="51">
         <v>0.20607524025825408</v>
@@ -7546,7 +7546,7 @@
         <v>44100.87974104536</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H152" s="51">
         <v>0.20607524025825408</v>
@@ -7560,7 +7560,7 @@
         <v>44127.8748757871</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H153" s="51">
         <v>0.20607524025825408</v>
@@ -7574,7 +7574,7 @@
         <v>44127.8748757871</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H154" s="51">
         <v>0.20434325690706523</v>
@@ -7588,7 +7588,7 @@
         <v>44137.57427290492</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H155" s="51">
         <v>0.20434325690706523</v>
@@ -7602,7 +7602,7 @@
         <v>44137.57427290492</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H156" s="51">
         <v>0.20434325690706523</v>
@@ -7616,7 +7616,7 @@
         <v>44137.57427290492</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H157" s="51">
         <v>0.20261204301920682</v>
@@ -7630,7 +7630,7 @@
         <v>44141.91603693603</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H158" s="51">
         <v>0.20261204301920682</v>
@@ -7644,7 +7644,7 @@
         <v>44178.54769214255</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H159" s="51">
         <v>0.20261204301920682</v>
@@ -7658,7 +7658,7 @@
         <v>44227.980277052535</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H160" s="51">
         <v>0.20261204301920682</v>
@@ -7672,7 +7672,7 @@
         <v>44228.10513824036</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H161" s="51">
         <v>0.20088005966801797</v>
@@ -7686,7 +7686,7 @@
         <v>44241.74544907699</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H162" s="51">
         <v>0.20088005966801797</v>
@@ -7700,7 +7700,7 @@
         <v>44246.19504777031</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H163" s="51">
         <v>0.20088005966801797</v>
@@ -7714,7 +7714,7 @@
         <v>44259.96761515437</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H164" s="51">
         <v>0.20088005966801797</v>
@@ -7728,7 +7728,7 @@
         <v>44281.61022104362</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H165" s="51">
         <v>0.19914807631682915</v>
@@ -7742,7 +7742,7 @@
         <v>44281.61022104362</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H166" s="51">
         <v>0.19914807631682915</v>
@@ -7756,7 +7756,7 @@
         <v>44289.38644558158</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H167" s="51">
         <v>0.19914807631682915</v>
@@ -7770,7 +7770,7 @@
         <v>44289.38644558158</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H168" s="51">
         <v>0.19914807631682915</v>
@@ -7784,7 +7784,7 @@
         <v>44289.38644558158</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H169" s="51">
         <v>0.19741686242897075</v>
@@ -7798,7 +7798,7 @@
         <v>44293.60695989818</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H170" s="51">
         <v>0.19741686242897075</v>
@@ -7812,7 +7812,7 @@
         <v>44329.215625899444</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H171" s="51">
         <v>0.19741686242897075</v>
@@ -7826,7 +7826,7 @@
         <v>44377.26773808808</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H172" s="51">
         <v>0.19741686242897075</v>
@@ -7840,7 +7840,7 @@
         <v>44377.389112356</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H173" s="51">
         <v>0.19568487907778193</v>
@@ -7854,7 +7854,7 @@
         <v>44390.648498807335</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H174" s="51">
         <v>0.19568487907778193</v>
@@ -7868,7 +7868,7 @@
         <v>44394.973836355326</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H175" s="51">
         <v>0.19568487907778193</v>
@@ -7882,7 +7882,7 @@
         <v>44408.36178590864</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H176" s="51">
         <v>0.19568487907778193</v>
@@ -7896,7 +7896,7 @@
         <v>44429.39999234956</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H177" s="51">
         <v>0.19395289572659308</v>
@@ -7910,7 +7910,7 @@
         <v>44429.39999234956</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H178" s="51">
         <v>0.19395289572659308</v>
@@ -7924,7 +7924,7 @@
         <v>44436.95905515363</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H179" s="51">
         <v>0.19395289572659308</v>
@@ -7938,7 +7938,7 @@
         <v>44436.95905515363</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H180" s="51">
         <v>0.19395289572659308</v>
@@ -7952,7 +7952,7 @@
         <v>44436.95905515363</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H181" s="51">
         <v>0.1922216818387347</v>
@@ -7966,7 +7966,7 @@
         <v>44441.072389191984</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H182" s="51">
         <v>0.1922216818387347</v>
@@ -7980,7 +7980,7 @@
         <v>44475.77677044406</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H183" s="51">
         <v>0.1922216818387347</v>
@@ -7994,7 +7994,7 @@
         <v>44522.60859563244</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H184" s="51">
         <v>0.1922216818387347</v>
@@ -8008,7 +8008,7 @@
         <v>44522.726887591714</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H185" s="51">
         <v>0.1922216818387347</v>
@@ -8022,7 +8022,7 @@
         <v>44535.64955092764</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H186" s="51">
         <v>0.19048969848754585</v>
@@ -8036,7 +8036,7 @@
         <v>44539.865046203544</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H187" s="51">
         <v>0.19048969848754585</v>
@@ -8050,7 +8050,7 @@
         <v>44552.91300777181</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H188" s="51">
         <v>0.19048969848754585</v>
@@ -8064,7 +8064,7 @@
         <v>44573.41694737909</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H189" s="51">
         <v>0.19048969848754585</v>
@@ -8072,7 +8072,7 @@
     </row>
     <row r="190" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G190" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H190" s="51">
         <v>0.188757715136357</v>
@@ -8080,7 +8080,7 @@
     </row>
     <row r="191" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G191" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H191" s="51">
         <v>0.188757715136357</v>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="192" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G192" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H192" s="51">
         <v>0.188757715136357</v>
@@ -8096,7 +8096,7 @@
     </row>
     <row r="193" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G193" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H193" s="51">
         <v>0.188757715136357</v>
@@ -8119,7 +8119,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="73" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="74" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B2" s="74"/>
       <c r="C2" s="74"/>
@@ -8141,25 +8141,25 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="75" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3" s="75" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C3" s="75" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D3" s="75" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E3" s="75" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F3" s="75" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G3" s="75" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8481,7 +8481,7 @@
         <v>0.16329999999999997</v>
       </c>
       <c r="G17" s="78">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8504,7 +8504,7 @@
         <v>0.16670000000000001</v>
       </c>
       <c r="G18" s="78">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8527,7 +8527,7 @@
         <v>0.17</v>
       </c>
       <c r="G19" s="78">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8550,7 +8550,7 @@
         <v>0.17</v>
       </c>
       <c r="G20" s="78">
-        <v>0.0433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8573,7 +8573,7 @@
         <v>0.17</v>
       </c>
       <c r="G21" s="78">
-        <v>0.0567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8734,32 +8734,32 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="73" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="74" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B2" s="74"/>
       <c r="C2" s="74"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="75" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B3" s="75" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C3" s="75" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="79" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B4" s="80">
         <v>3200</v>
@@ -8770,7 +8770,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="79" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B5" s="80">
         <v>2600</v>
@@ -8781,7 +8781,7 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="79" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B6" s="80">
         <v>900</v>
@@ -8810,7 +8810,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="73" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
@@ -8818,7 +8818,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="74" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B2" s="74"/>
       <c r="C2" s="74"/>
@@ -8826,7 +8826,7 @@
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="75" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3" s="75" t="s">
         <v>1</v>
@@ -8835,7 +8835,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="75" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -8849,7 +8849,7 @@
         <v>0.79</v>
       </c>
       <c r="D4" s="79" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -8863,7 +8863,7 @@
         <v>0.8</v>
       </c>
       <c r="D5" s="79" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -8877,7 +8877,7 @@
         <v>0.81</v>
       </c>
       <c r="D6" s="79" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -8891,7 +8891,7 @@
         <v>0.82</v>
       </c>
       <c r="D7" s="79" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -8905,7 +8905,7 @@
         <v>0.82</v>
       </c>
       <c r="D8" s="79" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -8919,7 +8919,7 @@
         <v>0.83</v>
       </c>
       <c r="D9" s="79" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/NAP mock data.xlsx
+++ b/NAP mock data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67C62745-9340-49A2-9CCF-16EDEAC747D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB25A1BC-D18D-419C-AA3F-EF60F349B971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market growth" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="Compliance" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="323">
   <si>
     <t>Year</t>
   </si>
@@ -999,9 +998,6 @@
   </si>
   <si>
     <t>8.4 mo</t>
-  </si>
-  <si>
-    <t>Revalidate</t>
   </si>
   <si>
     <t>Access</t>
@@ -1759,12 +1755,6 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1786,6 +1776,12 @@
     </xf>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2780,19 +2776,19 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="82" t="s">
+      <c r="C3" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="83" t="s">
+      <c r="D3" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="84" t="s">
+      <c r="E3" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="82" t="s">
         <v>62</v>
       </c>
       <c r="G3" s="45"/>
@@ -2804,19 +2800,19 @@
       <c r="O3" s="48"/>
     </row>
     <row r="4" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="85">
+      <c r="B4" s="83">
         <v>46204</v>
       </c>
-      <c r="C4" s="86">
+      <c r="C4" s="84">
         <v>0.02</v>
       </c>
-      <c r="D4" s="87">
+      <c r="D4" s="85">
         <v>1.9E-2</v>
       </c>
-      <c r="E4" s="88">
+      <c r="E4" s="86">
         <v>16000</v>
       </c>
-      <c r="F4" s="88">
+      <c r="F4" s="86">
         <v>18240</v>
       </c>
       <c r="G4" s="49"/>
@@ -2830,19 +2826,19 @@
       <c r="O4" s="16"/>
     </row>
     <row r="5" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="85">
+      <c r="B5" s="83">
         <v>46235</v>
       </c>
-      <c r="C5" s="86">
+      <c r="C5" s="84">
         <v>0.03</v>
       </c>
-      <c r="D5" s="87">
+      <c r="D5" s="85">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="E5" s="88">
+      <c r="E5" s="86">
         <v>32333</v>
       </c>
-      <c r="F5" s="88">
+      <c r="F5" s="86">
         <v>34920</v>
       </c>
       <c r="G5" s="49"/>
@@ -2856,19 +2852,19 @@
       <c r="O5" s="16"/>
     </row>
     <row r="6" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="85">
+      <c r="B6" s="83">
         <v>46266</v>
       </c>
-      <c r="C6" s="86">
+      <c r="C6" s="84">
         <v>0.05</v>
       </c>
-      <c r="D6" s="87">
+      <c r="D6" s="85">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="E6" s="88">
+      <c r="E6" s="86">
         <v>49000</v>
       </c>
-      <c r="F6" s="88">
+      <c r="F6" s="86">
         <v>52920</v>
       </c>
       <c r="G6" s="49"/>
@@ -2880,19 +2876,19 @@
       <c r="O6" s="16"/>
     </row>
     <row r="7" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="85">
+      <c r="B7" s="83">
         <v>46296</v>
       </c>
-      <c r="C7" s="86">
+      <c r="C7" s="84">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D7" s="87">
+      <c r="D7" s="85">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="E7" s="88">
+      <c r="E7" s="86">
         <v>66000</v>
       </c>
-      <c r="F7" s="88">
+      <c r="F7" s="86">
         <v>70290</v>
       </c>
       <c r="G7" s="49"/>
@@ -2904,19 +2900,19 @@
       <c r="O7" s="16"/>
     </row>
     <row r="8" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="85">
+      <c r="B8" s="83">
         <v>46327</v>
       </c>
-      <c r="C8" s="86">
+      <c r="C8" s="84">
         <v>0.08</v>
       </c>
-      <c r="D8" s="87">
+      <c r="D8" s="85">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="E8" s="88">
+      <c r="E8" s="86">
         <v>83333</v>
       </c>
-      <c r="F8" s="88">
+      <c r="F8" s="86">
         <v>88000</v>
       </c>
       <c r="G8" s="49"/>
@@ -2928,19 +2924,19 @@
       <c r="O8" s="16"/>
     </row>
     <row r="9" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="85">
+      <c r="B9" s="83">
         <v>46357</v>
       </c>
-      <c r="C9" s="86">
+      <c r="C9" s="84">
         <v>0.1</v>
       </c>
-      <c r="D9" s="87">
+      <c r="D9" s="85">
         <v>0.104</v>
       </c>
-      <c r="E9" s="88">
+      <c r="E9" s="86">
         <v>101000</v>
       </c>
-      <c r="F9" s="88">
+      <c r="F9" s="86">
         <v>105040</v>
       </c>
       <c r="G9" s="49"/>
@@ -2952,810 +2948,810 @@
       <c r="O9" s="16"/>
     </row>
     <row r="10" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="85">
+      <c r="B10" s="83">
         <v>46388</v>
       </c>
-      <c r="C10" s="86">
+      <c r="C10" s="84">
         <v>0.12</v>
       </c>
-      <c r="D10" s="89"/>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
       <c r="G10" s="49"/>
       <c r="H10" s="49"/>
       <c r="I10" s="49"/>
       <c r="J10" s="49"/>
     </row>
     <row r="11" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="85">
+      <c r="B11" s="83">
         <v>46419</v>
       </c>
-      <c r="C11" s="86">
+      <c r="C11" s="84">
         <v>0.13</v>
       </c>
-      <c r="D11" s="89"/>
-      <c r="E11" s="89"/>
-      <c r="F11" s="89"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
       <c r="G11" s="49"/>
       <c r="H11" s="49"/>
       <c r="I11" s="49"/>
       <c r="J11" s="49"/>
     </row>
     <row r="12" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="85">
+      <c r="B12" s="83">
         <v>46447</v>
       </c>
-      <c r="C12" s="86">
+      <c r="C12" s="84">
         <v>0.15</v>
       </c>
-      <c r="D12" s="89"/>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
       <c r="G12" s="49"/>
       <c r="H12" s="49"/>
       <c r="I12" s="49"/>
       <c r="J12" s="49"/>
     </row>
     <row r="13" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="85">
+      <c r="B13" s="83">
         <v>46478</v>
       </c>
-      <c r="C13" s="86">
+      <c r="C13" s="84">
         <v>0.17</v>
       </c>
-      <c r="D13" s="89"/>
-      <c r="E13" s="89"/>
-      <c r="F13" s="89"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
       <c r="G13" s="49"/>
       <c r="H13" s="49"/>
       <c r="I13" s="49"/>
       <c r="J13" s="49"/>
     </row>
     <row r="14" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="85">
+      <c r="B14" s="83">
         <v>46508</v>
       </c>
-      <c r="C14" s="86">
+      <c r="C14" s="84">
         <v>0.18</v>
       </c>
-      <c r="D14" s="89"/>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="87"/>
       <c r="G14" s="49"/>
       <c r="H14" s="49"/>
       <c r="I14" s="49"/>
       <c r="J14" s="49"/>
     </row>
     <row r="15" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="85">
+      <c r="B15" s="83">
         <v>46539</v>
       </c>
-      <c r="C15" s="86">
+      <c r="C15" s="84">
         <v>0.2</v>
       </c>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87"/>
+      <c r="F15" s="87"/>
       <c r="G15" s="49"/>
       <c r="H15" s="49"/>
       <c r="I15" s="49"/>
       <c r="J15" s="49"/>
     </row>
     <row r="16" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="85">
+      <c r="B16" s="83">
         <v>46569</v>
       </c>
-      <c r="C16" s="86">
+      <c r="C16" s="84">
         <v>0.22</v>
       </c>
-      <c r="D16" s="89"/>
-      <c r="E16" s="89"/>
-      <c r="F16" s="89"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
       <c r="G16" s="49"/>
       <c r="H16" s="49"/>
       <c r="I16" s="49"/>
       <c r="J16" s="49"/>
     </row>
     <row r="17" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="85">
+      <c r="B17" s="83">
         <v>46600</v>
       </c>
-      <c r="C17" s="86">
+      <c r="C17" s="84">
         <v>0.23</v>
       </c>
-      <c r="D17" s="89"/>
-      <c r="E17" s="89"/>
-      <c r="F17" s="89"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="87"/>
       <c r="G17" s="49"/>
       <c r="H17" s="49"/>
       <c r="I17" s="49"/>
       <c r="J17" s="49"/>
     </row>
     <row r="18" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="85">
+      <c r="B18" s="83">
         <v>46631</v>
       </c>
-      <c r="C18" s="86">
+      <c r="C18" s="84">
         <v>0.25</v>
       </c>
-      <c r="D18" s="89"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="89"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
       <c r="G18" s="49"/>
       <c r="H18" s="49"/>
       <c r="I18" s="49"/>
       <c r="J18" s="49"/>
     </row>
     <row r="19" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="85">
+      <c r="B19" s="83">
         <v>46661</v>
       </c>
-      <c r="C19" s="86">
+      <c r="C19" s="84">
         <v>0.27</v>
       </c>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
       <c r="G19" s="49"/>
       <c r="H19" s="49"/>
       <c r="I19" s="49"/>
       <c r="J19" s="49"/>
     </row>
     <row r="20" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="85">
+      <c r="B20" s="83">
         <v>46692</v>
       </c>
-      <c r="C20" s="86">
+      <c r="C20" s="84">
         <v>0.28000000000000003</v>
       </c>
-      <c r="D20" s="89"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
       <c r="G20" s="49"/>
       <c r="H20" s="49"/>
       <c r="I20" s="49"/>
       <c r="J20" s="49"/>
     </row>
     <row r="21" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="85">
+      <c r="B21" s="83">
         <v>46722</v>
       </c>
-      <c r="C21" s="86">
+      <c r="C21" s="84">
         <v>0.3</v>
       </c>
-      <c r="D21" s="89"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
       <c r="G21" s="49"/>
       <c r="H21" s="49"/>
       <c r="I21" s="49"/>
       <c r="J21" s="49"/>
     </row>
     <row r="22" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="85">
+      <c r="B22" s="83">
         <v>46753</v>
       </c>
-      <c r="C22" s="86">
+      <c r="C22" s="84">
         <v>0.32</v>
       </c>
-      <c r="D22" s="89"/>
-      <c r="E22" s="89"/>
-      <c r="F22" s="89"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="87"/>
+      <c r="F22" s="87"/>
       <c r="G22" s="49"/>
       <c r="H22" s="49"/>
       <c r="I22" s="49"/>
       <c r="J22" s="49"/>
     </row>
     <row r="23" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="85">
+      <c r="B23" s="83">
         <v>46784</v>
       </c>
-      <c r="C23" s="86">
+      <c r="C23" s="84">
         <v>0.33</v>
       </c>
-      <c r="D23" s="89"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="89"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="87"/>
+      <c r="F23" s="87"/>
       <c r="G23" s="49"/>
       <c r="H23" s="49"/>
       <c r="I23" s="49"/>
       <c r="J23" s="49"/>
     </row>
     <row r="24" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="85">
+      <c r="B24" s="83">
         <v>46813</v>
       </c>
-      <c r="C24" s="86">
+      <c r="C24" s="84">
         <v>0.35</v>
       </c>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="87"/>
       <c r="G24" s="49"/>
       <c r="H24" s="49"/>
       <c r="I24" s="49"/>
       <c r="J24" s="49"/>
     </row>
     <row r="25" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="85">
+      <c r="B25" s="83">
         <v>46844</v>
       </c>
-      <c r="C25" s="86">
+      <c r="C25" s="84">
         <v>0.37</v>
       </c>
-      <c r="D25" s="89"/>
-      <c r="E25" s="89"/>
-      <c r="F25" s="89"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
       <c r="G25" s="49"/>
       <c r="H25" s="49"/>
       <c r="I25" s="49"/>
       <c r="J25" s="49"/>
     </row>
     <row r="26" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="85">
+      <c r="B26" s="83">
         <v>46874</v>
       </c>
-      <c r="C26" s="86">
+      <c r="C26" s="84">
         <v>0.38</v>
       </c>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="89"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="87"/>
       <c r="G26" s="49"/>
       <c r="H26" s="49"/>
       <c r="I26" s="49"/>
       <c r="J26" s="49"/>
     </row>
     <row r="27" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="85">
+      <c r="B27" s="83">
         <v>46905</v>
       </c>
-      <c r="C27" s="86">
+      <c r="C27" s="84">
         <v>0.4</v>
       </c>
-      <c r="D27" s="89"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="89"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="87"/>
       <c r="G27" s="49"/>
       <c r="H27" s="49"/>
       <c r="I27" s="49"/>
       <c r="J27" s="49"/>
     </row>
     <row r="28" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="85">
+      <c r="B28" s="83">
         <v>46935</v>
       </c>
-      <c r="C28" s="86">
+      <c r="C28" s="84">
         <v>0.42</v>
       </c>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
+      <c r="F28" s="87"/>
       <c r="G28" s="49"/>
       <c r="H28" s="49"/>
       <c r="I28" s="49"/>
       <c r="J28" s="49"/>
     </row>
     <row r="29" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="85">
+      <c r="B29" s="83">
         <v>46966</v>
       </c>
-      <c r="C29" s="86">
+      <c r="C29" s="84">
         <v>0.43</v>
       </c>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
+      <c r="F29" s="87"/>
       <c r="G29" s="49"/>
       <c r="H29" s="49"/>
       <c r="I29" s="49"/>
       <c r="J29" s="49"/>
     </row>
     <row r="30" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="85">
+      <c r="B30" s="83">
         <v>46997</v>
       </c>
-      <c r="C30" s="86">
+      <c r="C30" s="84">
         <v>0.45</v>
       </c>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="87"/>
+      <c r="F30" s="87"/>
       <c r="G30" s="49"/>
       <c r="H30" s="49"/>
       <c r="I30" s="49"/>
       <c r="J30" s="49"/>
     </row>
     <row r="31" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="85">
+      <c r="B31" s="83">
         <v>47027</v>
       </c>
-      <c r="C31" s="86">
+      <c r="C31" s="84">
         <v>0.47</v>
       </c>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="89"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
+      <c r="F31" s="87"/>
       <c r="G31" s="49"/>
       <c r="H31" s="49"/>
       <c r="I31" s="49"/>
       <c r="J31" s="49"/>
     </row>
     <row r="32" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="85">
+      <c r="B32" s="83">
         <v>47058</v>
       </c>
-      <c r="C32" s="86">
+      <c r="C32" s="84">
         <v>0.48</v>
       </c>
-      <c r="D32" s="89"/>
-      <c r="E32" s="89"/>
-      <c r="F32" s="89"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
+      <c r="F32" s="87"/>
       <c r="G32" s="49"/>
       <c r="H32" s="49"/>
       <c r="I32" s="49"/>
       <c r="J32" s="49"/>
     </row>
     <row r="33" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="85">
+      <c r="B33" s="83">
         <v>47088</v>
       </c>
-      <c r="C33" s="86">
+      <c r="C33" s="84">
         <v>0.5</v>
       </c>
-      <c r="D33" s="89"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="89"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
+      <c r="F33" s="87"/>
       <c r="G33" s="49"/>
       <c r="H33" s="49"/>
       <c r="I33" s="49"/>
       <c r="J33" s="49"/>
     </row>
     <row r="34" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85">
+      <c r="B34" s="83">
         <v>47119</v>
       </c>
-      <c r="C34" s="86">
+      <c r="C34" s="84">
         <v>0.52</v>
       </c>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="87"/>
+      <c r="F34" s="87"/>
       <c r="G34" s="49"/>
       <c r="H34" s="49"/>
       <c r="I34" s="49"/>
       <c r="J34" s="49"/>
     </row>
     <row r="35" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="85">
+      <c r="B35" s="83">
         <v>47150</v>
       </c>
-      <c r="C35" s="86">
+      <c r="C35" s="84">
         <v>0.53</v>
       </c>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="89"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
+      <c r="F35" s="87"/>
       <c r="G35" s="49"/>
       <c r="H35" s="49"/>
       <c r="I35" s="49"/>
       <c r="J35" s="49"/>
     </row>
     <row r="36" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="85">
+      <c r="B36" s="83">
         <v>47178</v>
       </c>
-      <c r="C36" s="86">
+      <c r="C36" s="84">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D36" s="89"/>
-      <c r="E36" s="89"/>
-      <c r="F36" s="89"/>
+      <c r="D36" s="87"/>
+      <c r="E36" s="87"/>
+      <c r="F36" s="87"/>
       <c r="G36" s="49"/>
       <c r="H36" s="49"/>
       <c r="I36" s="49"/>
       <c r="J36" s="49"/>
     </row>
     <row r="37" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="85">
+      <c r="B37" s="83">
         <v>47209</v>
       </c>
-      <c r="C37" s="86">
+      <c r="C37" s="84">
         <v>0.56999999999999995</v>
       </c>
-      <c r="D37" s="89"/>
-      <c r="E37" s="89"/>
-      <c r="F37" s="89"/>
+      <c r="D37" s="87"/>
+      <c r="E37" s="87"/>
+      <c r="F37" s="87"/>
       <c r="G37" s="49"/>
       <c r="H37" s="49"/>
       <c r="I37" s="49"/>
       <c r="J37" s="49"/>
     </row>
     <row r="38" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="85">
+      <c r="B38" s="83">
         <v>47239</v>
       </c>
-      <c r="C38" s="86">
+      <c r="C38" s="84">
         <v>0.57999999999999996</v>
       </c>
-      <c r="D38" s="89"/>
-      <c r="E38" s="89"/>
-      <c r="F38" s="89"/>
+      <c r="D38" s="87"/>
+      <c r="E38" s="87"/>
+      <c r="F38" s="87"/>
       <c r="G38" s="49"/>
       <c r="H38" s="49"/>
       <c r="I38" s="49"/>
       <c r="J38" s="49"/>
     </row>
     <row r="39" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="85">
+      <c r="B39" s="83">
         <v>47270</v>
       </c>
-      <c r="C39" s="86">
+      <c r="C39" s="84">
         <v>0.6</v>
       </c>
-      <c r="D39" s="89"/>
-      <c r="E39" s="89"/>
-      <c r="F39" s="89"/>
+      <c r="D39" s="87"/>
+      <c r="E39" s="87"/>
+      <c r="F39" s="87"/>
       <c r="G39" s="49"/>
       <c r="H39" s="49"/>
       <c r="I39" s="49"/>
       <c r="J39" s="49"/>
     </row>
     <row r="40" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="85">
+      <c r="B40" s="83">
         <v>47300</v>
       </c>
-      <c r="C40" s="86">
+      <c r="C40" s="84">
         <v>0.62</v>
       </c>
-      <c r="D40" s="89"/>
-      <c r="E40" s="89"/>
-      <c r="F40" s="89"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="87"/>
       <c r="G40" s="49"/>
       <c r="H40" s="49"/>
       <c r="I40" s="49"/>
       <c r="J40" s="49"/>
     </row>
     <row r="41" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="85">
+      <c r="B41" s="83">
         <v>47331</v>
       </c>
-      <c r="C41" s="86">
+      <c r="C41" s="84">
         <v>0.63</v>
       </c>
-      <c r="D41" s="89"/>
-      <c r="E41" s="89"/>
-      <c r="F41" s="89"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="87"/>
+      <c r="F41" s="87"/>
       <c r="G41" s="49"/>
       <c r="H41" s="49"/>
       <c r="I41" s="49"/>
       <c r="J41" s="49"/>
     </row>
     <row r="42" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B42" s="85">
+      <c r="B42" s="83">
         <v>47362</v>
       </c>
-      <c r="C42" s="86">
+      <c r="C42" s="84">
         <v>0.65</v>
       </c>
-      <c r="D42" s="89"/>
-      <c r="E42" s="89"/>
-      <c r="F42" s="89"/>
+      <c r="D42" s="87"/>
+      <c r="E42" s="87"/>
+      <c r="F42" s="87"/>
       <c r="G42" s="49"/>
       <c r="H42" s="49"/>
       <c r="I42" s="49"/>
       <c r="J42" s="49"/>
     </row>
     <row r="43" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B43" s="85">
+      <c r="B43" s="83">
         <v>47392</v>
       </c>
-      <c r="C43" s="86">
+      <c r="C43" s="84">
         <v>0.67</v>
       </c>
-      <c r="D43" s="89"/>
-      <c r="E43" s="89"/>
-      <c r="F43" s="89"/>
+      <c r="D43" s="87"/>
+      <c r="E43" s="87"/>
+      <c r="F43" s="87"/>
       <c r="G43" s="49"/>
       <c r="H43" s="49"/>
       <c r="I43" s="49"/>
       <c r="J43" s="49"/>
     </row>
     <row r="44" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B44" s="85">
+      <c r="B44" s="83">
         <v>47423</v>
       </c>
-      <c r="C44" s="86">
+      <c r="C44" s="84">
         <v>0.68</v>
       </c>
-      <c r="D44" s="89"/>
-      <c r="E44" s="89"/>
-      <c r="F44" s="89"/>
+      <c r="D44" s="87"/>
+      <c r="E44" s="87"/>
+      <c r="F44" s="87"/>
       <c r="G44" s="49"/>
       <c r="H44" s="49"/>
       <c r="I44" s="49"/>
       <c r="J44" s="49"/>
     </row>
     <row r="45" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B45" s="85">
+      <c r="B45" s="83">
         <v>47453</v>
       </c>
-      <c r="C45" s="86">
+      <c r="C45" s="84">
         <v>0.7</v>
       </c>
-      <c r="D45" s="89"/>
-      <c r="E45" s="89"/>
-      <c r="F45" s="89"/>
+      <c r="D45" s="87"/>
+      <c r="E45" s="87"/>
+      <c r="F45" s="87"/>
       <c r="G45" s="49"/>
       <c r="H45" s="49"/>
       <c r="I45" s="49"/>
       <c r="J45" s="49"/>
     </row>
     <row r="46" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B46" s="85">
+      <c r="B46" s="83">
         <v>47484</v>
       </c>
-      <c r="C46" s="86">
+      <c r="C46" s="84">
         <v>0.72</v>
       </c>
-      <c r="D46" s="89"/>
-      <c r="E46" s="89"/>
-      <c r="F46" s="89"/>
+      <c r="D46" s="87"/>
+      <c r="E46" s="87"/>
+      <c r="F46" s="87"/>
       <c r="G46" s="49"/>
       <c r="H46" s="49"/>
       <c r="I46" s="49"/>
       <c r="J46" s="49"/>
     </row>
     <row r="47" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B47" s="85">
+      <c r="B47" s="83">
         <v>47515</v>
       </c>
-      <c r="C47" s="86">
+      <c r="C47" s="84">
         <v>0.73</v>
       </c>
-      <c r="D47" s="89"/>
-      <c r="E47" s="89"/>
-      <c r="F47" s="89"/>
+      <c r="D47" s="87"/>
+      <c r="E47" s="87"/>
+      <c r="F47" s="87"/>
       <c r="G47" s="49"/>
       <c r="H47" s="49"/>
       <c r="I47" s="49"/>
       <c r="J47" s="49"/>
     </row>
     <row r="48" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B48" s="85">
+      <c r="B48" s="83">
         <v>47543</v>
       </c>
-      <c r="C48" s="86">
+      <c r="C48" s="84">
         <v>0.75</v>
       </c>
-      <c r="D48" s="89"/>
-      <c r="E48" s="89"/>
-      <c r="F48" s="89"/>
+      <c r="D48" s="87"/>
+      <c r="E48" s="87"/>
+      <c r="F48" s="87"/>
       <c r="G48" s="49"/>
       <c r="H48" s="49"/>
       <c r="I48" s="49"/>
       <c r="J48" s="49"/>
     </row>
     <row r="49" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B49" s="85">
+      <c r="B49" s="83">
         <v>47574</v>
       </c>
-      <c r="C49" s="86">
+      <c r="C49" s="84">
         <v>0.77</v>
       </c>
-      <c r="D49" s="89"/>
-      <c r="E49" s="89"/>
-      <c r="F49" s="89"/>
+      <c r="D49" s="87"/>
+      <c r="E49" s="87"/>
+      <c r="F49" s="87"/>
       <c r="G49" s="49"/>
       <c r="H49" s="49"/>
       <c r="I49" s="49"/>
       <c r="J49" s="49"/>
     </row>
     <row r="50" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B50" s="85">
+      <c r="B50" s="83">
         <v>47604</v>
       </c>
-      <c r="C50" s="86">
+      <c r="C50" s="84">
         <v>0.78</v>
       </c>
-      <c r="D50" s="89"/>
-      <c r="E50" s="89"/>
-      <c r="F50" s="89"/>
+      <c r="D50" s="87"/>
+      <c r="E50" s="87"/>
+      <c r="F50" s="87"/>
       <c r="G50" s="49"/>
       <c r="H50" s="49"/>
       <c r="I50" s="49"/>
       <c r="J50" s="49"/>
     </row>
     <row r="51" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B51" s="85">
+      <c r="B51" s="83">
         <v>47635</v>
       </c>
-      <c r="C51" s="86">
+      <c r="C51" s="84">
         <v>0.8</v>
       </c>
-      <c r="D51" s="89"/>
-      <c r="E51" s="89"/>
-      <c r="F51" s="89"/>
+      <c r="D51" s="87"/>
+      <c r="E51" s="87"/>
+      <c r="F51" s="87"/>
       <c r="G51" s="49"/>
       <c r="H51" s="49"/>
       <c r="I51" s="49"/>
       <c r="J51" s="49"/>
     </row>
     <row r="52" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B52" s="85">
+      <c r="B52" s="83">
         <v>47665</v>
       </c>
-      <c r="C52" s="86">
+      <c r="C52" s="84">
         <v>0.82</v>
       </c>
-      <c r="D52" s="89"/>
-      <c r="E52" s="89"/>
-      <c r="F52" s="89"/>
+      <c r="D52" s="87"/>
+      <c r="E52" s="87"/>
+      <c r="F52" s="87"/>
       <c r="G52" s="49"/>
       <c r="H52" s="49"/>
       <c r="I52" s="49"/>
       <c r="J52" s="49"/>
     </row>
     <row r="53" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B53" s="85">
+      <c r="B53" s="83">
         <v>47696</v>
       </c>
-      <c r="C53" s="86">
+      <c r="C53" s="84">
         <v>0.83</v>
       </c>
-      <c r="D53" s="89"/>
-      <c r="E53" s="89"/>
-      <c r="F53" s="89"/>
+      <c r="D53" s="87"/>
+      <c r="E53" s="87"/>
+      <c r="F53" s="87"/>
       <c r="G53" s="49"/>
       <c r="H53" s="49"/>
       <c r="I53" s="49"/>
       <c r="J53" s="49"/>
     </row>
     <row r="54" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B54" s="85">
+      <c r="B54" s="83">
         <v>47727</v>
       </c>
-      <c r="C54" s="86">
+      <c r="C54" s="84">
         <v>0.85</v>
       </c>
-      <c r="D54" s="89"/>
-      <c r="E54" s="89"/>
-      <c r="F54" s="89"/>
+      <c r="D54" s="87"/>
+      <c r="E54" s="87"/>
+      <c r="F54" s="87"/>
       <c r="G54" s="49"/>
       <c r="H54" s="49"/>
       <c r="I54" s="49"/>
       <c r="J54" s="49"/>
     </row>
     <row r="55" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B55" s="85">
+      <c r="B55" s="83">
         <v>47757</v>
       </c>
-      <c r="C55" s="86">
+      <c r="C55" s="84">
         <v>0.87</v>
       </c>
-      <c r="D55" s="89"/>
-      <c r="E55" s="89"/>
-      <c r="F55" s="89"/>
+      <c r="D55" s="87"/>
+      <c r="E55" s="87"/>
+      <c r="F55" s="87"/>
       <c r="G55" s="49"/>
       <c r="H55" s="49"/>
       <c r="I55" s="49"/>
       <c r="J55" s="49"/>
     </row>
     <row r="56" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B56" s="85">
+      <c r="B56" s="83">
         <v>47788</v>
       </c>
-      <c r="C56" s="86">
+      <c r="C56" s="84">
         <v>0.88</v>
       </c>
-      <c r="D56" s="89"/>
-      <c r="E56" s="89"/>
-      <c r="F56" s="89"/>
+      <c r="D56" s="87"/>
+      <c r="E56" s="87"/>
+      <c r="F56" s="87"/>
       <c r="G56" s="49"/>
       <c r="H56" s="49"/>
       <c r="I56" s="49"/>
       <c r="J56" s="49"/>
     </row>
     <row r="57" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B57" s="85">
+      <c r="B57" s="83">
         <v>47818</v>
       </c>
-      <c r="C57" s="86">
+      <c r="C57" s="84">
         <v>0.9</v>
       </c>
-      <c r="D57" s="89"/>
-      <c r="E57" s="89"/>
-      <c r="F57" s="89"/>
+      <c r="D57" s="87"/>
+      <c r="E57" s="87"/>
+      <c r="F57" s="87"/>
       <c r="G57" s="49"/>
       <c r="H57" s="49"/>
       <c r="I57" s="49"/>
       <c r="J57" s="49"/>
     </row>
     <row r="58" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B58" s="85">
+      <c r="B58" s="83">
         <v>47849</v>
       </c>
-      <c r="C58" s="86">
+      <c r="C58" s="84">
         <v>0.92</v>
       </c>
-      <c r="D58" s="89"/>
-      <c r="E58" s="89"/>
-      <c r="F58" s="89"/>
+      <c r="D58" s="87"/>
+      <c r="E58" s="87"/>
+      <c r="F58" s="87"/>
       <c r="G58" s="49"/>
       <c r="H58" s="49"/>
       <c r="I58" s="49"/>
       <c r="J58" s="49"/>
     </row>
     <row r="59" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B59" s="85">
+      <c r="B59" s="83">
         <v>47880</v>
       </c>
-      <c r="C59" s="86">
+      <c r="C59" s="84">
         <v>0.93</v>
       </c>
-      <c r="D59" s="89"/>
-      <c r="E59" s="89"/>
-      <c r="F59" s="89"/>
+      <c r="D59" s="87"/>
+      <c r="E59" s="87"/>
+      <c r="F59" s="87"/>
       <c r="G59" s="49"/>
       <c r="H59" s="49"/>
       <c r="I59" s="49"/>
       <c r="J59" s="49"/>
     </row>
     <row r="60" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B60" s="85">
+      <c r="B60" s="83">
         <v>47908</v>
       </c>
-      <c r="C60" s="86">
+      <c r="C60" s="84">
         <v>0.95</v>
       </c>
-      <c r="D60" s="89"/>
-      <c r="E60" s="89"/>
-      <c r="F60" s="89"/>
+      <c r="D60" s="87"/>
+      <c r="E60" s="87"/>
+      <c r="F60" s="87"/>
       <c r="G60" s="49"/>
       <c r="H60" s="49"/>
       <c r="I60" s="49"/>
       <c r="J60" s="49"/>
     </row>
     <row r="61" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B61" s="85">
+      <c r="B61" s="83">
         <v>47939</v>
       </c>
-      <c r="C61" s="86">
+      <c r="C61" s="84">
         <v>0.97</v>
       </c>
-      <c r="D61" s="89"/>
-      <c r="E61" s="89"/>
-      <c r="F61" s="89"/>
+      <c r="D61" s="87"/>
+      <c r="E61" s="87"/>
+      <c r="F61" s="87"/>
       <c r="G61" s="49"/>
       <c r="H61" s="49"/>
       <c r="I61" s="49"/>
       <c r="J61" s="49"/>
     </row>
     <row r="62" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B62" s="85">
+      <c r="B62" s="83">
         <v>47969</v>
       </c>
-      <c r="C62" s="86">
+      <c r="C62" s="84">
         <v>0.98</v>
       </c>
-      <c r="D62" s="89"/>
-      <c r="E62" s="89"/>
-      <c r="F62" s="89"/>
+      <c r="D62" s="87"/>
+      <c r="E62" s="87"/>
+      <c r="F62" s="87"/>
       <c r="G62" s="49"/>
       <c r="H62" s="49"/>
       <c r="I62" s="49"/>
       <c r="J62" s="49"/>
     </row>
     <row r="63" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B63" s="85">
+      <c r="B63" s="83">
         <v>48000</v>
       </c>
-      <c r="C63" s="86">
+      <c r="C63" s="84">
         <v>1</v>
       </c>
-      <c r="D63" s="89"/>
-      <c r="E63" s="89"/>
-      <c r="F63" s="89"/>
+      <c r="D63" s="87"/>
+      <c r="E63" s="87"/>
+      <c r="F63" s="87"/>
       <c r="G63" s="49"/>
       <c r="H63" s="49"/>
       <c r="I63" s="49"/>
@@ -7096,6 +7092,7 @@
   <dimension ref="B3:H10"/>
   <sheetFormatPr defaultRowHeight="11.55" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7205,10 +7202,10 @@
         <v>7.8</v>
       </c>
       <c r="F7" s="70">
-        <v>7.3</v>
+        <v>9.5</v>
       </c>
       <c r="G7" s="67" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="H7" t="s">
         <v>293</v>
@@ -7216,7 +7213,7 @@
     </row>
     <row r="8" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" s="67" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C8" s="54">
         <v>0.41</v>
@@ -7234,12 +7231,12 @@
         <v>292</v>
       </c>
       <c r="H8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="67" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C9" s="54">
         <v>0.9</v>
@@ -7254,7 +7251,7 @@
         <v>0.87</v>
       </c>
       <c r="G9" s="67" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H9" t="s">
         <v>293</v>
@@ -7262,7 +7259,7 @@
     </row>
     <row r="10" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="67" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C10" s="54">
         <v>0.84</v>
@@ -7299,48 +7296,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="88" t="s">
+        <v>304</v>
+      </c>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="89" t="s">
         <v>305</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="80" t="s">
-        <v>306</v>
-      </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="71" t="s">
         <v>58</v>
       </c>
       <c r="B3" s="71" t="s">
+        <v>306</v>
+      </c>
+      <c r="C3" s="71" t="s">
         <v>307</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="D3" s="71" t="s">
         <v>308</v>
       </c>
-      <c r="D3" s="71" t="s">
+      <c r="E3" s="71" t="s">
         <v>309</v>
       </c>
-      <c r="E3" s="71" t="s">
+      <c r="F3" s="71" t="s">
         <v>310</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="G3" s="71" t="s">
         <v>311</v>
-      </c>
-      <c r="G3" s="71" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7914,33 +7911,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="88" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="89" t="s">
         <v>313</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="80" t="s">
-        <v>314</v>
-      </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
     </row>
     <row r="3" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="71" t="s">
+        <v>314</v>
+      </c>
+      <c r="B3" s="71" t="s">
         <v>315</v>
       </c>
-      <c r="B3" s="71" t="s">
+      <c r="C3" s="71" t="s">
         <v>316</v>
-      </c>
-      <c r="C3" s="71" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="75" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B4" s="76">
         <v>3200</v>
@@ -7951,7 +7948,7 @@
     </row>
     <row r="5" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="75" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B5" s="76">
         <v>2600</v>
@@ -7962,7 +7959,7 @@
     </row>
     <row r="6" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="75" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B6" s="76">
         <v>900</v>
@@ -7990,20 +7987,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="88" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="89" t="s">
         <v>321</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="80" t="s">
-        <v>322</v>
-      </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
     </row>
     <row r="3" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="71" t="s">
@@ -8030,7 +8027,7 @@
         <v>0.79</v>
       </c>
       <c r="D4" s="75" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8044,7 +8041,7 @@
         <v>0.8</v>
       </c>
       <c r="D5" s="75" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8058,7 +8055,7 @@
         <v>0.81</v>
       </c>
       <c r="D6" s="75" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8072,7 +8069,7 @@
         <v>0.82</v>
       </c>
       <c r="D7" s="75" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8086,7 +8083,7 @@
         <v>0.82</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8100,7 +8097,7 @@
         <v>0.83</v>
       </c>
       <c r="D9" s="75" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/NAP mock data.xlsx
+++ b/NAP mock data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB25A1BC-D18D-419C-AA3F-EF60F349B971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A585BCF-510A-4B2C-A6C4-94E29E038496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market growth" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="327">
   <si>
     <t>Year</t>
   </si>
@@ -544,9 +544,6 @@
     <t>New Forecast Blended Curve</t>
   </si>
   <si>
-    <t>Lipfendra persitency</t>
-  </si>
-  <si>
     <t>M01</t>
   </si>
   <si>
@@ -1070,6 +1067,21 @@
   </si>
   <si>
     <t>Illustrative claims data</t>
+  </si>
+  <si>
+    <t>Ezetimibe</t>
+  </si>
+  <si>
+    <t>Bempedoic</t>
+  </si>
+  <si>
+    <t>Repatha</t>
+  </si>
+  <si>
+    <t>Lipfendra</t>
+  </si>
+  <si>
+    <t>Leqvio</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1095,7 @@
     <numFmt numFmtId="167" formatCode="0.00&quot;M&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1181,6 +1193,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="14">
@@ -1555,7 +1573,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1781,6 +1799,12 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4220,12 +4244,20 @@
         <v>146</v>
       </c>
       <c r="I3" s="63" t="s">
-        <v>147</v>
-      </c>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
+        <v>325</v>
+      </c>
+      <c r="J3" s="90" t="s">
+        <v>322</v>
+      </c>
+      <c r="K3" s="90" t="s">
+        <v>323</v>
+      </c>
+      <c r="L3" s="90" t="s">
+        <v>324</v>
+      </c>
+      <c r="M3" s="90" t="s">
+        <v>326</v>
+      </c>
       <c r="N3" s="63"/>
       <c r="O3" s="63"/>
       <c r="P3" s="63"/>
@@ -4416,12 +4448,24 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H4" s="49">
         <v>1</v>
       </c>
       <c r="I4" s="62">
+        <v>1</v>
+      </c>
+      <c r="J4" s="91">
+        <v>1</v>
+      </c>
+      <c r="K4" s="91">
+        <v>1</v>
+      </c>
+      <c r="L4" s="91">
+        <v>1</v>
+      </c>
+      <c r="M4" s="91">
         <v>1</v>
       </c>
     </row>
@@ -4437,13 +4481,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H5" s="49">
         <v>0.90135151891139398</v>
       </c>
       <c r="I5" s="62">
         <v>0.92</v>
+      </c>
+      <c r="J5" s="91">
+        <v>0.92</v>
+      </c>
+      <c r="K5" s="91">
+        <v>0.89</v>
+      </c>
+      <c r="L5" s="91">
+        <v>0.6</v>
+      </c>
+      <c r="M5" s="91">
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="6" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -4458,13 +4514,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H6" s="49">
         <v>0.81886946701274754</v>
       </c>
       <c r="I6" s="62">
         <v>0.83</v>
+      </c>
+      <c r="J6" s="91">
+        <v>0.84</v>
+      </c>
+      <c r="K6" s="91">
+        <v>0.79</v>
+      </c>
+      <c r="L6" s="91">
+        <v>0.52</v>
+      </c>
+      <c r="M6" s="91">
+        <v>0.49</v>
       </c>
     </row>
     <row r="7" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -4479,13 +4547,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H7" s="49">
         <v>0.73028739681327393</v>
       </c>
       <c r="I7" s="62">
         <v>0.77</v>
+      </c>
+      <c r="J7" s="91">
+        <v>0.74</v>
+      </c>
+      <c r="K7" s="91">
+        <v>0.69</v>
+      </c>
+      <c r="L7" s="91">
+        <v>0.45</v>
+      </c>
+      <c r="M7" s="91">
+        <v>0.43</v>
       </c>
     </row>
     <row r="8" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -4500,13 +4580,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H8" s="49">
         <v>0.65091647694349852</v>
       </c>
       <c r="I8" s="62">
         <v>0.7</v>
+      </c>
+      <c r="J8" s="91">
+        <v>0.65</v>
+      </c>
+      <c r="K8" s="91">
+        <v>0.59</v>
+      </c>
+      <c r="L8" s="91">
+        <v>0.4</v>
+      </c>
+      <c r="M8" s="91">
+        <v>0.38</v>
       </c>
     </row>
     <row r="9" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -4521,13 +4613,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H9" s="49">
         <v>0.58245497498580945</v>
       </c>
       <c r="I9" s="62">
         <v>0.65</v>
+      </c>
+      <c r="J9" s="91">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="K9" s="91">
+        <v>0.52</v>
+      </c>
+      <c r="L9" s="91">
+        <v>0.37</v>
+      </c>
+      <c r="M9" s="91">
+        <v>0.35</v>
       </c>
     </row>
     <row r="10" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -5294,7 +5398,7 @@
         <v>43110.846741568232</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H64" s="49">
         <v>0.26322222675085089</v>
@@ -5308,7 +5412,7 @@
         <v>43111.302435506419</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H65" s="49">
         <v>0.26149024339966198</v>
@@ -5322,7 +5426,7 @@
         <v>43161.084173704337</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H66" s="49">
         <v>0.26149024339966198</v>
@@ -5336,7 +5440,7 @@
         <v>43177.323448592513</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H67" s="49">
         <v>0.25975902951180363</v>
@@ -5350,7 +5454,7 @@
         <v>43227.587870865435</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H68" s="49">
         <v>0.25802704616061478</v>
@@ -5364,7 +5468,7 @@
         <v>43306.574820151465</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H69" s="49">
         <v>0.25802704616061478</v>
@@ -5378,7 +5482,7 @@
         <v>43306.574820151465</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H70" s="49">
         <v>0.25629506280942593</v>
@@ -5392,7 +5496,7 @@
         <v>43334.954963298725</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H71" s="49">
         <v>0.25629506280942593</v>
@@ -5406,7 +5510,7 @@
         <v>43334.954963298725</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H72" s="49">
         <v>0.25456384892156758</v>
@@ -5420,7 +5524,7 @@
         <v>43334.954963298725</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H73" s="49">
         <v>0.25456384892156758</v>
@@ -5434,7 +5538,7 @@
         <v>43325.00078598156</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H74" s="49">
         <v>0.25283186557037873</v>
@@ -5448,7 +5552,7 @@
         <v>43241.016951591933</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H75" s="49">
         <v>0.25283186557037873</v>
@@ -5462,7 +5566,7 @@
         <v>43127.684971338058</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H76" s="49">
         <v>0.25109988221918988</v>
@@ -5476,7 +5580,7 @@
         <v>43127.39870741521</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H77" s="49">
         <v>0.25109988221918988</v>
@@ -5490,7 +5594,7 @@
         <v>43096.126148207368</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H78" s="49">
         <v>0.24936866833133148</v>
@@ -5504,7 +5608,7 @@
         <v>43085.924742956835</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H79" s="49">
         <v>0.24936866833133148</v>
@@ -5518,7 +5622,7 @@
         <v>43054.348964800411</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H80" s="49">
         <v>0.24763668498014263</v>
@@ -5532,7 +5636,7 @@
         <v>43004.729884840322</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H81" s="49">
         <v>0.24763668498014263</v>
@@ -5546,7 +5650,7 @@
         <v>43004.729884840322</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H82" s="49">
         <v>0.24590470162895378</v>
@@ -5560,7 +5664,7 @@
         <v>42986.901666320278</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H83" s="49">
         <v>0.24590470162895378</v>
@@ -5574,7 +5678,7 @@
         <v>42986.901666320278</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H84" s="49">
         <v>0.24590470162895378</v>
@@ -5588,7 +5692,7 @@
         <v>42986.901666320278</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H85" s="49">
         <v>0.24417348774109537</v>
@@ -5602,7 +5706,7 @@
         <v>42990.888277132348</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H86" s="49">
         <v>0.24417348774109537</v>
@@ -5616,7 +5720,7 @@
         <v>43024.52348891821</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H87" s="49">
         <v>0.24244150438990655</v>
@@ -5630,7 +5734,7 @@
         <v>43069.912523434839</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H88" s="49">
         <v>0.24244150438990655</v>
@@ -5644,7 +5748,7 @@
         <v>43070.027171066038</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H89" s="49">
         <v>0.24070952103871773</v>
@@ -5658,7 +5762,7 @@
         <v>43082.551714148474</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H90" s="49">
         <v>0.24070952103871773</v>
@@ -5672,7 +5776,7 @@
         <v>43086.63733882385</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H91" s="49">
         <v>0.24070952103871773</v>
@@ -5686,7 +5790,7 @@
         <v>43099.283319961927</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H92" s="49">
         <v>0.23897830715085933</v>
@@ -5700,7 +5804,7 @@
         <v>43119.15557603605</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H93" s="49">
         <v>0.23897830715085933</v>
@@ -5714,7 +5818,7 @@
         <v>43119.15557603605</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H94" s="49">
         <v>0.23724632379967048</v>
@@ -5728,7 +5832,7 @@
         <v>43126.295710920873</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H95" s="49">
         <v>0.23724632379967048</v>
@@ -5742,7 +5846,7 @@
         <v>43126.295710920873</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H96" s="49">
         <v>0.23724632379967048</v>
@@ -5756,7 +5860,7 @@
         <v>43126.295710920873</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H97" s="49">
         <v>0.23551434044848166</v>
@@ -5770,7 +5874,7 @@
         <v>43132.514717378268</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H98" s="49">
         <v>0.23551434044848166</v>
@@ -5784,7 +5888,7 @@
         <v>43184.984749983072</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H99" s="49">
         <v>0.23551434044848166</v>
@@ -5798,7 +5902,7 @@
         <v>43255.790432318317</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H100" s="49">
         <v>0.23378312656062325</v>
@@ -5812,7 +5916,7 @@
         <v>43255.969279562851</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H101" s="49">
         <v>0.23378312656062325</v>
@@ -5826,7 +5930,7 @@
         <v>43275.507232470045</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H102" s="49">
         <v>0.23378312656062325</v>
@@ -5840,7 +5944,7 @@
         <v>43281.880697911351</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H103" s="49">
         <v>0.2320511432094344</v>
@@ -5854,7 +5958,7 @@
         <v>43301.608090943955</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H104" s="49">
         <v>0.2320511432094344</v>
@@ -5868,7 +5972,7 @@
         <v>43332.608279995206</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H105" s="49">
         <v>0.2320511432094344</v>
@@ -5882,7 +5986,7 @@
         <v>43332.608279995206</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H106" s="49">
         <v>0.23031915985824558</v>
@@ -5896,7 +6000,7 @@
         <v>43343.746699833151</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H107" s="49">
         <v>0.23031915985824558</v>
@@ -5910,7 +6014,7 @@
         <v>43343.746699833151</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H108" s="49">
         <v>0.23031915985824558</v>
@@ -5924,7 +6028,7 @@
         <v>43343.746699833151</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H109" s="49">
         <v>0.22858794597038715</v>
@@ -5938,7 +6042,7 @@
         <v>43349.711459327867</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H110" s="49">
         <v>0.22858794597038715</v>
@@ -5952,7 +6056,7 @@
         <v>43400.03639906094</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H111" s="49">
         <v>0.22858794597038715</v>
@@ -5966,7 +6070,7 @@
         <v>43467.947385949752</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H112" s="49">
         <v>0.22685596261919833</v>
@@ -5980,7 +6084,7 @@
         <v>43468.118921516922</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H113" s="49">
         <v>0.22685596261919833</v>
@@ -5994,7 +6098,7 @@
         <v>43486.858118993099</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H114" s="49">
         <v>0.22685596261919833</v>
@@ -6008,7 +6112,7 @@
         <v>43492.971022841288</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H115" s="49">
         <v>0.22512397926800948</v>
@@ -6022,7 +6126,7 @@
         <v>43511.89191570472</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H116" s="49">
         <v>0.22512397926800948</v>
@@ -6036,7 +6140,7 @@
         <v>43541.624747347269</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H117" s="49">
         <v>0.22512397926800948</v>
@@ -6050,7 +6154,7 @@
         <v>43541.624747347269</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H118" s="49">
         <v>0.2233927653801511</v>
@@ -6064,7 +6168,7 @@
         <v>43552.307803545991</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H119" s="49">
         <v>0.2233927653801511</v>
@@ -6078,7 +6182,7 @@
         <v>43552.307803545991</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H120" s="49">
         <v>0.2233927653801511</v>
@@ -6092,7 +6196,7 @@
         <v>43552.307803545991</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H121" s="49">
         <v>0.22166078202896228</v>
@@ -6106,7 +6210,7 @@
         <v>43558.059639988765</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H122" s="49">
         <v>0.22166078202896228</v>
@@ -6120,7 +6224,7 @@
         <v>43606.588138512991</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H123" s="49">
         <v>0.22166078202896228</v>
@@ -6134,7 +6238,7 @@
         <v>43672.074917920829</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H124" s="49">
         <v>0.2199287986777734</v>
@@ -6148,7 +6252,7 @@
         <v>43672.240330210683</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H125" s="49">
         <v>0.2199287986777734</v>
@@ -6162,7 +6266,7 @@
         <v>43690.310597594835</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H126" s="49">
         <v>0.2199287986777734</v>
@@ -6176,7 +6280,7 @@
         <v>43696.205290106118</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H127" s="49">
         <v>0.21819758478991505</v>
@@ -6190,7 +6294,7 @@
         <v>43714.45076692677</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H128" s="49">
         <v>0.21819758478991505</v>
@@ -6204,7 +6308,7 @@
         <v>43743.122230502078</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H129" s="49">
         <v>0.21819758478991505</v>
@@ -6218,7 +6322,7 @@
         <v>43743.122230502078</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H130" s="49">
         <v>0.2164656014387262</v>
@@ -6232,7 +6336,7 @@
         <v>43753.423935376923</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H131" s="49">
         <v>0.2164656014387262</v>
@@ -6246,7 +6350,7 @@
         <v>43753.423935376923</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H132" s="49">
         <v>0.2164656014387262</v>
@@ -6260,7 +6364,7 @@
         <v>43753.423935376923</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H133" s="49">
         <v>0.21473361808753735</v>
@@ -6274,7 +6378,7 @@
         <v>43758.994927860324</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H134" s="49">
         <v>0.21473361808753735</v>
@@ -6288,7 +6392,7 @@
         <v>43805.997637898952</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H135" s="49">
         <v>0.21473361808753735</v>
@@ -6302,7 +6406,7 @@
         <v>43869.425442126878</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H136" s="49">
         <v>0.21473361808753735</v>
@@ -6316,7 +6420,7 @@
         <v>43869.585653675422</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H137" s="49">
         <v>0.21300240419967897</v>
@@ -6330,7 +6434,7 @@
         <v>43887.08777230687</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H138" s="49">
         <v>0.21300240419967897</v>
@@ -6344,7 +6448,7 @@
         <v>43892.797129309467</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H139" s="49">
         <v>0.21300240419967897</v>
@@ -6358,7 +6462,7 @@
         <v>43910.468948603215</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H140" s="49">
         <v>0.21127042084849015</v>
@@ -6372,7 +6476,7 @@
         <v>43938.238950350555</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H141" s="49">
         <v>0.21127042084849015</v>
@@ -6386,7 +6490,7 @@
         <v>43938.238950350555</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H142" s="49">
         <v>0.21127042084849015</v>
@@ -6400,7 +6504,7 @@
         <v>43948.216758481045</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H143" s="49">
         <v>0.20953843749730128</v>
@@ -6414,7 +6518,7 @@
         <v>43948.216758481045</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H144" s="49">
         <v>0.20953843749730128</v>
@@ -6428,7 +6532,7 @@
         <v>43948.216758481045</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H145" s="49">
         <v>0.20953843749730128</v>
@@ -6442,7 +6546,7 @@
         <v>43953.632303431419</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H146" s="49">
         <v>0.20953843749730128</v>
@@ -6456,7 +6560,7 @@
         <v>43999.323495757031</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H147" s="49">
         <v>0.2078072236094429</v>
@@ -6470,7 +6574,7 @@
         <v>44060.981472486201</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H148" s="49">
         <v>0.2078072236094429</v>
@@ -6484,7 +6588,7 @@
         <v>44061.137213648173</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H149" s="49">
         <v>0.2078072236094429</v>
@@ -6498,7 +6602,7 @@
         <v>44078.150970255796</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H150" s="49">
         <v>0.20607524025825408</v>
@@ -6512,7 +6616,7 @@
         <v>44083.701018936968</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H151" s="49">
         <v>0.20607524025825408</v>
@@ -6526,7 +6630,7 @@
         <v>44100.879741045363</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H152" s="49">
         <v>0.20607524025825408</v>
@@ -6540,7 +6644,7 @@
         <v>44127.8748757871</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H153" s="49">
         <v>0.20607524025825408</v>
@@ -6554,7 +6658,7 @@
         <v>44127.8748757871</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H154" s="49">
         <v>0.20434325690706523</v>
@@ -6568,7 +6672,7 @@
         <v>44137.574272904923</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H155" s="49">
         <v>0.20434325690706523</v>
@@ -6582,7 +6686,7 @@
         <v>44137.574272904923</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H156" s="49">
         <v>0.20434325690706523</v>
@@ -6596,7 +6700,7 @@
         <v>44137.574272904923</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H157" s="49">
         <v>0.20261204301920682</v>
@@ -6610,7 +6714,7 @@
         <v>44141.916036936032</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H158" s="49">
         <v>0.20261204301920682</v>
@@ -6624,7 +6728,7 @@
         <v>44178.547692142551</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H159" s="49">
         <v>0.20261204301920682</v>
@@ -6638,7 +6742,7 @@
         <v>44227.980277052535</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H160" s="49">
         <v>0.20261204301920682</v>
@@ -6652,7 +6756,7 @@
         <v>44228.10513824036</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H161" s="49">
         <v>0.20088005966801797</v>
@@ -6666,7 +6770,7 @@
         <v>44241.745449076989</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H162" s="49">
         <v>0.20088005966801797</v>
@@ -6680,7 +6784,7 @@
         <v>44246.195047770307</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H163" s="49">
         <v>0.20088005966801797</v>
@@ -6694,7 +6798,7 @@
         <v>44259.967615154368</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H164" s="49">
         <v>0.20088005966801797</v>
@@ -6708,7 +6812,7 @@
         <v>44281.610221043622</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H165" s="49">
         <v>0.19914807631682915</v>
@@ -6722,7 +6826,7 @@
         <v>44281.610221043622</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H166" s="49">
         <v>0.19914807631682915</v>
@@ -6736,7 +6840,7 @@
         <v>44289.386445581578</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H167" s="49">
         <v>0.19914807631682915</v>
@@ -6750,7 +6854,7 @@
         <v>44289.386445581578</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H168" s="49">
         <v>0.19914807631682915</v>
@@ -6764,7 +6868,7 @@
         <v>44289.386445581578</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H169" s="49">
         <v>0.19741686242897075</v>
@@ -6778,7 +6882,7 @@
         <v>44293.606959898178</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H170" s="49">
         <v>0.19741686242897075</v>
@@ -6792,7 +6896,7 @@
         <v>44329.215625899444</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H171" s="49">
         <v>0.19741686242897075</v>
@@ -6806,7 +6910,7 @@
         <v>44377.267738088078</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H172" s="49">
         <v>0.19741686242897075</v>
@@ -6820,7 +6924,7 @@
         <v>44377.389112356002</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H173" s="49">
         <v>0.19568487907778193</v>
@@ -6834,7 +6938,7 @@
         <v>44390.648498807335</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H174" s="49">
         <v>0.19568487907778193</v>
@@ -6848,7 +6952,7 @@
         <v>44394.973836355326</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H175" s="49">
         <v>0.19568487907778193</v>
@@ -6862,7 +6966,7 @@
         <v>44408.361785908637</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H176" s="49">
         <v>0.19568487907778193</v>
@@ -6876,7 +6980,7 @@
         <v>44429.399992349558</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H177" s="49">
         <v>0.19395289572659308</v>
@@ -6890,7 +6994,7 @@
         <v>44429.399992349558</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H178" s="49">
         <v>0.19395289572659308</v>
@@ -6904,7 +7008,7 @@
         <v>44436.959055153631</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H179" s="49">
         <v>0.19395289572659308</v>
@@ -6918,7 +7022,7 @@
         <v>44436.959055153631</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H180" s="49">
         <v>0.19395289572659308</v>
@@ -6932,7 +7036,7 @@
         <v>44436.959055153631</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H181" s="49">
         <v>0.1922216818387347</v>
@@ -6946,7 +7050,7 @@
         <v>44441.072389191984</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H182" s="49">
         <v>0.1922216818387347</v>
@@ -6960,7 +7064,7 @@
         <v>44475.776770444063</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H183" s="49">
         <v>0.1922216818387347</v>
@@ -6974,7 +7078,7 @@
         <v>44522.608595632439</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H184" s="49">
         <v>0.1922216818387347</v>
@@ -6988,7 +7092,7 @@
         <v>44522.726887591714</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H185" s="49">
         <v>0.1922216818387347</v>
@@ -7002,7 +7106,7 @@
         <v>44535.649550927643</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H186" s="49">
         <v>0.19048969848754585</v>
@@ -7016,7 +7120,7 @@
         <v>44539.865046203544</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H187" s="49">
         <v>0.19048969848754585</v>
@@ -7030,7 +7134,7 @@
         <v>44552.913007771807</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H188" s="49">
         <v>0.19048969848754585</v>
@@ -7044,7 +7148,7 @@
         <v>44573.41694737909</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H189" s="49">
         <v>0.19048969848754585</v>
@@ -7052,7 +7156,7 @@
     </row>
     <row r="190" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="G190" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H190" s="49">
         <v>0.188757715136357</v>
@@ -7060,7 +7164,7 @@
     </row>
     <row r="191" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="G191" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H191" s="49">
         <v>0.188757715136357</v>
@@ -7068,7 +7172,7 @@
     </row>
     <row r="192" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="G192" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H192" s="49">
         <v>0.188757715136357</v>
@@ -7076,7 +7180,7 @@
     </row>
     <row r="193" spans="7:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="G193" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H193" s="49">
         <v>0.188757715136357</v>
@@ -7098,30 +7202,30 @@
   <sheetData>
     <row r="3" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="51" t="s">
+        <v>283</v>
+      </c>
+      <c r="C3" s="51" t="s">
         <v>284</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="D3" s="51" t="s">
         <v>285</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="E3" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="F3" s="51" t="s">
         <v>287</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="G3" s="51" t="s">
         <v>288</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="H3" t="s">
         <v>289</v>
-      </c>
-      <c r="H3" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="67" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C4" s="68">
         <v>1.5800000000000002E-2</v>
@@ -7136,15 +7240,15 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G4" s="67" t="s">
+        <v>291</v>
+      </c>
+      <c r="H4" t="s">
         <v>292</v>
-      </c>
-      <c r="H4" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="67" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C5" s="68">
         <v>0.80600000000000005</v>
@@ -7159,15 +7263,15 @@
         <v>0.81</v>
       </c>
       <c r="G5" s="67" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="67" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C6" s="68">
         <v>0.80700000000000005</v>
@@ -7182,18 +7286,18 @@
         <v>0.81499999999999995</v>
       </c>
       <c r="G6" s="67" t="s">
+        <v>291</v>
+      </c>
+      <c r="H6" t="s">
         <v>292</v>
-      </c>
-      <c r="H6" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="67" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7" s="67" t="s">
         <v>297</v>
-      </c>
-      <c r="C7" s="67" t="s">
-        <v>298</v>
       </c>
       <c r="D7" s="67">
         <v>8.1999999999999993</v>
@@ -7205,15 +7309,15 @@
         <v>9.5</v>
       </c>
       <c r="G7" s="67" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" s="67" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C8" s="54">
         <v>0.41</v>
@@ -7228,15 +7332,15 @@
         <v>0.39</v>
       </c>
       <c r="G8" s="67" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="67" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C9" s="54">
         <v>0.9</v>
@@ -7251,15 +7355,15 @@
         <v>0.87</v>
       </c>
       <c r="G9" s="67" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="67" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C10" s="54">
         <v>0.84</v>
@@ -7274,10 +7378,10 @@
         <v>0.83</v>
       </c>
       <c r="G10" s="67" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -7297,7 +7401,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="88" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B1" s="88"/>
       <c r="C1" s="88"/>
@@ -7308,7 +7412,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="89" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B2" s="89"/>
       <c r="C2" s="89"/>
@@ -7322,22 +7426,22 @@
         <v>58</v>
       </c>
       <c r="B3" s="71" t="s">
+        <v>305</v>
+      </c>
+      <c r="C3" s="71" t="s">
         <v>306</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="D3" s="71" t="s">
         <v>307</v>
       </c>
-      <c r="D3" s="71" t="s">
+      <c r="E3" s="71" t="s">
         <v>308</v>
       </c>
-      <c r="E3" s="71" t="s">
+      <c r="F3" s="71" t="s">
         <v>309</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="G3" s="71" t="s">
         <v>310</v>
-      </c>
-      <c r="G3" s="71" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7912,32 +8016,32 @@
   <sheetData>
     <row r="1" spans="1:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="88" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B1" s="88"/>
       <c r="C1" s="88"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="89" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B2" s="89"/>
       <c r="C2" s="89"/>
     </row>
     <row r="3" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="71" t="s">
+        <v>313</v>
+      </c>
+      <c r="B3" s="71" t="s">
         <v>314</v>
       </c>
-      <c r="B3" s="71" t="s">
+      <c r="C3" s="71" t="s">
         <v>315</v>
-      </c>
-      <c r="C3" s="71" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="75" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B4" s="76">
         <v>3200</v>
@@ -7948,7 +8052,7 @@
     </row>
     <row r="5" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="75" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B5" s="76">
         <v>2600</v>
@@ -7959,7 +8063,7 @@
     </row>
     <row r="6" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="75" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B6" s="76">
         <v>900</v>
@@ -7988,7 +8092,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="88" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B1" s="88"/>
       <c r="C1" s="88"/>
@@ -7996,7 +8100,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="89" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B2" s="89"/>
       <c r="C2" s="89"/>
@@ -8013,7 +8117,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="71" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8027,7 +8131,7 @@
         <v>0.79</v>
       </c>
       <c r="D4" s="75" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8041,7 +8145,7 @@
         <v>0.8</v>
       </c>
       <c r="D5" s="75" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8055,7 +8159,7 @@
         <v>0.81</v>
       </c>
       <c r="D6" s="75" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8069,7 +8173,7 @@
         <v>0.82</v>
       </c>
       <c r="D7" s="75" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8083,7 +8187,7 @@
         <v>0.82</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8097,7 +8201,7 @@
         <v>0.83</v>
       </c>
       <c r="D9" s="75" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>

--- a/NAP mock data.xlsx
+++ b/NAP mock data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A585BCF-510A-4B2C-A6C4-94E29E038496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC561869-D2D5-4A1D-824E-BD4C11E46DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market growth" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="327">
   <si>
     <t>Year</t>
   </si>
@@ -1095,7 +1095,7 @@
     <numFmt numFmtId="167" formatCode="0.00&quot;M&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1199,6 +1199,14 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="14">
@@ -1573,7 +1581,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1794,17 +1802,26 @@
     </xf>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3799,6 +3816,8 @@
     <col min="4" max="4" width="20.109375" customWidth="1"/>
     <col min="5" max="5" width="22.5546875" customWidth="1"/>
     <col min="6" max="6" width="16.109375" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:13" ht="46.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4048,8 +4067,12 @@
         <v>128</v>
       </c>
       <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
+      <c r="H13" s="93" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="93" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="14" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B14" s="63">
@@ -4068,8 +4091,12 @@
         <v>131</v>
       </c>
       <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
+      <c r="H14" s="94">
+        <v>46204</v>
+      </c>
+      <c r="I14" s="92" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="15" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B15" s="63">
@@ -4088,8 +4115,12 @@
         <v>133</v>
       </c>
       <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
+      <c r="H15" s="94">
+        <v>46235</v>
+      </c>
+      <c r="I15" s="92" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="16" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B16" s="63">
@@ -4108,8 +4139,12 @@
         <v>135</v>
       </c>
       <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
+      <c r="H16" s="94">
+        <v>46266</v>
+      </c>
+      <c r="I16" s="92" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="17" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B17" s="63">
@@ -4128,8 +4163,12 @@
         <v>137</v>
       </c>
       <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
+      <c r="H17" s="94">
+        <v>46296</v>
+      </c>
+      <c r="I17" s="92" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="18" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B18" s="63">
@@ -4148,8 +4187,12 @@
         <v>139</v>
       </c>
       <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
+      <c r="H18" s="94">
+        <v>46327</v>
+      </c>
+      <c r="I18" s="92" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="19" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B19" s="63">
@@ -4168,8 +4211,12 @@
         <v>141</v>
       </c>
       <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
+      <c r="H19" s="94">
+        <v>46357</v>
+      </c>
+      <c r="I19" s="93" t="s">
+        <v>141</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4246,16 +4293,16 @@
       <c r="I3" s="63" t="s">
         <v>325</v>
       </c>
-      <c r="J3" s="90" t="s">
+      <c r="J3" s="88" t="s">
         <v>322</v>
       </c>
-      <c r="K3" s="90" t="s">
+      <c r="K3" s="88" t="s">
         <v>323</v>
       </c>
-      <c r="L3" s="90" t="s">
+      <c r="L3" s="88" t="s">
         <v>324</v>
       </c>
-      <c r="M3" s="90" t="s">
+      <c r="M3" s="88" t="s">
         <v>326</v>
       </c>
       <c r="N3" s="63"/>
@@ -4456,16 +4503,16 @@
       <c r="I4" s="62">
         <v>1</v>
       </c>
-      <c r="J4" s="91">
+      <c r="J4" s="89">
         <v>1</v>
       </c>
-      <c r="K4" s="91">
+      <c r="K4" s="89">
         <v>1</v>
       </c>
-      <c r="L4" s="91">
+      <c r="L4" s="89">
         <v>1</v>
       </c>
-      <c r="M4" s="91">
+      <c r="M4" s="89">
         <v>1</v>
       </c>
     </row>
@@ -4489,16 +4536,16 @@
       <c r="I5" s="62">
         <v>0.92</v>
       </c>
-      <c r="J5" s="91">
+      <c r="J5" s="89">
         <v>0.92</v>
       </c>
-      <c r="K5" s="91">
+      <c r="K5" s="89">
         <v>0.89</v>
       </c>
-      <c r="L5" s="91">
+      <c r="L5" s="89">
         <v>0.6</v>
       </c>
-      <c r="M5" s="91">
+      <c r="M5" s="89">
         <v>0.56000000000000005</v>
       </c>
     </row>
@@ -4522,16 +4569,16 @@
       <c r="I6" s="62">
         <v>0.83</v>
       </c>
-      <c r="J6" s="91">
+      <c r="J6" s="89">
         <v>0.84</v>
       </c>
-      <c r="K6" s="91">
+      <c r="K6" s="89">
         <v>0.79</v>
       </c>
-      <c r="L6" s="91">
+      <c r="L6" s="89">
         <v>0.52</v>
       </c>
-      <c r="M6" s="91">
+      <c r="M6" s="89">
         <v>0.49</v>
       </c>
     </row>
@@ -4555,16 +4602,16 @@
       <c r="I7" s="62">
         <v>0.77</v>
       </c>
-      <c r="J7" s="91">
+      <c r="J7" s="89">
         <v>0.74</v>
       </c>
-      <c r="K7" s="91">
+      <c r="K7" s="89">
         <v>0.69</v>
       </c>
-      <c r="L7" s="91">
+      <c r="L7" s="89">
         <v>0.45</v>
       </c>
-      <c r="M7" s="91">
+      <c r="M7" s="89">
         <v>0.43</v>
       </c>
     </row>
@@ -4588,16 +4635,16 @@
       <c r="I8" s="62">
         <v>0.7</v>
       </c>
-      <c r="J8" s="91">
+      <c r="J8" s="89">
         <v>0.65</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="89">
         <v>0.59</v>
       </c>
-      <c r="L8" s="91">
+      <c r="L8" s="89">
         <v>0.4</v>
       </c>
-      <c r="M8" s="91">
+      <c r="M8" s="89">
         <v>0.38</v>
       </c>
     </row>
@@ -4621,16 +4668,16 @@
       <c r="I9" s="62">
         <v>0.65</v>
       </c>
-      <c r="J9" s="91">
+      <c r="J9" s="89">
         <v>0.56999999999999995</v>
       </c>
-      <c r="K9" s="91">
+      <c r="K9" s="89">
         <v>0.52</v>
       </c>
-      <c r="L9" s="91">
+      <c r="L9" s="89">
         <v>0.37</v>
       </c>
-      <c r="M9" s="91">
+      <c r="M9" s="89">
         <v>0.35</v>
       </c>
     </row>
@@ -7400,26 +7447,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="90" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="91" t="s">
         <v>304</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
     </row>
     <row r="3" spans="1:7" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="71" t="s">
@@ -8015,18 +8062,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="90" t="s">
         <v>311</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="91" t="s">
         <v>312</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
     </row>
     <row r="3" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="71" t="s">
@@ -8091,20 +8138,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="90" t="s">
         <v>319</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="91" t="s">
         <v>320</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
     </row>
     <row r="3" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="71" t="s">

--- a/NAP mock data.xlsx
+++ b/NAP mock data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC561869-D2D5-4A1D-824E-BD4C11E46DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00EC873D-5AD3-43D0-967E-2A55EC5A7505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market growth" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="323">
   <si>
     <t>Year</t>
   </si>
@@ -997,18 +997,6 @@
     <t>8.4 mo</t>
   </si>
   <si>
-    <t>Access</t>
-  </si>
-  <si>
-    <t>MMIT Formulary Coverage Data</t>
-  </si>
-  <si>
-    <t>Fulfilment</t>
-  </si>
-  <si>
-    <t>Improving</t>
-  </si>
-  <si>
     <t>Compliance</t>
   </si>
   <si>
@@ -1057,9 +1045,6 @@
     <t>Primary care</t>
   </si>
   <si>
-    <t>Lipid spec.</t>
-  </si>
-  <si>
     <t>Liphendra Compliance — monthly source data</t>
   </si>
   <si>
@@ -1082,6 +1067,9 @@
   </si>
   <si>
     <t>Leqvio</t>
+  </si>
+  <si>
+    <t>Other spec.</t>
   </si>
 </sst>
 </file>
@@ -1808,12 +1796,6 @@
     <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1822,6 +1804,12 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4067,10 +4055,10 @@
         <v>128</v>
       </c>
       <c r="G13" s="52"/>
-      <c r="H13" s="93" t="s">
+      <c r="H13" s="91" t="s">
         <v>58</v>
       </c>
-      <c r="I13" s="93" t="s">
+      <c r="I13" s="91" t="s">
         <v>128</v>
       </c>
     </row>
@@ -4091,10 +4079,10 @@
         <v>131</v>
       </c>
       <c r="G14" s="58"/>
-      <c r="H14" s="94">
+      <c r="H14" s="92">
         <v>46204</v>
       </c>
-      <c r="I14" s="92" t="s">
+      <c r="I14" s="90" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4115,10 +4103,10 @@
         <v>133</v>
       </c>
       <c r="G15" s="58"/>
-      <c r="H15" s="94">
+      <c r="H15" s="92">
         <v>46235</v>
       </c>
-      <c r="I15" s="92" t="s">
+      <c r="I15" s="90" t="s">
         <v>133</v>
       </c>
     </row>
@@ -4139,10 +4127,10 @@
         <v>135</v>
       </c>
       <c r="G16" s="58"/>
-      <c r="H16" s="94">
+      <c r="H16" s="92">
         <v>46266</v>
       </c>
-      <c r="I16" s="92" t="s">
+      <c r="I16" s="90" t="s">
         <v>135</v>
       </c>
     </row>
@@ -4163,10 +4151,10 @@
         <v>137</v>
       </c>
       <c r="G17" s="58"/>
-      <c r="H17" s="94">
+      <c r="H17" s="92">
         <v>46296</v>
       </c>
-      <c r="I17" s="92" t="s">
+      <c r="I17" s="90" t="s">
         <v>137</v>
       </c>
     </row>
@@ -4187,10 +4175,10 @@
         <v>139</v>
       </c>
       <c r="G18" s="58"/>
-      <c r="H18" s="94">
+      <c r="H18" s="92">
         <v>46327</v>
       </c>
-      <c r="I18" s="92" t="s">
+      <c r="I18" s="90" t="s">
         <v>139</v>
       </c>
     </row>
@@ -4211,10 +4199,10 @@
         <v>141</v>
       </c>
       <c r="G19" s="61"/>
-      <c r="H19" s="94">
+      <c r="H19" s="92">
         <v>46357</v>
       </c>
-      <c r="I19" s="93" t="s">
+      <c r="I19" s="91" t="s">
         <v>141</v>
       </c>
     </row>
@@ -4291,19 +4279,19 @@
         <v>146</v>
       </c>
       <c r="I3" s="63" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="J3" s="88" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="K3" s="88" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="L3" s="88" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="M3" s="88" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="N3" s="63"/>
       <c r="O3" s="63"/>
@@ -7362,75 +7350,38 @@
         <v>292</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="67" t="s">
         <v>298</v>
       </c>
       <c r="C8" s="54">
-        <v>0.41</v>
-      </c>
-      <c r="D8" s="54">
-        <v>0.35</v>
-      </c>
-      <c r="E8" s="54">
-        <v>0.38</v>
-      </c>
-      <c r="F8" s="55">
-        <v>0.39</v>
+        <v>0.84</v>
+      </c>
+      <c r="D8" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="54">
+        <v>0.83</v>
       </c>
       <c r="G8" s="67" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H8" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="67" t="s">
-        <v>300</v>
-      </c>
-      <c r="C9" s="54">
-        <v>0.9</v>
-      </c>
-      <c r="D9" s="54">
-        <v>0.82</v>
-      </c>
-      <c r="E9" s="54">
-        <v>0.85</v>
-      </c>
-      <c r="F9" s="55">
-        <v>0.87</v>
-      </c>
-      <c r="G9" s="67" t="s">
-        <v>301</v>
-      </c>
-      <c r="H9" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="67" t="s">
-        <v>302</v>
-      </c>
-      <c r="C10" s="54">
-        <v>0.84</v>
-      </c>
-      <c r="D10" s="67" t="s">
-        <v>130</v>
-      </c>
-      <c r="E10" s="67" t="s">
-        <v>130</v>
-      </c>
-      <c r="F10" s="54">
-        <v>0.83</v>
-      </c>
-      <c r="G10" s="67" t="s">
-        <v>294</v>
-      </c>
-      <c r="H10" t="s">
-        <v>292</v>
-      </c>
-    </row>
+      <c r="B9" s="67"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="67"/>
+    </row>
+    <row r="10" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7447,48 +7398,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="90" t="s">
-        <v>303</v>
-      </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
+      <c r="A1" s="93" t="s">
+        <v>299</v>
+      </c>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="91" t="s">
-        <v>304</v>
-      </c>
-      <c r="B2" s="91"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
+      <c r="A2" s="94" t="s">
+        <v>300</v>
+      </c>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
     </row>
     <row r="3" spans="1:7" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="71" t="s">
         <v>58</v>
       </c>
       <c r="B3" s="71" t="s">
+        <v>301</v>
+      </c>
+      <c r="C3" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="D3" s="71" t="s">
+        <v>303</v>
+      </c>
+      <c r="E3" s="71" t="s">
+        <v>304</v>
+      </c>
+      <c r="F3" s="71" t="s">
         <v>305</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="G3" s="71" t="s">
         <v>306</v>
-      </c>
-      <c r="D3" s="71" t="s">
-        <v>307</v>
-      </c>
-      <c r="E3" s="71" t="s">
-        <v>308</v>
-      </c>
-      <c r="F3" s="71" t="s">
-        <v>309</v>
-      </c>
-      <c r="G3" s="71" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8062,61 +8013,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="90" t="s">
-        <v>311</v>
-      </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
+      <c r="A1" s="93" t="s">
+        <v>307</v>
+      </c>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="91" t="s">
-        <v>312</v>
-      </c>
-      <c r="B2" s="91"/>
-      <c r="C2" s="91"/>
+      <c r="A2" s="94" t="s">
+        <v>308</v>
+      </c>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
     </row>
     <row r="3" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="71" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B3" s="71" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C3" s="71" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="75" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B4" s="76">
         <v>3200</v>
       </c>
       <c r="C4" s="77">
-        <v>6.1</v>
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="75" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B5" s="76">
         <v>2600</v>
       </c>
       <c r="C5" s="77">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="75" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B6" s="76">
         <v>900</v>
       </c>
       <c r="C6" s="77">
-        <v>9.1999999999999993</v>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>
@@ -8138,20 +8089,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="90" t="s">
-        <v>319</v>
-      </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
+      <c r="A1" s="93" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="91" t="s">
-        <v>320</v>
-      </c>
-      <c r="B2" s="91"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
+      <c r="A2" s="94" t="s">
+        <v>315</v>
+      </c>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
     </row>
     <row r="3" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="71" t="s">
@@ -8172,13 +8123,13 @@
         <v>46204</v>
       </c>
       <c r="B4" s="78">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="C4" s="78">
         <v>0.79</v>
       </c>
       <c r="D4" s="75" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8186,13 +8137,13 @@
         <v>46235</v>
       </c>
       <c r="B5" s="78">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="C5" s="78">
         <v>0.8</v>
       </c>
       <c r="D5" s="75" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8200,13 +8151,13 @@
         <v>46266</v>
       </c>
       <c r="B6" s="78">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="C6" s="78">
         <v>0.81</v>
       </c>
       <c r="D6" s="75" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8214,13 +8165,13 @@
         <v>46296</v>
       </c>
       <c r="B7" s="78">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="C7" s="78">
         <v>0.82</v>
       </c>
       <c r="D7" s="75" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8228,13 +8179,13 @@
         <v>46327</v>
       </c>
       <c r="B8" s="78">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="C8" s="78">
         <v>0.82</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -8242,13 +8193,13 @@
         <v>46357</v>
       </c>
       <c r="B9" s="78">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="C9" s="78">
         <v>0.83</v>
       </c>
       <c r="D9" s="75" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>

--- a/NAP mock data.xlsx
+++ b/NAP mock data.xlsx
@@ -1,23 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{960A146B-9343-4688-84E4-DD7F9786AC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="5" activeTab="7"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Market growth" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Patient split" state="visible" r:id="rId5"/>
-    <sheet sheetId="5" name="Product Uptake" state="visible" r:id="rId6"/>
-    <sheet sheetId="3" name="Source of Liphendra starts" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="Liphendra NPS and Persistency" state="visible" r:id="rId8"/>
-    <sheet sheetId="4" name="Assumption Monitor" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="LLT Product Mix" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Prescriber Breadth Depth" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Compliance" state="visible" r:id="rId12"/>
+    <sheet name="Market growth" sheetId="1" r:id="rId1"/>
+    <sheet name="Patient split" sheetId="2" r:id="rId2"/>
+    <sheet name="Product Uptake" sheetId="5" r:id="rId3"/>
+    <sheet name="Source of Liphendra starts" sheetId="3" r:id="rId4"/>
+    <sheet name="Liphendra NPS and Persistency" sheetId="6" r:id="rId5"/>
+    <sheet name="Assumption Monitor" sheetId="4" r:id="rId6"/>
+    <sheet name="LLT Product Mix" sheetId="7" r:id="rId7"/>
+    <sheet name="Prescriber Breadth Depth" sheetId="8" r:id="rId8"/>
+    <sheet name="Compliance" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -84,7 +99,7 @@
     <t>ASCVD 21+ Points Above Goal | Max Dose Statin and/or Combo Therapy</t>
   </si>
   <si>
-    <t xml:space="preserve">1D
+    <t>1D
 ——
 Inadequately Treated (Max Tolerated Statin)
 21+ pts above goal</t>
@@ -93,7 +108,7 @@
     <t>ASCVD at Goal</t>
   </si>
   <si>
-    <t xml:space="preserve">1F
+    <t>1F
 ——
  Any Treatment
 At goal (≤5)</t>
@@ -102,7 +117,7 @@
     <t>ASCVD 21+ Points Above Goal | Intolerant/Unwilling to Use Statins</t>
   </si>
   <si>
-    <t xml:space="preserve">1B
+    <t>1B
 ——
 Statin Intolerant / Unwilling
 21+ pts above goal</t>
@@ -111,7 +126,7 @@
     <t>ASCVD 6-20 Points Above Goal| Intolerant/Unwilling to Use Statins</t>
   </si>
   <si>
-    <t xml:space="preserve">1A
+    <t>1A
 ——
 Statin Intolerant / Unwilling
 6–20 pts above goal</t>
@@ -120,7 +135,7 @@
     <t>ASCVD 6-20 Points Above Goal | Max Dose Statin and/or Combo Therapy</t>
   </si>
   <si>
-    <t xml:space="preserve">1C
+    <t>1C
 ——
 Inadequately Treated (Max Tolerated Statin)
 6–20 pts above goal</t>
@@ -129,7 +144,7 @@
     <t>ASCVD | Statin Only Treatment</t>
   </si>
   <si>
-    <t xml:space="preserve">1E
+    <t>1E
 ——
 No treatment beyond statin needed
 6+ pts above goal</t>
@@ -138,7 +153,7 @@
     <t>PP w/T2D 21+ Points Above Goal | Max Dose Statin and/or Combo Therapy</t>
   </si>
   <si>
-    <t xml:space="preserve">2D
+    <t>2D
 ——
 Inadequately Treated (Max Tolerated Statin)
 21+ pts above goal</t>
@@ -147,7 +162,7 @@
     <t>PP w/T2D 6-20 Points Above Goal | Max Dose Statin and/or Combo Therapy</t>
   </si>
   <si>
-    <t xml:space="preserve">2C
+    <t>2C
 ——
 Inadequately Treated (Max Tolerated Statin)
 6–20 pts above goal</t>
@@ -156,7 +171,7 @@
     <t>PP w/T2D at Goal</t>
   </si>
   <si>
-    <t xml:space="preserve">2F
+    <t>2F
 ——
  Any Treatment
 At goal (≤5)</t>
@@ -165,7 +180,7 @@
     <t>PP w/T2D 6-20 Points Above Goal | Intolerant/Unwilling to Use Statins</t>
   </si>
   <si>
-    <t xml:space="preserve">2B
+    <t>2B
 ——
 Statin Intolerant / Unwilling
 21+ pts above goal</t>
@@ -174,7 +189,7 @@
     <t>PP w/T2D 21+ Points Above Goal | Intolerant/Unwilling to Use Statins</t>
   </si>
   <si>
-    <t xml:space="preserve">2A
+    <t>2A
 ——
 Statin Intolerant / Unwilling
 6–20 pts above goal</t>
@@ -183,7 +198,7 @@
     <t>PP w/T2D | Statin Only Treatment</t>
   </si>
   <si>
-    <t xml:space="preserve">2E
+    <t>2E
 ——
 No treatment beyond statin needed
 6+ pts above goal</t>
@@ -204,60 +219,60 @@
     <t>Total - Base case</t>
   </si>
   <si>
-    <t xml:space="preserve">3A
+    <t>3A
 ——
 Statin Intolerant or Inadequate
 0+ pts above goal</t>
   </si>
   <si>
-    <t xml:space="preserve">3B
+    <t>3B
 ——
 No treatment beyond statin needed 
 0+ pts above goal</t>
   </si>
   <si>
-    <t xml:space="preserve">3C
+    <t>3C
 ——
 Not treated</t>
   </si>
   <si>
-    <t xml:space="preserve">4
+    <t>4
 ——
 Statin Intolerant or Inadequate 
 0+ pts above goal</t>
   </si>
   <si>
-    <t xml:space="preserve">4
+    <t>4
 ——
 No treatment beyond statin needed
 0+ pts above goal</t>
   </si>
   <si>
-    <t xml:space="preserve">4
+    <t>4
 ——
 Statin Intolerant or Inadequate or Statin Titrated
 0+ pts above goal</t>
   </si>
   <si>
-    <t xml:space="preserve">1G
+    <t>1G
 ——
 Not treated
 At goal (≤5 above)</t>
   </si>
   <si>
-    <t xml:space="preserve">1H
+    <t>1H
 ——
 Not treated
 6+ pts above goal</t>
   </si>
   <si>
-    <t xml:space="preserve">2G
+    <t>2G
 ——
 Not treated
 At goal (≤5 above)</t>
   </si>
   <si>
-    <t xml:space="preserve">2H
+    <t>2H
 ——
 Not treated
 6+ pts above goal</t>
@@ -1061,125 +1076,125 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#.#,,&quot;M&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="mmm yy"/>
+    <numFmt numFmtId="166" formatCode="mmm\ yy"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;M&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF2E5CA8"/>
-      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
-      <sz val="8"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <i/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
+      <sz val="15"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="15"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <i/>
+      <sz val="11"/>
       <color rgb="FF667085"/>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
@@ -1240,7 +1255,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999511703848384"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -1781,12 +1796,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1797,6 +1806,12 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1815,26 +1830,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="Table14" displayName="Table14" ref="B3:I63" totalsRowShown="1" headerRowCount="0">
-  <autoFilter>
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table14" displayName="Table14" ref="B3:I63" headerRowCount="0">
   <tableColumns count="8">
-    <tableColumn id="1" name="Month"/>
-    <tableColumn id="2" name="Nurtec (Oral CGRP)"/>
-    <tableColumn id="3" name="Ezetemibe"/>
-    <tableColumn id="4" name="Farxiga"/>
-    <tableColumn id="5" name="Jardiance"/>
-    <tableColumn id="6" name="Ozempic"/>
-    <tableColumn id="7" name="Nucala"/>
-    <tableColumn id="8" name="Ubrelvy"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Month"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nurtec (Oral CGRP)"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Ezetemibe"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Farxiga"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Jardiance"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ozempic"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Nucala"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Ubrelvy"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2034,15 +2039,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:F25"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.109375" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="14.4" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -2056,66 +2061,66 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="14.4" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>2026</v>
       </c>
       <c r="C4" s="3">
-        <v>70276510.1282979</v>
+        <v>70276510.128297895</v>
       </c>
       <c r="D4" s="3">
-        <v>70776510.1282979</v>
+        <v>70776510.128297895</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="14.4" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <f t="shared" ref="B5:B21" si="0">B4+1</f>
         <v>2027</v>
       </c>
       <c r="C5" s="3">
-        <v>71500000.1305315</v>
+        <v>71500000.130531505</v>
       </c>
       <c r="D5" s="3">
-        <v>72300000.1305315</v>
+        <v>72300000.130531505</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" ht="14.4" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
       <c r="C6" s="3">
-        <v>72939400.1331593</v>
+        <v>72939400.133159295</v>
       </c>
       <c r="D6" s="3">
-        <v>73839400.1331593</v>
+        <v>73839400.133159295</v>
       </c>
       <c r="F6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="14.4" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="C7" s="3">
-        <v>74483147.8735519</v>
+        <v>74483147.873551905</v>
       </c>
       <c r="D7" s="3">
-        <v>75483147.8735519</v>
+        <v>75483147.873551905</v>
       </c>
       <c r="F7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <f t="shared" si="0"/>
         <v>2030</v>
@@ -2127,173 +2132,173 @@
         <v>77045549.3195225</v>
       </c>
     </row>
-    <row r="9" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
       <c r="C9" s="3">
-        <v>77584100.0617359</v>
+        <v>77584100.061735898</v>
       </c>
       <c r="D9" s="3">
-        <v>78584100.0617359</v>
-      </c>
-    </row>
-    <row r="10" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>78584100.061735898</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
       <c r="C10" s="3">
-        <v>79078001.4307763</v>
+        <v>79078001.430776298</v>
       </c>
       <c r="D10" s="3">
-        <v>80278001.4307763</v>
-      </c>
-    </row>
-    <row r="11" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>80278001.430776298</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <f t="shared" si="0"/>
         <v>2033</v>
       </c>
       <c r="C11" s="3">
-        <v>80517404.8384735</v>
+        <v>80517404.838473499</v>
       </c>
       <c r="D11" s="3">
-        <v>82017404.8384735</v>
-      </c>
-    </row>
-    <row r="12" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>82017404.838473499</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <f t="shared" si="0"/>
         <v>2034</v>
       </c>
       <c r="C12" s="3">
-        <v>81904630.2507732</v>
+        <v>81904630.250773206</v>
       </c>
       <c r="D12" s="3">
-        <v>83704630.2507732</v>
-      </c>
-    </row>
-    <row r="13" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>83704630.250773206</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <f t="shared" si="0"/>
         <v>2035</v>
       </c>
       <c r="C13" s="3">
-        <v>83242203.0826524</v>
+        <v>83242203.082652405</v>
       </c>
       <c r="D13" s="3">
-        <v>85542203.0826524</v>
-      </c>
-    </row>
-    <row r="14" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>85542203.082652405</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <f t="shared" si="0"/>
         <v>2036</v>
       </c>
       <c r="C14" s="3">
-        <v>84528479.8723046</v>
+        <v>84528479.872304603</v>
       </c>
       <c r="D14" s="3">
-        <v>87328479.8723046</v>
-      </c>
-    </row>
-    <row r="15" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>87328479.872304603</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <f t="shared" si="0"/>
         <v>2037</v>
       </c>
       <c r="C15" s="3">
-        <v>85765943.3481735</v>
+        <v>85765943.348173499</v>
       </c>
       <c r="D15" s="3">
-        <v>89065943.3481735</v>
-      </c>
-    </row>
-    <row r="16" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>89065943.348173499</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <f t="shared" si="0"/>
         <v>2038</v>
       </c>
       <c r="C16" s="3">
-        <v>86956956.0746462</v>
+        <v>86956956.074646205</v>
       </c>
       <c r="D16" s="3">
-        <v>91056956.0746462</v>
-      </c>
-    </row>
-    <row r="17" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>91056956.074646205</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <f t="shared" si="0"/>
         <v>2039</v>
       </c>
       <c r="C17" s="3">
-        <v>88103766.2679935</v>
+        <v>88103766.267993495</v>
       </c>
       <c r="D17" s="3">
-        <v>92903766.2679935</v>
-      </c>
-    </row>
-    <row r="18" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>92903766.267993495</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <f t="shared" si="0"/>
         <v>2040</v>
       </c>
       <c r="C18" s="3">
-        <v>89208513.3308187</v>
+        <v>89208513.330818698</v>
       </c>
       <c r="D18" s="3">
-        <v>94808513.3308187</v>
-      </c>
-    </row>
-    <row r="19" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>94808513.330818698</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <f t="shared" si="0"/>
         <v>2041</v>
       </c>
       <c r="C19" s="3">
-        <v>90269246.9147585</v>
+        <v>90269246.914758503</v>
       </c>
       <c r="D19" s="3">
-        <v>96869246.9147585</v>
-      </c>
-    </row>
-    <row r="20" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>96869246.914758503</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <f t="shared" si="0"/>
         <v>2042</v>
       </c>
       <c r="C20" s="3">
-        <v>91288097.272191</v>
+        <v>91288097.272191003</v>
       </c>
       <c r="D20" s="3">
-        <v>98688097.272191</v>
-      </c>
-    </row>
-    <row r="21" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>98688097.272191003</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <f t="shared" si="0"/>
         <v>2043</v>
       </c>
       <c r="C21" s="3">
-        <v>92267091.5512792</v>
+        <v>92267091.551279202</v>
       </c>
       <c r="D21" s="3">
-        <v>100667091.551279</v>
-      </c>
-    </row>
-    <row r="22" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>100667091.55127899</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="25" ht="14.4" customHeight="1" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
     </row>
@@ -2303,9 +2308,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:I40"/>
-  <sheetFormatPr defaultRowHeight="11.55" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="11.55" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="64.88671875" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
@@ -2314,12 +2319,12 @@
     <col min="8" max="8" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="14.4" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>9</v>
       </c>
@@ -2327,7 +2332,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
@@ -2336,35 +2341,35 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="6" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C19:C24)</f>
-        <v>0.296</v>
-      </c>
-    </row>
-    <row r="7" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+        <v>0.29599999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="7">
         <f>SUM(C25:C26)</f>
-        <v>0.354</v>
-      </c>
-    </row>
-    <row r="10" ht="14.4" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+        <v>0.35399999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" ht="14.4" customHeight="1" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G11" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" ht="14.4" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
         <v>16</v>
       </c>
@@ -2375,7 +2380,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" ht="12" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>19</v>
       </c>
@@ -2383,7 +2388,7 @@
         <v>0.104</v>
       </c>
       <c r="D13" s="15">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="G13" t="s">
         <v>20</v>
@@ -2393,10 +2398,10 @@
       </c>
       <c r="I13" s="4">
         <f t="shared" ref="I13" si="0">H13/SUM($H$13:$H$26)</f>
-        <v>0.01133297909930196</v>
-      </c>
-    </row>
-    <row r="14" ht="12" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.1332979099301961E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="17" t="s">
         <v>21</v>
       </c>
@@ -2414,18 +2419,18 @@
       </c>
       <c r="I14" s="4">
         <f t="shared" ref="I14:I26" si="1">H14/SUM($H$13:$H$26)</f>
-        <v>0.04021670924443566</v>
-      </c>
-    </row>
-    <row r="15" ht="12" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>4.0216709244435662E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="17" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="18">
-        <v>0.077</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="D15" s="19">
-        <v>0.082</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="G15" t="s">
         <v>24</v>
@@ -2435,18 +2440,18 @@
       </c>
       <c r="I15" s="4">
         <f t="shared" si="1"/>
-        <v>0.005488044174117084</v>
-      </c>
-    </row>
-    <row r="16" ht="12" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>5.4880441741170837E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="20" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="21">
-        <v>0.009</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="D16" s="22">
-        <v>0.009</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="G16" t="s">
         <v>26</v>
@@ -2456,60 +2461,60 @@
       </c>
       <c r="I16" s="4">
         <f t="shared" si="1"/>
-        <v>0.0006478753574953763</v>
-      </c>
-    </row>
-    <row r="17" ht="12" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>6.4787535749537631E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C17" s="21">
-        <v>0.016</v>
+        <v>1.6E-2</v>
       </c>
       <c r="D17" s="22">
-        <v>0.016</v>
+        <v>1.6E-2</v>
       </c>
       <c r="G17" t="s">
         <v>28</v>
       </c>
       <c r="H17" s="16">
-        <v>9836.87374749499</v>
+        <v>9836.8737474949903</v>
       </c>
       <c r="I17" s="4">
         <f t="shared" si="1"/>
-        <v>0.002143001898487242</v>
-      </c>
-    </row>
-    <row r="18" ht="14.4" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.1430018984872419E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="23" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="24">
-        <v>0.033</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="D18" s="25">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="G18" t="s">
         <v>30</v>
       </c>
       <c r="H18" s="16">
-        <v>633852.8607292289</v>
+        <v>633852.86072922894</v>
       </c>
       <c r="I18" s="4">
         <f t="shared" si="1"/>
         <v>0.13808735567539607</v>
       </c>
     </row>
-    <row r="19" ht="12" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="26" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="27">
-        <v>0.096</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="D19" s="28">
-        <v>0.091</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="G19" t="s">
         <v>32</v>
@@ -2519,39 +2524,39 @@
       </c>
       <c r="I19" s="4">
         <f t="shared" si="1"/>
-        <v>0.0026059737536730486</v>
-      </c>
-    </row>
-    <row r="20" ht="12" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2.6059737536730486E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="29" t="s">
         <v>33</v>
       </c>
       <c r="C20" s="30">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D20" s="31">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G20" t="s">
         <v>34</v>
       </c>
       <c r="H20" s="16">
-        <v>3892.316806416332</v>
+        <v>3892.3168064163319</v>
       </c>
       <c r="I20" s="4">
         <f t="shared" si="1"/>
-        <v>0.0008479566292886637</v>
-      </c>
-    </row>
-    <row r="21" ht="12" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>8.4795662928866368E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="29" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="30">
-        <v>0.061</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="D21" s="31">
-        <v>0.064</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="G21" t="s">
         <v>36</v>
@@ -2561,18 +2566,18 @@
       </c>
       <c r="I21" s="4">
         <f t="shared" si="1"/>
-        <v>0.08013848155987159</v>
-      </c>
-    </row>
-    <row r="22" ht="12" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>8.0138481559871591E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="29" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="30">
-        <v>0.011</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="D22" s="31">
-        <v>0.012</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G22" t="s">
         <v>38</v>
@@ -2582,18 +2587,18 @@
       </c>
       <c r="I22" s="4">
         <f t="shared" si="1"/>
-        <v>0.00145435481299314</v>
-      </c>
-    </row>
-    <row r="23" ht="12" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1.45435481299314E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="29" t="s">
         <v>39</v>
       </c>
       <c r="C23" s="30">
-        <v>0.077</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="D23" s="31">
-        <v>0.068</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="G23" t="s">
         <v>40</v>
@@ -2603,18 +2608,18 @@
       </c>
       <c r="I23" s="4">
         <f t="shared" si="1"/>
-        <v>0.0004959789060296322</v>
-      </c>
-    </row>
-    <row r="24" ht="14.4" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>4.9597890602963218E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="32" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="33">
-        <v>0.036</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="D24" s="34">
-        <v>0.035</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="G24" t="s">
         <v>42</v>
@@ -2624,15 +2629,15 @@
       </c>
       <c r="I24" s="4">
         <f t="shared" si="1"/>
-        <v>0.05519243738230881</v>
-      </c>
-    </row>
-    <row r="25" ht="12" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+        <v>5.5192437382308807E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="35" t="s">
         <v>43</v>
       </c>
       <c r="C25" s="36">
-        <v>0.256</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="D25" s="37">
         <v>0.27</v>
@@ -2649,16 +2654,16 @@
         <v>0.35380942702012164</v>
       </c>
     </row>
-    <row r="26" ht="14.4" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="38" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="39">
-        <v>0.098</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="D26" s="40">
         <f>1-SUM(D13:D25)</f>
-        <v>0.09399999999999975</v>
+        <v>9.399999999999975E-2</v>
       </c>
       <c r="G26" t="s">
         <v>46</v>
@@ -2669,10 +2674,10 @@
       </c>
       <c r="I26" s="4">
         <f t="shared" si="1"/>
-        <v>0.3075394244864801</v>
-      </c>
-    </row>
-    <row r="27" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.30753942448648008</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="41" t="s">
         <v>47</v>
       </c>
@@ -2687,16 +2692,16 @@
       <c r="E27" s="44"/>
       <c r="H27" s="16"/>
     </row>
-    <row r="28" ht="14.4" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H28" s="16"/>
     </row>
-    <row r="29" ht="14.4" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H29" s="16"/>
     </row>
-    <row r="30" ht="14.4" customHeight="1" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H30" s="16"/>
     </row>
-    <row r="31" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G31" t="s">
         <v>48</v>
       </c>
@@ -2704,7 +2709,7 @@
         <v>113118</v>
       </c>
     </row>
-    <row r="32" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G32" t="s">
         <v>49</v>
       </c>
@@ -2712,7 +2717,7 @@
         <v>1301493</v>
       </c>
     </row>
-    <row r="33" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G33" t="s">
         <v>50</v>
       </c>
@@ -2720,7 +2725,7 @@
         <v>209456</v>
       </c>
     </row>
-    <row r="34" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G34" t="s">
         <v>51</v>
       </c>
@@ -2728,7 +2733,7 @@
         <v>79616</v>
       </c>
     </row>
-    <row r="35" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G35" t="s">
         <v>52</v>
       </c>
@@ -2736,7 +2741,7 @@
         <v>1046324</v>
       </c>
     </row>
-    <row r="36" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G36" t="s">
         <v>53</v>
       </c>
@@ -2744,15 +2749,15 @@
         <v>285737</v>
       </c>
     </row>
-    <row r="37" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G37" t="s">
         <v>54</v>
       </c>
       <c r="H37" s="16">
-        <v>25600.42778390298</v>
-      </c>
-    </row>
-    <row r="38" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+        <v>25600.427783902978</v>
+      </c>
+    </row>
+    <row r="38" spans="7:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G38" t="s">
         <v>55</v>
       </c>
@@ -2760,15 +2765,15 @@
         <v>133075.57221609703</v>
       </c>
     </row>
-    <row r="39" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G39" t="s">
         <v>56</v>
       </c>
       <c r="H39" s="16">
-        <v>40414.10333531864</v>
-      </c>
-    </row>
-    <row r="40" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+        <v>40414.103335318643</v>
+      </c>
+    </row>
+    <row r="40" spans="7:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G40" t="s">
         <v>57</v>
       </c>
@@ -2782,587 +2787,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:M19"/>
-  <sheetFormatPr defaultRowHeight="11.55" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
-  <cols>
-    <col min="2" max="2" width="9.109375" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" customWidth="1"/>
-    <col min="5" max="5" width="22.5546875" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="23.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" ht="46.05" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="60" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="60" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="60" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="H3" s="60" t="s">
-        <v>58</v>
-      </c>
-      <c r="I3" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="J3" s="61" t="s">
-        <v>67</v>
-      </c>
-      <c r="K3" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="L3" s="61" t="s">
-        <v>69</v>
-      </c>
-      <c r="M3" s="61" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" ht="14.4" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="62">
-        <v>46204</v>
-      </c>
-      <c r="C4" s="63">
-        <v>0.06</v>
-      </c>
-      <c r="D4" s="64">
-        <v>0.9</v>
-      </c>
-      <c r="E4" s="63">
-        <v>0.04</v>
-      </c>
-      <c r="H4" s="65">
-        <v>46229</v>
-      </c>
-      <c r="I4" s="66">
-        <v>1200</v>
-      </c>
-      <c r="J4" s="67">
-        <v>0.58</v>
-      </c>
-      <c r="K4" s="67">
-        <v>0.78</v>
-      </c>
-      <c r="L4" s="68">
-        <v>6.8</v>
-      </c>
-      <c r="M4" s="66">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="5" ht="14.4" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="62">
-        <v>46235</v>
-      </c>
-      <c r="C5" s="63">
-        <v>0.08</v>
-      </c>
-      <c r="D5" s="64">
-        <v>0.88</v>
-      </c>
-      <c r="E5" s="63">
-        <v>0.04</v>
-      </c>
-      <c r="H5" s="65">
-        <v>46260</v>
-      </c>
-      <c r="I5" s="66">
-        <v>1450</v>
-      </c>
-      <c r="J5" s="67">
-        <v>0.55</v>
-      </c>
-      <c r="K5" s="67">
-        <v>0.75</v>
-      </c>
-      <c r="L5" s="68">
-        <v>6.6</v>
-      </c>
-      <c r="M5" s="68">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="6" ht="14.4" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="62">
-        <v>46266</v>
-      </c>
-      <c r="C6" s="63">
-        <v>0.1</v>
-      </c>
-      <c r="D6" s="64">
-        <v>0.86</v>
-      </c>
-      <c r="E6" s="63">
-        <v>0.04</v>
-      </c>
-      <c r="H6" s="65">
-        <v>46291</v>
-      </c>
-      <c r="I6" s="66">
-        <v>1750</v>
-      </c>
-      <c r="J6" s="67">
-        <v>0.51</v>
-      </c>
-      <c r="K6" s="67">
-        <v>0.72</v>
-      </c>
-      <c r="L6" s="68">
-        <v>6.4</v>
-      </c>
-      <c r="M6" s="68">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="7" ht="14.4" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="62">
-        <v>46296</v>
-      </c>
-      <c r="C7" s="63">
-        <v>0.12</v>
-      </c>
-      <c r="D7" s="64">
-        <v>0.84</v>
-      </c>
-      <c r="E7" s="63">
-        <v>0.04</v>
-      </c>
-      <c r="H7" s="65">
-        <v>46321</v>
-      </c>
-      <c r="I7" s="66">
-        <v>2100</v>
-      </c>
-      <c r="J7" s="67">
-        <v>0.47</v>
-      </c>
-      <c r="K7" s="67">
-        <v>0.68</v>
-      </c>
-      <c r="L7" s="68">
-        <v>6.2</v>
-      </c>
-      <c r="M7" s="68">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="8" ht="14.4" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="62">
-        <v>46327</v>
-      </c>
-      <c r="C8" s="63">
-        <v>0.14</v>
-      </c>
-      <c r="D8" s="64">
-        <v>0.82</v>
-      </c>
-      <c r="E8" s="63">
-        <v>0.04</v>
-      </c>
-      <c r="H8" s="65">
-        <v>46352</v>
-      </c>
-      <c r="I8" s="66">
-        <v>2500</v>
-      </c>
-      <c r="J8" s="67">
-        <v>0.43</v>
-      </c>
-      <c r="K8" s="67">
-        <v>0.64</v>
-      </c>
-      <c r="L8" s="68">
-        <v>6</v>
-      </c>
-      <c r="M8" s="68">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" ht="14.4" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="62">
-        <v>46357</v>
-      </c>
-      <c r="C9" s="63">
-        <v>0.16</v>
-      </c>
-      <c r="D9" s="64">
-        <v>0.8</v>
-      </c>
-      <c r="E9" s="63">
-        <v>0.04</v>
-      </c>
-      <c r="H9" s="65">
-        <v>46382</v>
-      </c>
-      <c r="I9" s="69">
-        <v>2950</v>
-      </c>
-      <c r="J9" s="70">
-        <v>0.39</v>
-      </c>
-      <c r="K9" s="70">
-        <v>0.6</v>
-      </c>
-      <c r="L9" s="61">
-        <v>5.8</v>
-      </c>
-      <c r="M9" s="61">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="10" ht="14.4" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="62"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-    </row>
-    <row r="13" ht="46.05" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="60" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="61" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="61" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" s="61"/>
-      <c r="H13" s="72" t="s">
-        <v>58</v>
-      </c>
-      <c r="I13" s="72" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" ht="14.4" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="73">
-        <v>46204</v>
-      </c>
-      <c r="C14" s="68" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="68" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="66">
-        <v>8200</v>
-      </c>
-      <c r="F14" s="68" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="67"/>
-      <c r="H14" s="74">
-        <v>46204</v>
-      </c>
-      <c r="I14" s="75" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" ht="14.4" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="73">
-        <v>46235</v>
-      </c>
-      <c r="C15" s="68" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="76">
-        <v>0.01</v>
-      </c>
-      <c r="E15" s="66">
-        <v>8450</v>
-      </c>
-      <c r="F15" s="68" t="s">
-        <v>79</v>
-      </c>
-      <c r="G15" s="67"/>
-      <c r="H15" s="74">
-        <v>46235</v>
-      </c>
-      <c r="I15" s="75" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" ht="14.4" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="73">
-        <v>46266</v>
-      </c>
-      <c r="C16" s="68" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="76">
-        <v>0.01</v>
-      </c>
-      <c r="E16" s="66">
-        <v>8750</v>
-      </c>
-      <c r="F16" s="68" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" s="67"/>
-      <c r="H16" s="74">
-        <v>46266</v>
-      </c>
-      <c r="I16" s="75" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" ht="14.4" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="73">
-        <v>46296</v>
-      </c>
-      <c r="C17" s="68" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="76">
-        <v>0.015</v>
-      </c>
-      <c r="E17" s="66">
-        <v>9050</v>
-      </c>
-      <c r="F17" s="68" t="s">
-        <v>83</v>
-      </c>
-      <c r="G17" s="67"/>
-      <c r="H17" s="74">
-        <v>46296</v>
-      </c>
-      <c r="I17" s="75" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" ht="14.4" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="73">
-        <v>46327</v>
-      </c>
-      <c r="C18" s="68" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" s="76">
-        <v>0.019</v>
-      </c>
-      <c r="E18" s="66">
-        <v>9400</v>
-      </c>
-      <c r="F18" s="68" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" s="67"/>
-      <c r="H18" s="74">
-        <v>46327</v>
-      </c>
-      <c r="I18" s="75" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" ht="14.4" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="73">
-        <v>46357</v>
-      </c>
-      <c r="C19" s="61" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" s="76">
-        <v>0.019</v>
-      </c>
-      <c r="E19" s="69">
-        <v>9800</v>
-      </c>
-      <c r="F19" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="70"/>
-      <c r="H19" s="74">
-        <v>46357</v>
-      </c>
-      <c r="I19" s="72" t="s">
-        <v>87</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:H10"/>
-  <sheetFormatPr defaultRowHeight="11.55" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
-  <cols>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" ht="22.95" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="60" t="s">
-        <v>288</v>
-      </c>
-      <c r="C3" s="60" t="s">
-        <v>289</v>
-      </c>
-      <c r="D3" s="60" t="s">
-        <v>290</v>
-      </c>
-      <c r="E3" s="60" t="s">
-        <v>291</v>
-      </c>
-      <c r="F3" s="60" t="s">
-        <v>292</v>
-      </c>
-      <c r="G3" s="60" t="s">
-        <v>293</v>
-      </c>
-      <c r="H3" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="4" ht="22.95" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="81" t="s">
-        <v>295</v>
-      </c>
-      <c r="C4" s="82">
-        <v>0.0158</v>
-      </c>
-      <c r="D4" s="82">
-        <v>0.017</v>
-      </c>
-      <c r="E4" s="82">
-        <v>0.019</v>
-      </c>
-      <c r="F4" s="83">
-        <v>0.021</v>
-      </c>
-      <c r="G4" s="81" t="s">
-        <v>296</v>
-      </c>
-      <c r="H4" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="5" ht="22.95" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="81" t="s">
-        <v>298</v>
-      </c>
-      <c r="C5" s="82">
-        <v>0.806</v>
-      </c>
-      <c r="D5" s="82">
-        <v>0.807</v>
-      </c>
-      <c r="E5" s="82">
-        <v>0.808</v>
-      </c>
-      <c r="F5" s="83">
-        <v>0.81</v>
-      </c>
-      <c r="G5" s="81" t="s">
-        <v>299</v>
-      </c>
-      <c r="H5" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="6" ht="22.95" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="81" t="s">
-        <v>300</v>
-      </c>
-      <c r="C6" s="82">
-        <v>0.807</v>
-      </c>
-      <c r="D6" s="82">
-        <v>0.808</v>
-      </c>
-      <c r="E6" s="82">
-        <v>0.811</v>
-      </c>
-      <c r="F6" s="83">
-        <v>0.815</v>
-      </c>
-      <c r="G6" s="81" t="s">
-        <v>296</v>
-      </c>
-      <c r="H6" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="7" ht="22.95" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="81" t="s">
-        <v>301</v>
-      </c>
-      <c r="C7" s="81" t="s">
-        <v>302</v>
-      </c>
-      <c r="D7" s="81">
-        <v>8.2</v>
-      </c>
-      <c r="E7" s="81">
-        <v>7.8</v>
-      </c>
-      <c r="F7" s="84">
-        <v>7.3</v>
-      </c>
-      <c r="G7" s="81" t="s">
-        <v>299</v>
-      </c>
-      <c r="H7" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="8" ht="28.8" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="81" t="s">
-        <v>303</v>
-      </c>
-      <c r="C8" s="63">
-        <v>0.84</v>
-      </c>
-      <c r="D8" s="81" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="81" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="63">
-        <v>0.83</v>
-      </c>
-      <c r="G8" s="81" t="s">
-        <v>299</v>
-      </c>
-      <c r="H8" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="9" ht="22.95" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="81"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="81"/>
-    </row>
-    <row r="10" ht="22.95" customHeight="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B3:O63"/>
-  <sheetFormatPr defaultRowHeight="11.55" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="11.55" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.33203125" customWidth="1"/>
     <col min="3" max="3" width="16.5546875" customWidth="1"/>
@@ -3378,7 +2805,7 @@
     <col min="14" max="15" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="11.55" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="45" t="s">
         <v>58</v>
       </c>
@@ -3402,7 +2829,7 @@
       <c r="N3" s="52"/>
       <c r="O3" s="52"/>
     </row>
-    <row r="4" ht="11.55" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="53">
         <v>46204</v>
       </c>
@@ -3410,7 +2837,7 @@
         <v>0.02</v>
       </c>
       <c r="D4" s="55">
-        <v>0.019</v>
+        <v>1.9E-2</v>
       </c>
       <c r="E4" s="56">
         <v>16000</v>
@@ -3428,7 +2855,7 @@
       <c r="N4" s="16"/>
       <c r="O4" s="16"/>
     </row>
-    <row r="5" ht="11.55" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="53">
         <v>46235</v>
       </c>
@@ -3436,7 +2863,7 @@
         <v>0.03</v>
       </c>
       <c r="D5" s="55">
-        <v>0.036</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="E5" s="56">
         <v>32333</v>
@@ -3454,7 +2881,7 @@
       <c r="N5" s="16"/>
       <c r="O5" s="16"/>
     </row>
-    <row r="6" ht="11.55" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="53">
         <v>46266</v>
       </c>
@@ -3462,7 +2889,7 @@
         <v>0.05</v>
       </c>
       <c r="D6" s="55">
-        <v>0.054</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="E6" s="56">
         <v>49000</v>
@@ -3478,15 +2905,15 @@
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
     </row>
-    <row r="7" ht="11.55" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="53">
         <v>46296</v>
       </c>
       <c r="C7" s="54">
-        <v>0.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D7" s="55">
-        <v>0.071</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="E7" s="56">
         <v>66000</v>
@@ -3502,7 +2929,7 @@
       <c r="N7" s="16"/>
       <c r="O7" s="16"/>
     </row>
-    <row r="8" ht="11.55" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="53">
         <v>46327</v>
       </c>
@@ -3510,7 +2937,7 @@
         <v>0.08</v>
       </c>
       <c r="D8" s="55">
-        <v>0.088</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="E8" s="56">
         <v>83333</v>
@@ -3526,7 +2953,7 @@
       <c r="N8" s="16"/>
       <c r="O8" s="16"/>
     </row>
-    <row r="9" ht="11.55" customHeight="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="53">
         <v>46357</v>
       </c>
@@ -3550,7 +2977,7 @@
       <c r="N9" s="16"/>
       <c r="O9" s="16"/>
     </row>
-    <row r="10" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="53">
         <v>46388</v>
       </c>
@@ -3565,7 +2992,7 @@
       <c r="I10" s="57"/>
       <c r="J10" s="57"/>
     </row>
-    <row r="11" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="53">
         <v>46419</v>
       </c>
@@ -3580,7 +3007,7 @@
       <c r="I11" s="57"/>
       <c r="J11" s="57"/>
     </row>
-    <row r="12" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="53">
         <v>46447</v>
       </c>
@@ -3595,7 +3022,7 @@
       <c r="I12" s="57"/>
       <c r="J12" s="57"/>
     </row>
-    <row r="13" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="53">
         <v>46478</v>
       </c>
@@ -3610,7 +3037,7 @@
       <c r="I13" s="57"/>
       <c r="J13" s="57"/>
     </row>
-    <row r="14" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="53">
         <v>46508</v>
       </c>
@@ -3625,7 +3052,7 @@
       <c r="I14" s="57"/>
       <c r="J14" s="57"/>
     </row>
-    <row r="15" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="53">
         <v>46539</v>
       </c>
@@ -3640,7 +3067,7 @@
       <c r="I15" s="57"/>
       <c r="J15" s="57"/>
     </row>
-    <row r="16" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="53">
         <v>46569</v>
       </c>
@@ -3655,7 +3082,7 @@
       <c r="I16" s="57"/>
       <c r="J16" s="57"/>
     </row>
-    <row r="17" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="53">
         <v>46600</v>
       </c>
@@ -3670,7 +3097,7 @@
       <c r="I17" s="57"/>
       <c r="J17" s="57"/>
     </row>
-    <row r="18" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="53">
         <v>46631</v>
       </c>
@@ -3685,7 +3112,7 @@
       <c r="I18" s="57"/>
       <c r="J18" s="57"/>
     </row>
-    <row r="19" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="53">
         <v>46661</v>
       </c>
@@ -3700,12 +3127,12 @@
       <c r="I19" s="57"/>
       <c r="J19" s="57"/>
     </row>
-    <row r="20" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="53">
         <v>46692</v>
       </c>
       <c r="C20" s="54">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="D20" s="59"/>
       <c r="E20" s="59"/>
@@ -3715,7 +3142,7 @@
       <c r="I20" s="57"/>
       <c r="J20" s="57"/>
     </row>
-    <row r="21" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="53">
         <v>46722</v>
       </c>
@@ -3730,7 +3157,7 @@
       <c r="I21" s="57"/>
       <c r="J21" s="57"/>
     </row>
-    <row r="22" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="53">
         <v>46753</v>
       </c>
@@ -3745,7 +3172,7 @@
       <c r="I22" s="57"/>
       <c r="J22" s="57"/>
     </row>
-    <row r="23" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="53">
         <v>46784</v>
       </c>
@@ -3760,7 +3187,7 @@
       <c r="I23" s="57"/>
       <c r="J23" s="57"/>
     </row>
-    <row r="24" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="53">
         <v>46813</v>
       </c>
@@ -3775,7 +3202,7 @@
       <c r="I24" s="57"/>
       <c r="J24" s="57"/>
     </row>
-    <row r="25" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="53">
         <v>46844</v>
       </c>
@@ -3790,7 +3217,7 @@
       <c r="I25" s="57"/>
       <c r="J25" s="57"/>
     </row>
-    <row r="26" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="53">
         <v>46874</v>
       </c>
@@ -3805,7 +3232,7 @@
       <c r="I26" s="57"/>
       <c r="J26" s="57"/>
     </row>
-    <row r="27" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="53">
         <v>46905</v>
       </c>
@@ -3820,7 +3247,7 @@
       <c r="I27" s="57"/>
       <c r="J27" s="57"/>
     </row>
-    <row r="28" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="53">
         <v>46935</v>
       </c>
@@ -3835,7 +3262,7 @@
       <c r="I28" s="57"/>
       <c r="J28" s="57"/>
     </row>
-    <row r="29" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="53">
         <v>46966</v>
       </c>
@@ -3850,7 +3277,7 @@
       <c r="I29" s="57"/>
       <c r="J29" s="57"/>
     </row>
-    <row r="30" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="53">
         <v>46997</v>
       </c>
@@ -3865,7 +3292,7 @@
       <c r="I30" s="57"/>
       <c r="J30" s="57"/>
     </row>
-    <row r="31" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="53">
         <v>47027</v>
       </c>
@@ -3880,7 +3307,7 @@
       <c r="I31" s="57"/>
       <c r="J31" s="57"/>
     </row>
-    <row r="32" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="53">
         <v>47058</v>
       </c>
@@ -3895,7 +3322,7 @@
       <c r="I32" s="57"/>
       <c r="J32" s="57"/>
     </row>
-    <row r="33" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="53">
         <v>47088</v>
       </c>
@@ -3910,7 +3337,7 @@
       <c r="I33" s="57"/>
       <c r="J33" s="57"/>
     </row>
-    <row r="34" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="53">
         <v>47119</v>
       </c>
@@ -3925,7 +3352,7 @@
       <c r="I34" s="57"/>
       <c r="J34" s="57"/>
     </row>
-    <row r="35" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="53">
         <v>47150</v>
       </c>
@@ -3940,12 +3367,12 @@
       <c r="I35" s="57"/>
       <c r="J35" s="57"/>
     </row>
-    <row r="36" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="53">
         <v>47178</v>
       </c>
       <c r="C36" s="54">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="D36" s="59"/>
       <c r="E36" s="59"/>
@@ -3955,12 +3382,12 @@
       <c r="I36" s="57"/>
       <c r="J36" s="57"/>
     </row>
-    <row r="37" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="53">
         <v>47209</v>
       </c>
       <c r="C37" s="54">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="D37" s="59"/>
       <c r="E37" s="59"/>
@@ -3970,12 +3397,12 @@
       <c r="I37" s="57"/>
       <c r="J37" s="57"/>
     </row>
-    <row r="38" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="53">
         <v>47239</v>
       </c>
       <c r="C38" s="54">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="D38" s="59"/>
       <c r="E38" s="59"/>
@@ -3985,7 +3412,7 @@
       <c r="I38" s="57"/>
       <c r="J38" s="57"/>
     </row>
-    <row r="39" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="53">
         <v>47270</v>
       </c>
@@ -4000,7 +3427,7 @@
       <c r="I39" s="57"/>
       <c r="J39" s="57"/>
     </row>
-    <row r="40" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="53">
         <v>47300</v>
       </c>
@@ -4015,7 +3442,7 @@
       <c r="I40" s="57"/>
       <c r="J40" s="57"/>
     </row>
-    <row r="41" ht="11.55" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:10" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="53">
         <v>47331</v>
       </c>
@@ -4030,7 +3457,7 @@
       <c r="I41" s="57"/>
       <c r="J41" s="57"/>
     </row>
-    <row r="42" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="53">
         <v>47362</v>
       </c>
@@ -4045,7 +3472,7 @@
       <c r="I42" s="57"/>
       <c r="J42" s="57"/>
     </row>
-    <row r="43" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="53">
         <v>47392</v>
       </c>
@@ -4060,7 +3487,7 @@
       <c r="I43" s="57"/>
       <c r="J43" s="57"/>
     </row>
-    <row r="44" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="53">
         <v>47423</v>
       </c>
@@ -4075,7 +3502,7 @@
       <c r="I44" s="57"/>
       <c r="J44" s="57"/>
     </row>
-    <row r="45" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="53">
         <v>47453</v>
       </c>
@@ -4090,7 +3517,7 @@
       <c r="I45" s="57"/>
       <c r="J45" s="57"/>
     </row>
-    <row r="46" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="53">
         <v>47484</v>
       </c>
@@ -4105,7 +3532,7 @@
       <c r="I46" s="57"/>
       <c r="J46" s="57"/>
     </row>
-    <row r="47" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="53">
         <v>47515</v>
       </c>
@@ -4120,7 +3547,7 @@
       <c r="I47" s="57"/>
       <c r="J47" s="57"/>
     </row>
-    <row r="48" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="53">
         <v>47543</v>
       </c>
@@ -4135,7 +3562,7 @@
       <c r="I48" s="57"/>
       <c r="J48" s="57"/>
     </row>
-    <row r="49" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="53">
         <v>47574</v>
       </c>
@@ -4150,7 +3577,7 @@
       <c r="I49" s="57"/>
       <c r="J49" s="57"/>
     </row>
-    <row r="50" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="53">
         <v>47604</v>
       </c>
@@ -4165,7 +3592,7 @@
       <c r="I50" s="57"/>
       <c r="J50" s="57"/>
     </row>
-    <row r="51" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="53">
         <v>47635</v>
       </c>
@@ -4180,7 +3607,7 @@
       <c r="I51" s="57"/>
       <c r="J51" s="57"/>
     </row>
-    <row r="52" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="53">
         <v>47665</v>
       </c>
@@ -4195,7 +3622,7 @@
       <c r="I52" s="57"/>
       <c r="J52" s="57"/>
     </row>
-    <row r="53" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="53">
         <v>47696</v>
       </c>
@@ -4210,7 +3637,7 @@
       <c r="I53" s="57"/>
       <c r="J53" s="57"/>
     </row>
-    <row r="54" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="53">
         <v>47727</v>
       </c>
@@ -4225,7 +3652,7 @@
       <c r="I54" s="57"/>
       <c r="J54" s="57"/>
     </row>
-    <row r="55" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="53">
         <v>47757</v>
       </c>
@@ -4240,7 +3667,7 @@
       <c r="I55" s="57"/>
       <c r="J55" s="57"/>
     </row>
-    <row r="56" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="53">
         <v>47788</v>
       </c>
@@ -4255,7 +3682,7 @@
       <c r="I56" s="57"/>
       <c r="J56" s="57"/>
     </row>
-    <row r="57" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="53">
         <v>47818</v>
       </c>
@@ -4270,7 +3697,7 @@
       <c r="I57" s="57"/>
       <c r="J57" s="57"/>
     </row>
-    <row r="58" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="53">
         <v>47849</v>
       </c>
@@ -4285,7 +3712,7 @@
       <c r="I58" s="57"/>
       <c r="J58" s="57"/>
     </row>
-    <row r="59" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="53">
         <v>47880</v>
       </c>
@@ -4300,7 +3727,7 @@
       <c r="I59" s="57"/>
       <c r="J59" s="57"/>
     </row>
-    <row r="60" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="53">
         <v>47908</v>
       </c>
@@ -4315,7 +3742,7 @@
       <c r="I60" s="57"/>
       <c r="J60" s="57"/>
     </row>
-    <row r="61" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="53">
         <v>47939</v>
       </c>
@@ -4330,7 +3757,7 @@
       <c r="I61" s="57"/>
       <c r="J61" s="57"/>
     </row>
-    <row r="62" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="53">
         <v>47969</v>
       </c>
@@ -4345,7 +3772,7 @@
       <c r="I62" s="57"/>
       <c r="J62" s="57"/>
     </row>
-    <row r="63" ht="14.4" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="53">
         <v>48000</v>
       </c>
@@ -4368,10 +3795,427 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B3:M19"/>
+  <sheetFormatPr defaultRowHeight="11.55" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.109375" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" customWidth="1"/>
+    <col min="5" max="5" width="22.5546875" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="23.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:13" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="60" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="60" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="L3" s="61" t="s">
+        <v>69</v>
+      </c>
+      <c r="M3" s="61" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="62">
+        <v>46204</v>
+      </c>
+      <c r="C4" s="63">
+        <v>0.06</v>
+      </c>
+      <c r="D4" s="64">
+        <v>0.9</v>
+      </c>
+      <c r="E4" s="63">
+        <v>0.04</v>
+      </c>
+      <c r="H4" s="65">
+        <v>46229</v>
+      </c>
+      <c r="I4" s="66">
+        <v>1200</v>
+      </c>
+      <c r="J4" s="67">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="K4" s="67">
+        <v>0.78</v>
+      </c>
+      <c r="L4" s="68">
+        <v>6.8</v>
+      </c>
+      <c r="M4" s="66">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="62">
+        <v>46235</v>
+      </c>
+      <c r="C5" s="63">
+        <v>0.08</v>
+      </c>
+      <c r="D5" s="64">
+        <v>0.88</v>
+      </c>
+      <c r="E5" s="63">
+        <v>0.04</v>
+      </c>
+      <c r="H5" s="65">
+        <v>46260</v>
+      </c>
+      <c r="I5" s="66">
+        <v>1450</v>
+      </c>
+      <c r="J5" s="67">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K5" s="67">
+        <v>0.75</v>
+      </c>
+      <c r="L5" s="68">
+        <v>6.6</v>
+      </c>
+      <c r="M5" s="68">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="62">
+        <v>46266</v>
+      </c>
+      <c r="C6" s="63">
+        <v>0.1</v>
+      </c>
+      <c r="D6" s="64">
+        <v>0.86</v>
+      </c>
+      <c r="E6" s="63">
+        <v>0.04</v>
+      </c>
+      <c r="H6" s="65">
+        <v>46291</v>
+      </c>
+      <c r="I6" s="66">
+        <v>1750</v>
+      </c>
+      <c r="J6" s="67">
+        <v>0.51</v>
+      </c>
+      <c r="K6" s="67">
+        <v>0.72</v>
+      </c>
+      <c r="L6" s="68">
+        <v>6.4</v>
+      </c>
+      <c r="M6" s="68">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="62">
+        <v>46296</v>
+      </c>
+      <c r="C7" s="63">
+        <v>0.12</v>
+      </c>
+      <c r="D7" s="64">
+        <v>0.84</v>
+      </c>
+      <c r="E7" s="63">
+        <v>0.04</v>
+      </c>
+      <c r="H7" s="65">
+        <v>46321</v>
+      </c>
+      <c r="I7" s="66">
+        <v>2100</v>
+      </c>
+      <c r="J7" s="67">
+        <v>0.47</v>
+      </c>
+      <c r="K7" s="67">
+        <v>0.68</v>
+      </c>
+      <c r="L7" s="68">
+        <v>6.2</v>
+      </c>
+      <c r="M7" s="68">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="62">
+        <v>46327</v>
+      </c>
+      <c r="C8" s="63">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D8" s="64">
+        <v>0.82</v>
+      </c>
+      <c r="E8" s="63">
+        <v>0.04</v>
+      </c>
+      <c r="H8" s="65">
+        <v>46352</v>
+      </c>
+      <c r="I8" s="66">
+        <v>2500</v>
+      </c>
+      <c r="J8" s="67">
+        <v>0.43</v>
+      </c>
+      <c r="K8" s="67">
+        <v>0.64</v>
+      </c>
+      <c r="L8" s="68">
+        <v>6</v>
+      </c>
+      <c r="M8" s="68">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="62">
+        <v>46357</v>
+      </c>
+      <c r="C9" s="63">
+        <v>0.16</v>
+      </c>
+      <c r="D9" s="64">
+        <v>0.8</v>
+      </c>
+      <c r="E9" s="63">
+        <v>0.04</v>
+      </c>
+      <c r="H9" s="65">
+        <v>46382</v>
+      </c>
+      <c r="I9" s="69">
+        <v>2950</v>
+      </c>
+      <c r="J9" s="70">
+        <v>0.39</v>
+      </c>
+      <c r="K9" s="70">
+        <v>0.6</v>
+      </c>
+      <c r="L9" s="61">
+        <v>5.8</v>
+      </c>
+      <c r="M9" s="61">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="62"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+    </row>
+    <row r="13" spans="2:13" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="60" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="61"/>
+      <c r="H13" s="72" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="72" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="73">
+        <v>46204</v>
+      </c>
+      <c r="C14" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="66">
+        <v>8200</v>
+      </c>
+      <c r="F14" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="67"/>
+      <c r="H14" s="74">
+        <v>46204</v>
+      </c>
+      <c r="I14" s="75" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="73">
+        <v>46235</v>
+      </c>
+      <c r="C15" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="76">
+        <v>0.01</v>
+      </c>
+      <c r="E15" s="66">
+        <v>8450</v>
+      </c>
+      <c r="F15" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="67"/>
+      <c r="H15" s="74">
+        <v>46235</v>
+      </c>
+      <c r="I15" s="75" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="73">
+        <v>46266</v>
+      </c>
+      <c r="C16" s="68" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="76">
+        <v>0.01</v>
+      </c>
+      <c r="E16" s="66">
+        <v>8750</v>
+      </c>
+      <c r="F16" s="68" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="67"/>
+      <c r="H16" s="74">
+        <v>46266</v>
+      </c>
+      <c r="I16" s="75" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="73">
+        <v>46296</v>
+      </c>
+      <c r="C17" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="76">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E17" s="66">
+        <v>9050</v>
+      </c>
+      <c r="F17" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="67"/>
+      <c r="H17" s="74">
+        <v>46296</v>
+      </c>
+      <c r="I17" s="75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="73">
+        <v>46327</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="76">
+        <v>1.9E-2</v>
+      </c>
+      <c r="E18" s="66">
+        <v>9400</v>
+      </c>
+      <c r="F18" s="68" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="67"/>
+      <c r="H18" s="74">
+        <v>46327</v>
+      </c>
+      <c r="I18" s="75" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="73">
+        <v>46357</v>
+      </c>
+      <c r="C19" s="61" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="76">
+        <v>1.9E-2</v>
+      </c>
+      <c r="E19" s="69">
+        <v>9800</v>
+      </c>
+      <c r="F19" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="70"/>
+      <c r="H19" s="74">
+        <v>46357</v>
+      </c>
+      <c r="I19" s="72" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:GH193"/>
-  <sheetFormatPr defaultRowHeight="11.55" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="11.55" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.109375" customWidth="1"/>
     <col min="3" max="4" width="9.44140625" customWidth="1"/>
@@ -4409,7 +4253,7 @@
     <col min="188" max="190" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="11.55" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="77" t="s">
         <v>88</v>
       </c>
@@ -4417,7 +4261,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" ht="11.55" customHeight="1" spans="2:190" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>58</v>
       </c>
@@ -4628,12 +4472,12 @@
       <c r="GG3" s="73"/>
       <c r="GH3" s="73"/>
     </row>
-    <row r="4" ht="11.55" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="73">
         <v>46204</v>
       </c>
       <c r="C4" s="79">
-        <v>539.5384119090506</v>
+        <v>539.53841190905064</v>
       </c>
       <c r="D4" s="79" t="e">
         <f>C4*('Product Uptake'!$M$5/'Product Uptake'!$L$5)</f>
@@ -4661,12 +4505,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="11.55" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="73">
         <v>46235</v>
       </c>
       <c r="C5" s="79">
-        <v>5259.322577313609</v>
+        <v>5259.3225773136091</v>
       </c>
       <c r="D5" s="79" t="e">
         <f>C5*('Product Uptake'!$M$5/'Product Uptake'!$L$5)</f>
@@ -4676,7 +4520,7 @@
         <v>99</v>
       </c>
       <c r="H5" s="57">
-        <v>0.901351518911394</v>
+        <v>0.90135151891139398</v>
       </c>
       <c r="I5" s="71">
         <v>0.92</v>
@@ -4691,10 +4535,10 @@
         <v>0.6</v>
       </c>
       <c r="M5" s="80">
-        <v>0.56</v>
-      </c>
-    </row>
-    <row r="6" ht="11.55" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="73">
         <v>46266</v>
       </c>
@@ -4709,7 +4553,7 @@
         <v>100</v>
       </c>
       <c r="H6" s="57">
-        <v>0.8188694670127475</v>
+        <v>0.81886946701274754</v>
       </c>
       <c r="I6" s="71">
         <v>0.83</v>
@@ -4727,7 +4571,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="7" ht="11.55" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="73">
         <v>46296</v>
       </c>
@@ -4742,7 +4586,7 @@
         <v>101</v>
       </c>
       <c r="H7" s="57">
-        <v>0.7302873968132739</v>
+        <v>0.73028739681327393</v>
       </c>
       <c r="I7" s="71">
         <v>0.77</v>
@@ -4760,7 +4604,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="8" ht="11.55" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="73">
         <v>46327</v>
       </c>
@@ -4775,7 +4619,7 @@
         <v>102</v>
       </c>
       <c r="H8" s="57">
-        <v>0.6509164769434985</v>
+        <v>0.65091647694349852</v>
       </c>
       <c r="I8" s="71">
         <v>0.7</v>
@@ -4793,7 +4637,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="9" ht="11.55" customHeight="1" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="73">
         <v>46357</v>
       </c>
@@ -4808,13 +4652,13 @@
         <v>103</v>
       </c>
       <c r="H9" s="57">
-        <v>0.5824549749858094</v>
+        <v>0.58245497498580945</v>
       </c>
       <c r="I9" s="71">
         <v>0.65</v>
       </c>
       <c r="J9" s="80">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="K9" s="80">
         <v>0.52</v>
@@ -4826,7 +4670,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="10" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="73">
         <v>46388</v>
       </c>
@@ -4837,10 +4681,10 @@
         <v>104</v>
       </c>
       <c r="H10" s="57">
-        <v>0.557878163361794</v>
-      </c>
-    </row>
-    <row r="11" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.55787816336179397</v>
+      </c>
+    </row>
+    <row r="11" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="73">
         <v>46419</v>
       </c>
@@ -4851,10 +4695,10 @@
         <v>105</v>
       </c>
       <c r="H11" s="57">
-        <v>0.5367591461398546</v>
-      </c>
-    </row>
-    <row r="12" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.53675914613985465</v>
+      </c>
+    </row>
+    <row r="12" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="73">
         <v>46447</v>
       </c>
@@ -4865,10 +4709,10 @@
         <v>106</v>
       </c>
       <c r="H12" s="57">
-        <v>0.5164894592233565</v>
-      </c>
-    </row>
-    <row r="13" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.51648945922335654</v>
+      </c>
+    </row>
+    <row r="13" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="73">
         <v>46478</v>
       </c>
@@ -4879,29 +4723,29 @@
         <v>107</v>
       </c>
       <c r="H13" s="57">
-        <v>0.4983590995890034</v>
-      </c>
-    </row>
-    <row r="14" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.49835909958900337</v>
+      </c>
+    </row>
+    <row r="14" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="73">
         <v>46508</v>
       </c>
       <c r="C14" s="79">
-        <v>24577.43744758986</v>
+        <v>24577.437447589858</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>108</v>
       </c>
       <c r="H14" s="57">
-        <v>0.48131960314016</v>
-      </c>
-    </row>
-    <row r="15" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.48131960314015998</v>
+      </c>
+    </row>
+    <row r="15" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="73">
         <v>46539</v>
       </c>
       <c r="C15" s="79">
-        <v>25250.57493014599</v>
+        <v>25250.574930145991</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>109</v>
@@ -4910,7 +4754,7 @@
         <v>0.46640327524352176</v>
       </c>
     </row>
-    <row r="16" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:190" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="73">
         <v>46569</v>
       </c>
@@ -4924,7 +4768,7 @@
         <v>0.45375317406651494</v>
       </c>
     </row>
-    <row r="17" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="73">
         <v>46600</v>
       </c>
@@ -4938,7 +4782,7 @@
         <v>0.44178850750555915</v>
       </c>
     </row>
-    <row r="18" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="73">
         <v>46631</v>
       </c>
@@ -4949,38 +4793,38 @@
         <v>112</v>
       </c>
       <c r="H18" s="57">
-        <v>0.4302469671706629</v>
-      </c>
-    </row>
-    <row r="19" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.43024696717066291</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="73">
         <v>46661</v>
       </c>
       <c r="C19" s="79">
-        <v>27723.50591838969</v>
+        <v>27723.505918389688</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>113</v>
       </c>
       <c r="H19" s="57">
-        <v>0.419644705745174</v>
-      </c>
-    </row>
-    <row r="20" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.41964470574517398</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="73">
         <v>46692</v>
       </c>
       <c r="C20" s="79">
-        <v>28278.54261980982</v>
+        <v>28278.542619809821</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>114</v>
       </c>
       <c r="H20" s="57">
-        <v>0.4086786453757704</v>
-      </c>
-    </row>
-    <row r="21" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.40867864537577042</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="73">
         <v>46722</v>
       </c>
@@ -4991,24 +4835,24 @@
         <v>115</v>
       </c>
       <c r="H21" s="57">
-        <v>0.3983849387457999</v>
-      </c>
-    </row>
-    <row r="22" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.39838493874579989</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="73">
         <v>46753</v>
       </c>
       <c r="C22" s="79">
-        <v>29542.7321240539</v>
+        <v>29542.732124053899</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>116</v>
       </c>
       <c r="H22" s="57">
-        <v>0.390417774804375</v>
-      </c>
-    </row>
-    <row r="23" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.39041777480437501</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="73">
         <v>46784</v>
       </c>
@@ -5019,10 +4863,10 @@
         <v>117</v>
       </c>
       <c r="H23" s="57">
-        <v>0.3832313803262805</v>
-      </c>
-    </row>
-    <row r="24" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.38323138032628051</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="73">
         <v>46813</v>
       </c>
@@ -5036,7 +4880,7 @@
         <v>0.3757842163848556</v>
       </c>
     </row>
-    <row r="25" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="73">
         <v>46844</v>
       </c>
@@ -5050,12 +4894,12 @@
         <v>0.37058903579461955</v>
       </c>
     </row>
-    <row r="26" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="73">
         <v>46874</v>
       </c>
       <c r="C26" s="79">
-        <v>31650.37938929695</v>
+        <v>31650.379389296952</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>120</v>
@@ -5064,7 +4908,7 @@
         <v>0.3636618718531946</v>
       </c>
     </row>
-    <row r="27" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="73">
         <v>46905</v>
       </c>
@@ -5078,7 +4922,7 @@
         <v>0.35846669126295855</v>
       </c>
     </row>
-    <row r="28" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="73">
         <v>46935</v>
       </c>
@@ -5092,7 +4936,7 @@
         <v>0.35327151067272244</v>
       </c>
     </row>
-    <row r="29" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="73">
         <v>46966</v>
       </c>
@@ -5106,21 +4950,21 @@
         <v>0.3480763300824864</v>
       </c>
     </row>
-    <row r="30" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="73">
         <v>46997</v>
       </c>
       <c r="C30" s="79">
-        <v>34098.10152128227</v>
+        <v>34098.101521282268</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>124</v>
       </c>
       <c r="H30" s="57">
-        <v>0.3428811494922503</v>
-      </c>
-    </row>
-    <row r="31" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.34288114949225029</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="73">
         <v>47027</v>
       </c>
@@ -5134,7 +4978,7 @@
         <v>0.33768596890201424</v>
       </c>
     </row>
-    <row r="32" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="73">
         <v>47058</v>
       </c>
@@ -5148,7 +4992,7 @@
         <v>0.33422277166296704</v>
       </c>
     </row>
-    <row r="33" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="73">
         <v>47088</v>
       </c>
@@ -5162,7 +5006,7 @@
         <v>0.32902759107273094</v>
       </c>
     </row>
-    <row r="34" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="73">
         <v>47119</v>
       </c>
@@ -5173,10 +5017,10 @@
         <v>128</v>
       </c>
       <c r="H34" s="57">
-        <v>0.3255643938336837</v>
-      </c>
-    </row>
-    <row r="35" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.32556439383368369</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="73">
         <v>47150</v>
       </c>
@@ -5187,24 +5031,24 @@
         <v>129</v>
       </c>
       <c r="H35" s="57">
-        <v>0.322100427131306</v>
-      </c>
-    </row>
-    <row r="36" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.32210042713130599</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="73">
         <v>47178</v>
       </c>
       <c r="C36" s="79">
-        <v>37307.01455063151</v>
+        <v>37307.014550631509</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>130</v>
       </c>
       <c r="H36" s="57">
-        <v>0.3186372298922588</v>
-      </c>
-    </row>
-    <row r="37" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.31863722989225879</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="73">
         <v>47209</v>
       </c>
@@ -5218,7 +5062,7 @@
         <v>0.31517403265321153</v>
       </c>
     </row>
-    <row r="38" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="73">
         <v>47239</v>
       </c>
@@ -5229,10 +5073,10 @@
         <v>132</v>
       </c>
       <c r="H38" s="57">
-        <v>0.3117100659508339</v>
-      </c>
-    </row>
-    <row r="39" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.31171006595083389</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="73">
         <v>47270</v>
       </c>
@@ -5246,12 +5090,12 @@
         <v>0.30824686871178664</v>
       </c>
     </row>
-    <row r="40" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="73">
         <v>47300</v>
       </c>
       <c r="C40" s="79">
-        <v>40177.80199605892</v>
+        <v>40177.801996058923</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>134</v>
@@ -5260,7 +5104,7 @@
         <v>0.30478367147273944</v>
       </c>
     </row>
-    <row r="41" ht="11.55" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" ht="11.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="73">
         <v>47331</v>
       </c>
@@ -5271,15 +5115,15 @@
         <v>135</v>
       </c>
       <c r="H41" s="57">
-        <v>0.3030516881215506</v>
-      </c>
-    </row>
-    <row r="42" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.30305168812155059</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="73">
         <v>47362</v>
       </c>
       <c r="C42" s="79">
-        <v>41230.91050471592</v>
+        <v>41230.910504715917</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>136</v>
@@ -5288,12 +5132,12 @@
         <v>0.29958849088250333</v>
       </c>
     </row>
-    <row r="43" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="73">
         <v>47392</v>
       </c>
       <c r="C43" s="79">
-        <v>41750.06402680537</v>
+        <v>41750.064026805368</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>137</v>
@@ -5302,26 +5146,26 @@
         <v>0.29785650753131454</v>
       </c>
     </row>
-    <row r="44" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="73">
         <v>47423</v>
       </c>
       <c r="C44" s="79">
-        <v>42402.03493617121</v>
+        <v>42402.034936171207</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>138</v>
       </c>
       <c r="H44" s="57">
-        <v>0.2943933102922673</v>
-      </c>
-    </row>
-    <row r="45" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.29439331029226729</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="73">
         <v>47453</v>
       </c>
       <c r="C45" s="79">
-        <v>42948.81780920555</v>
+        <v>42948.817809205553</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>139</v>
@@ -5330,26 +5174,26 @@
         <v>0.29266132694107844</v>
       </c>
     </row>
-    <row r="46" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="73">
         <v>47484</v>
       </c>
       <c r="C46" s="79">
-        <v>43107.15232725287</v>
+        <v>43107.152327252872</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>140</v>
       </c>
       <c r="H46" s="57">
-        <v>0.2909301130532201</v>
-      </c>
-    </row>
-    <row r="47" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.29093011305322009</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="73">
         <v>47515</v>
       </c>
       <c r="C47" s="79">
-        <v>43323.72661174839</v>
+        <v>43323.726611748389</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>141</v>
@@ -5358,7 +5202,7 @@
         <v>0.28746614635084244</v>
       </c>
     </row>
-    <row r="48" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="73">
         <v>47543</v>
       </c>
@@ -5369,15 +5213,15 @@
         <v>142</v>
       </c>
       <c r="H48" s="57">
-        <v>0.285734932462984</v>
-      </c>
-    </row>
-    <row r="49" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.28573493246298398</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="73">
         <v>47574</v>
       </c>
       <c r="C49" s="79">
-        <v>43452.67660587634</v>
+        <v>43452.676605876339</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>143</v>
@@ -5386,7 +5230,7 @@
         <v>0.28400294911179513</v>
       </c>
     </row>
-    <row r="50" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="73">
         <v>47604</v>
       </c>
@@ -5397,15 +5241,15 @@
         <v>144</v>
       </c>
       <c r="H50" s="57">
-        <v>0.2822709657606063</v>
-      </c>
-    </row>
-    <row r="51" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.28227096576060628</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="73">
         <v>47635</v>
       </c>
       <c r="C51" s="79">
-        <v>43609.07701202549</v>
+        <v>43609.077012025489</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>145</v>
@@ -5414,7 +5258,7 @@
         <v>0.28053975187274793</v>
       </c>
     </row>
-    <row r="52" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="73">
         <v>47665</v>
       </c>
@@ -5425,15 +5269,15 @@
         <v>146</v>
       </c>
       <c r="H52" s="57">
-        <v>0.2788077685215591</v>
-      </c>
-    </row>
-    <row r="53" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.27880776852155909</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="73">
         <v>47696</v>
       </c>
       <c r="C53" s="79">
-        <v>43695.03769421823</v>
+        <v>43695.037694218227</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>147</v>
@@ -5442,35 +5286,35 @@
         <v>0.27707578517037024</v>
       </c>
     </row>
-    <row r="54" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="73">
         <v>47727</v>
       </c>
       <c r="C54" s="79">
-        <v>43653.22830820949</v>
+        <v>43653.228308209487</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>148</v>
       </c>
       <c r="H54" s="57">
-        <v>0.2753445712825119</v>
-      </c>
-    </row>
-    <row r="55" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.27534457128251189</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="73">
         <v>47757</v>
       </c>
       <c r="C55" s="79">
-        <v>43555.4243740708</v>
+        <v>43555.424374070797</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>149</v>
       </c>
       <c r="H55" s="57">
-        <v>0.273612587931323</v>
-      </c>
-    </row>
-    <row r="56" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.27361258793132298</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="73">
         <v>47788</v>
       </c>
@@ -5481,43 +5325,43 @@
         <v>150</v>
       </c>
       <c r="H56" s="57">
-        <v>0.2718806045801342</v>
-      </c>
-    </row>
-    <row r="57" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.27188060458013419</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="73">
         <v>47818</v>
       </c>
       <c r="C57" s="79">
-        <v>43565.63924255693</v>
+        <v>43565.639242556928</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>151</v>
       </c>
       <c r="H57" s="57">
-        <v>0.2718806045801342</v>
-      </c>
-    </row>
-    <row r="58" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.27188060458013419</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="73">
         <v>47849</v>
       </c>
       <c r="C58" s="79">
-        <v>43440.26477604743</v>
+        <v>43440.264776047428</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>152</v>
       </c>
       <c r="H58" s="57">
-        <v>0.2701493906922758</v>
-      </c>
-    </row>
-    <row r="59" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.27014939069227578</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="73">
         <v>47880</v>
       </c>
       <c r="C59" s="79">
-        <v>43361.37985636941</v>
+        <v>43361.379856369407</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>153</v>
@@ -5526,7 +5370,7 @@
         <v>0.26841740734108693</v>
       </c>
     </row>
-    <row r="60" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="73">
         <v>47908</v>
       </c>
@@ -5537,10 +5381,10 @@
         <v>154</v>
       </c>
       <c r="H60" s="57">
-        <v>0.2666854239898981</v>
-      </c>
-    </row>
-    <row r="61" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.26668542398989808</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="73">
         <v>47939</v>
       </c>
@@ -5551,15 +5395,15 @@
         <v>155</v>
       </c>
       <c r="H61" s="57">
-        <v>0.2666854239898981</v>
-      </c>
-    </row>
-    <row r="62" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.26668542398989808</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="73">
         <v>47969</v>
       </c>
       <c r="C62" s="79">
-        <v>43047.85734887935</v>
+        <v>43047.857348879348</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>156</v>
@@ -5568,68 +5412,68 @@
         <v>0.26495421010203973</v>
       </c>
     </row>
-    <row r="63" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="73">
         <v>48000</v>
       </c>
       <c r="C63" s="79">
-        <v>43056.38509853063</v>
+        <v>43056.385098530627</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H63" s="57">
-        <v>0.2632222267508509</v>
-      </c>
-    </row>
-    <row r="64" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.26322222675085089</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="73">
         <v>48030</v>
       </c>
       <c r="C64" s="79">
-        <v>43110.84674156823</v>
+        <v>43110.846741568232</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>158</v>
       </c>
       <c r="H64" s="57">
-        <v>0.2632222267508509</v>
-      </c>
-    </row>
-    <row r="65" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.26322222675085089</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="73">
         <v>48061</v>
       </c>
       <c r="C65" s="79">
-        <v>43111.30243550642</v>
+        <v>43111.302435506419</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>159</v>
       </c>
       <c r="H65" s="57">
-        <v>0.261490243399662</v>
-      </c>
-    </row>
-    <row r="66" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.26149024339966198</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="73">
         <v>48092</v>
       </c>
       <c r="C66" s="79">
-        <v>43161.08417370434</v>
+        <v>43161.084173704337</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>160</v>
       </c>
       <c r="H66" s="57">
-        <v>0.261490243399662</v>
-      </c>
-    </row>
-    <row r="67" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.26149024339966198</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="73">
         <v>48122</v>
       </c>
       <c r="C67" s="79">
-        <v>43177.32344859251</v>
+        <v>43177.323448592513</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>161</v>
@@ -5638,7 +5482,7 @@
         <v>0.25975902951180363</v>
       </c>
     </row>
-    <row r="68" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="73">
         <v>48153</v>
       </c>
@@ -5649,10 +5493,10 @@
         <v>162</v>
       </c>
       <c r="H68" s="57">
-        <v>0.2580270461606148</v>
-      </c>
-    </row>
-    <row r="69" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.25802704616061478</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="73">
         <v>48183</v>
       </c>
@@ -5663,10 +5507,10 @@
         <v>163</v>
       </c>
       <c r="H69" s="57">
-        <v>0.2580270461606148</v>
-      </c>
-    </row>
-    <row r="70" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.25802704616061478</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="73">
         <v>48214</v>
       </c>
@@ -5680,7 +5524,7 @@
         <v>0.25629506280942593</v>
       </c>
     </row>
-    <row r="71" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="73">
         <v>48245</v>
       </c>
@@ -5694,7 +5538,7 @@
         <v>0.25629506280942593</v>
       </c>
     </row>
-    <row r="72" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="73">
         <v>48274</v>
       </c>
@@ -5705,10 +5549,10 @@
         <v>166</v>
       </c>
       <c r="H72" s="57">
-        <v>0.2545638489215676</v>
-      </c>
-    </row>
-    <row r="73" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.25456384892156758</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="73">
         <v>48305</v>
       </c>
@@ -5719,10 +5563,10 @@
         <v>167</v>
       </c>
       <c r="H73" s="57">
-        <v>0.2545638489215676</v>
-      </c>
-    </row>
-    <row r="74" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.25456384892156758</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="73">
         <v>48335</v>
       </c>
@@ -5736,12 +5580,12 @@
         <v>0.25283186557037873</v>
       </c>
     </row>
-    <row r="75" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="73">
         <v>48366</v>
       </c>
       <c r="C75" s="79">
-        <v>43241.01695159193</v>
+        <v>43241.016951591933</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>169</v>
@@ -5750,21 +5594,21 @@
         <v>0.25283186557037873</v>
       </c>
     </row>
-    <row r="76" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="73">
         <v>48396</v>
       </c>
       <c r="C76" s="79">
-        <v>43127.68497133806</v>
+        <v>43127.684971338058</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>170</v>
       </c>
       <c r="H76" s="57">
-        <v>0.2510998822191899</v>
-      </c>
-    </row>
-    <row r="77" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.25109988221918988</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="73">
         <v>48427</v>
       </c>
@@ -5775,15 +5619,15 @@
         <v>171</v>
       </c>
       <c r="H77" s="57">
-        <v>0.2510998822191899</v>
-      </c>
-    </row>
-    <row r="78" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.25109988221918988</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="73">
         <v>48458</v>
       </c>
       <c r="C78" s="79">
-        <v>43096.12614820737</v>
+        <v>43096.126148207368</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>172</v>
@@ -5792,7 +5636,7 @@
         <v>0.24936866833133148</v>
       </c>
     </row>
-    <row r="79" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="73">
         <v>48488</v>
       </c>
@@ -5806,12 +5650,12 @@
         <v>0.24936866833133148</v>
       </c>
     </row>
-    <row r="80" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="73">
         <v>48519</v>
       </c>
       <c r="C80" s="79">
-        <v>43054.34896480041</v>
+        <v>43054.348964800411</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>174</v>
@@ -5820,12 +5664,12 @@
         <v>0.24763668498014263</v>
       </c>
     </row>
-    <row r="81" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="73">
         <v>48549</v>
       </c>
       <c r="C81" s="79">
-        <v>43004.72988484032</v>
+        <v>43004.729884840322</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>175</v>
@@ -5834,12 +5678,12 @@
         <v>0.24763668498014263</v>
       </c>
     </row>
-    <row r="82" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="73">
         <v>48580</v>
       </c>
       <c r="C82" s="79">
-        <v>43004.72988484032</v>
+        <v>43004.729884840322</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>176</v>
@@ -5848,12 +5692,12 @@
         <v>0.24590470162895378</v>
       </c>
     </row>
-    <row r="83" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="73">
         <v>48611</v>
       </c>
       <c r="C83" s="79">
-        <v>42986.90166632028</v>
+        <v>42986.901666320278</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>177</v>
@@ -5862,12 +5706,12 @@
         <v>0.24590470162895378</v>
       </c>
     </row>
-    <row r="84" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="73">
         <v>48639</v>
       </c>
       <c r="C84" s="79">
-        <v>42986.90166632028</v>
+        <v>42986.901666320278</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>178</v>
@@ -5876,12 +5720,12 @@
         <v>0.24590470162895378</v>
       </c>
     </row>
-    <row r="85" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="73">
         <v>48670</v>
       </c>
       <c r="C85" s="79">
-        <v>42986.90166632028</v>
+        <v>42986.901666320278</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>179</v>
@@ -5890,12 +5734,12 @@
         <v>0.24417348774109537</v>
       </c>
     </row>
-    <row r="86" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="73">
         <v>48700</v>
       </c>
       <c r="C86" s="79">
-        <v>42990.88827713235</v>
+        <v>42990.888277132348</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>180</v>
@@ -5904,7 +5748,7 @@
         <v>0.24417348774109537</v>
       </c>
     </row>
-    <row r="87" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="73">
         <v>48731</v>
       </c>
@@ -5918,12 +5762,12 @@
         <v>0.24244150438990655</v>
       </c>
     </row>
-    <row r="88" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="73">
         <v>48761</v>
       </c>
       <c r="C88" s="79">
-        <v>43069.91252343484</v>
+        <v>43069.912523434839</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>182</v>
@@ -5932,12 +5776,12 @@
         <v>0.24244150438990655</v>
       </c>
     </row>
-    <row r="89" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="73">
         <v>48792</v>
       </c>
       <c r="C89" s="79">
-        <v>43070.02717106604</v>
+        <v>43070.027171066038</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>183</v>
@@ -5946,7 +5790,7 @@
         <v>0.24070952103871773</v>
       </c>
     </row>
-    <row r="90" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="73">
         <v>48823</v>
       </c>
@@ -5960,7 +5804,7 @@
         <v>0.24070952103871773</v>
       </c>
     </row>
-    <row r="91" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="73">
         <v>48853</v>
       </c>
@@ -5974,12 +5818,12 @@
         <v>0.24070952103871773</v>
       </c>
     </row>
-    <row r="92" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="73">
         <v>48884</v>
       </c>
       <c r="C92" s="79">
-        <v>43099.28331996193</v>
+        <v>43099.283319961927</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>186</v>
@@ -5988,7 +5832,7 @@
         <v>0.23897830715085933</v>
       </c>
     </row>
-    <row r="93" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="73">
         <v>48914</v>
       </c>
@@ -6002,7 +5846,7 @@
         <v>0.23897830715085933</v>
       </c>
     </row>
-    <row r="94" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="73">
         <v>48945</v>
       </c>
@@ -6016,12 +5860,12 @@
         <v>0.23724632379967048</v>
       </c>
     </row>
-    <row r="95" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="73">
         <v>48976</v>
       </c>
       <c r="C95" s="79">
-        <v>43126.29571092087</v>
+        <v>43126.295710920873</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>189</v>
@@ -6030,12 +5874,12 @@
         <v>0.23724632379967048</v>
       </c>
     </row>
-    <row r="96" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="73">
         <v>49004</v>
       </c>
       <c r="C96" s="79">
-        <v>43126.29571092087</v>
+        <v>43126.295710920873</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>190</v>
@@ -6044,12 +5888,12 @@
         <v>0.23724632379967048</v>
       </c>
     </row>
-    <row r="97" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="73">
         <v>49035</v>
       </c>
       <c r="C97" s="79">
-        <v>43126.29571092087</v>
+        <v>43126.295710920873</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>191</v>
@@ -6058,12 +5902,12 @@
         <v>0.23551434044848166</v>
       </c>
     </row>
-    <row r="98" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="73">
         <v>49065</v>
       </c>
       <c r="C98" s="79">
-        <v>43132.51471737827</v>
+        <v>43132.514717378268</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>192</v>
@@ -6072,12 +5916,12 @@
         <v>0.23551434044848166</v>
       </c>
     </row>
-    <row r="99" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="73">
         <v>49096</v>
       </c>
       <c r="C99" s="79">
-        <v>43184.98474998307</v>
+        <v>43184.984749983072</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>193</v>
@@ -6086,12 +5930,12 @@
         <v>0.23551434044848166</v>
       </c>
     </row>
-    <row r="100" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="73">
         <v>49126</v>
       </c>
       <c r="C100" s="79">
-        <v>43255.79043231832</v>
+        <v>43255.790432318317</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>194</v>
@@ -6100,12 +5944,12 @@
         <v>0.23378312656062325</v>
       </c>
     </row>
-    <row r="101" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="73">
         <v>49157</v>
       </c>
       <c r="C101" s="79">
-        <v>43255.96927956285</v>
+        <v>43255.969279562851</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>195</v>
@@ -6114,7 +5958,7 @@
         <v>0.23378312656062325</v>
       </c>
     </row>
-    <row r="102" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="73">
         <v>49188</v>
       </c>
@@ -6128,12 +5972,12 @@
         <v>0.23378312656062325</v>
       </c>
     </row>
-    <row r="103" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="73">
         <v>49218</v>
       </c>
       <c r="C103" s="79">
-        <v>43281.88069791135</v>
+        <v>43281.880697911351</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>197</v>
@@ -6142,7 +5986,7 @@
         <v>0.2320511432094344</v>
       </c>
     </row>
-    <row r="104" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="73">
         <v>49249</v>
       </c>
@@ -6156,7 +6000,7 @@
         <v>0.2320511432094344</v>
       </c>
     </row>
-    <row r="105" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="73">
         <v>49279</v>
       </c>
@@ -6170,7 +6014,7 @@
         <v>0.2320511432094344</v>
       </c>
     </row>
-    <row r="106" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="73">
         <v>49310</v>
       </c>
@@ -6184,12 +6028,12 @@
         <v>0.23031915985824558</v>
       </c>
     </row>
-    <row r="107" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="73">
         <v>49341</v>
       </c>
       <c r="C107" s="79">
-        <v>43343.74669983315</v>
+        <v>43343.746699833151</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>201</v>
@@ -6198,12 +6042,12 @@
         <v>0.23031915985824558</v>
       </c>
     </row>
-    <row r="108" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="73">
         <v>49369</v>
       </c>
       <c r="C108" s="79">
-        <v>43343.74669983315</v>
+        <v>43343.746699833151</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>202</v>
@@ -6212,12 +6056,12 @@
         <v>0.23031915985824558</v>
       </c>
     </row>
-    <row r="109" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="73">
         <v>49400</v>
       </c>
       <c r="C109" s="79">
-        <v>43343.74669983315</v>
+        <v>43343.746699833151</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>203</v>
@@ -6226,12 +6070,12 @@
         <v>0.22858794597038715</v>
       </c>
     </row>
-    <row r="110" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="73">
         <v>49430</v>
       </c>
       <c r="C110" s="79">
-        <v>43349.71145932787</v>
+        <v>43349.711459327867</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>204</v>
@@ -6240,7 +6084,7 @@
         <v>0.22858794597038715</v>
       </c>
     </row>
-    <row r="111" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="73">
         <v>49461</v>
       </c>
@@ -6254,12 +6098,12 @@
         <v>0.22858794597038715</v>
       </c>
     </row>
-    <row r="112" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="73">
         <v>49491</v>
       </c>
       <c r="C112" s="79">
-        <v>43467.94738594975</v>
+        <v>43467.947385949752</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>206</v>
@@ -6268,12 +6112,12 @@
         <v>0.22685596261919833</v>
       </c>
     </row>
-    <row r="113" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="73">
         <v>49522</v>
       </c>
       <c r="C113" s="79">
-        <v>43468.11892151692</v>
+        <v>43468.118921516922</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>207</v>
@@ -6282,12 +6126,12 @@
         <v>0.22685596261919833</v>
       </c>
     </row>
-    <row r="114" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="73">
         <v>49553</v>
       </c>
       <c r="C114" s="79">
-        <v>43486.8581189931</v>
+        <v>43486.858118993099</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>208</v>
@@ -6296,12 +6140,12 @@
         <v>0.22685596261919833</v>
       </c>
     </row>
-    <row r="115" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="73">
         <v>49583</v>
       </c>
       <c r="C115" s="79">
-        <v>43492.97102284129</v>
+        <v>43492.971022841288</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>209</v>
@@ -6310,7 +6154,7 @@
         <v>0.22512397926800948</v>
       </c>
     </row>
-    <row r="116" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="73">
         <v>49614</v>
       </c>
@@ -6324,12 +6168,12 @@
         <v>0.22512397926800948</v>
       </c>
     </row>
-    <row r="117" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="73">
         <v>49644</v>
       </c>
       <c r="C117" s="79">
-        <v>43541.62474734727</v>
+        <v>43541.624747347269</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>211</v>
@@ -6338,12 +6182,12 @@
         <v>0.22512397926800948</v>
       </c>
     </row>
-    <row r="118" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="73">
         <v>49675</v>
       </c>
       <c r="C118" s="79">
-        <v>43541.62474734727</v>
+        <v>43541.624747347269</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>212</v>
@@ -6352,12 +6196,12 @@
         <v>0.2233927653801511</v>
       </c>
     </row>
-    <row r="119" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="73">
         <v>49706</v>
       </c>
       <c r="C119" s="79">
-        <v>43552.30780354599</v>
+        <v>43552.307803545991</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>213</v>
@@ -6366,12 +6210,12 @@
         <v>0.2233927653801511</v>
       </c>
     </row>
-    <row r="120" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="73">
         <v>49735</v>
       </c>
       <c r="C120" s="79">
-        <v>43552.30780354599</v>
+        <v>43552.307803545991</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>214</v>
@@ -6380,12 +6224,12 @@
         <v>0.2233927653801511</v>
       </c>
     </row>
-    <row r="121" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B121" s="73">
         <v>49766</v>
       </c>
       <c r="C121" s="79">
-        <v>43552.30780354599</v>
+        <v>43552.307803545991</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>215</v>
@@ -6394,7 +6238,7 @@
         <v>0.22166078202896228</v>
       </c>
     </row>
-    <row r="122" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="73">
         <v>49796</v>
       </c>
@@ -6408,12 +6252,12 @@
         <v>0.22166078202896228</v>
       </c>
     </row>
-    <row r="123" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="73">
         <v>49827</v>
       </c>
       <c r="C123" s="79">
-        <v>43606.58813851299</v>
+        <v>43606.588138512991</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>217</v>
@@ -6422,12 +6266,12 @@
         <v>0.22166078202896228</v>
       </c>
     </row>
-    <row r="124" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="73">
         <v>49857</v>
       </c>
       <c r="C124" s="79">
-        <v>43672.07491792083</v>
+        <v>43672.074917920829</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>218</v>
@@ -6436,12 +6280,12 @@
         <v>0.2199287986777734</v>
       </c>
     </row>
-    <row r="125" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B125" s="73">
         <v>49888</v>
       </c>
       <c r="C125" s="79">
-        <v>43672.24033021068</v>
+        <v>43672.240330210683</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>219</v>
@@ -6450,7 +6294,7 @@
         <v>0.2199287986777734</v>
       </c>
     </row>
-    <row r="126" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="73">
         <v>49919</v>
       </c>
@@ -6464,12 +6308,12 @@
         <v>0.2199287986777734</v>
       </c>
     </row>
-    <row r="127" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B127" s="73">
         <v>49949</v>
       </c>
       <c r="C127" s="79">
-        <v>43696.20529010612</v>
+        <v>43696.205290106118</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>221</v>
@@ -6478,7 +6322,7 @@
         <v>0.21819758478991505</v>
       </c>
     </row>
-    <row r="128" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B128" s="73">
         <v>49980</v>
       </c>
@@ -6492,12 +6336,12 @@
         <v>0.21819758478991505</v>
       </c>
     </row>
-    <row r="129" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B129" s="73">
         <v>50010</v>
       </c>
       <c r="C129" s="79">
-        <v>43743.12223050208</v>
+        <v>43743.122230502078</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>223</v>
@@ -6506,12 +6350,12 @@
         <v>0.21819758478991505</v>
       </c>
     </row>
-    <row r="130" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B130" s="73">
         <v>50041</v>
       </c>
       <c r="C130" s="79">
-        <v>43743.12223050208</v>
+        <v>43743.122230502078</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>224</v>
@@ -6520,12 +6364,12 @@
         <v>0.2164656014387262</v>
       </c>
     </row>
-    <row r="131" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B131" s="73">
         <v>50072</v>
       </c>
       <c r="C131" s="79">
-        <v>43753.42393537692</v>
+        <v>43753.423935376923</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>225</v>
@@ -6534,12 +6378,12 @@
         <v>0.2164656014387262</v>
       </c>
     </row>
-    <row r="132" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B132" s="73">
         <v>50100</v>
       </c>
       <c r="C132" s="79">
-        <v>43753.42393537692</v>
+        <v>43753.423935376923</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>226</v>
@@ -6548,12 +6392,12 @@
         <v>0.2164656014387262</v>
       </c>
     </row>
-    <row r="133" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B133" s="73">
         <v>50131</v>
       </c>
       <c r="C133" s="79">
-        <v>43753.42393537692</v>
+        <v>43753.423935376923</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>227</v>
@@ -6562,12 +6406,12 @@
         <v>0.21473361808753735</v>
       </c>
     </row>
-    <row r="134" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B134" s="73">
         <v>50161</v>
       </c>
       <c r="C134" s="79">
-        <v>43758.99492786032</v>
+        <v>43758.994927860324</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>228</v>
@@ -6576,12 +6420,12 @@
         <v>0.21473361808753735</v>
       </c>
     </row>
-    <row r="135" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B135" s="73">
         <v>50192</v>
       </c>
       <c r="C135" s="79">
-        <v>43805.99763789895</v>
+        <v>43805.997637898952</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>229</v>
@@ -6590,12 +6434,12 @@
         <v>0.21473361808753735</v>
       </c>
     </row>
-    <row r="136" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B136" s="73">
         <v>50222</v>
       </c>
       <c r="C136" s="79">
-        <v>43869.42544212688</v>
+        <v>43869.425442126878</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>230</v>
@@ -6604,12 +6448,12 @@
         <v>0.21473361808753735</v>
       </c>
     </row>
-    <row r="137" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B137" s="73">
         <v>50253</v>
       </c>
       <c r="C137" s="79">
-        <v>43869.58565367542</v>
+        <v>43869.585653675422</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>231</v>
@@ -6618,7 +6462,7 @@
         <v>0.21300240419967897</v>
       </c>
     </row>
-    <row r="138" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B138" s="73">
         <v>50284</v>
       </c>
@@ -6632,12 +6476,12 @@
         <v>0.21300240419967897</v>
       </c>
     </row>
-    <row r="139" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B139" s="73">
         <v>50314</v>
       </c>
       <c r="C139" s="79">
-        <v>43892.79712930947</v>
+        <v>43892.797129309467</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>233</v>
@@ -6646,7 +6490,7 @@
         <v>0.21300240419967897</v>
       </c>
     </row>
-    <row r="140" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="73">
         <v>50345</v>
       </c>
@@ -6660,7 +6504,7 @@
         <v>0.21127042084849015</v>
       </c>
     </row>
-    <row r="141" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="73">
         <v>50375</v>
       </c>
@@ -6674,7 +6518,7 @@
         <v>0.21127042084849015</v>
       </c>
     </row>
-    <row r="142" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B142" s="73">
         <v>50406</v>
       </c>
@@ -6688,7 +6532,7 @@
         <v>0.21127042084849015</v>
       </c>
     </row>
-    <row r="143" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B143" s="73">
         <v>50437</v>
       </c>
@@ -6702,7 +6546,7 @@
         <v>0.20953843749730128</v>
       </c>
     </row>
-    <row r="144" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B144" s="73">
         <v>50465</v>
       </c>
@@ -6716,7 +6560,7 @@
         <v>0.20953843749730128</v>
       </c>
     </row>
-    <row r="145" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B145" s="73">
         <v>50496</v>
       </c>
@@ -6730,12 +6574,12 @@
         <v>0.20953843749730128</v>
       </c>
     </row>
-    <row r="146" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B146" s="73">
         <v>50526</v>
       </c>
       <c r="C146" s="79">
-        <v>43953.63230343142</v>
+        <v>43953.632303431419</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>240</v>
@@ -6744,12 +6588,12 @@
         <v>0.20953843749730128</v>
       </c>
     </row>
-    <row r="147" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B147" s="73">
         <v>50557</v>
       </c>
       <c r="C147" s="79">
-        <v>43999.32349575703</v>
+        <v>43999.323495757031</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>241</v>
@@ -6758,12 +6602,12 @@
         <v>0.2078072236094429</v>
       </c>
     </row>
-    <row r="148" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B148" s="73">
         <v>50587</v>
       </c>
       <c r="C148" s="79">
-        <v>44060.9814724862</v>
+        <v>44060.981472486201</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>242</v>
@@ -6772,12 +6616,12 @@
         <v>0.2078072236094429</v>
       </c>
     </row>
-    <row r="149" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B149" s="73">
         <v>50618</v>
       </c>
       <c r="C149" s="79">
-        <v>44061.13721364817</v>
+        <v>44061.137213648173</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>243</v>
@@ -6786,7 +6630,7 @@
         <v>0.2078072236094429</v>
       </c>
     </row>
-    <row r="150" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B150" s="73">
         <v>50649</v>
       </c>
@@ -6800,12 +6644,12 @@
         <v>0.20607524025825408</v>
       </c>
     </row>
-    <row r="151" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B151" s="73">
         <v>50679</v>
       </c>
       <c r="C151" s="79">
-        <v>44083.70101893697</v>
+        <v>44083.701018936968</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>245</v>
@@ -6814,12 +6658,12 @@
         <v>0.20607524025825408</v>
       </c>
     </row>
-    <row r="152" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B152" s="73">
         <v>50710</v>
       </c>
       <c r="C152" s="79">
-        <v>44100.87974104536</v>
+        <v>44100.879741045363</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>246</v>
@@ -6828,7 +6672,7 @@
         <v>0.20607524025825408</v>
       </c>
     </row>
-    <row r="153" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B153" s="73">
         <v>50740</v>
       </c>
@@ -6842,7 +6686,7 @@
         <v>0.20607524025825408</v>
       </c>
     </row>
-    <row r="154" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="73">
         <v>50771</v>
       </c>
@@ -6856,12 +6700,12 @@
         <v>0.20434325690706523</v>
       </c>
     </row>
-    <row r="155" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B155" s="73">
         <v>50802</v>
       </c>
       <c r="C155" s="79">
-        <v>44137.57427290492</v>
+        <v>44137.574272904923</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>249</v>
@@ -6870,12 +6714,12 @@
         <v>0.20434325690706523</v>
       </c>
     </row>
-    <row r="156" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B156" s="73">
         <v>50830</v>
       </c>
       <c r="C156" s="79">
-        <v>44137.57427290492</v>
+        <v>44137.574272904923</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>250</v>
@@ -6884,12 +6728,12 @@
         <v>0.20434325690706523</v>
       </c>
     </row>
-    <row r="157" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B157" s="73">
         <v>50861</v>
       </c>
       <c r="C157" s="79">
-        <v>44137.57427290492</v>
+        <v>44137.574272904923</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>251</v>
@@ -6898,12 +6742,12 @@
         <v>0.20261204301920682</v>
       </c>
     </row>
-    <row r="158" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B158" s="73">
         <v>50891</v>
       </c>
       <c r="C158" s="79">
-        <v>44141.91603693603</v>
+        <v>44141.916036936032</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>252</v>
@@ -6912,12 +6756,12 @@
         <v>0.20261204301920682</v>
       </c>
     </row>
-    <row r="159" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B159" s="73">
         <v>50922</v>
       </c>
       <c r="C159" s="79">
-        <v>44178.54769214255</v>
+        <v>44178.547692142551</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>253</v>
@@ -6926,7 +6770,7 @@
         <v>0.20261204301920682</v>
       </c>
     </row>
-    <row r="160" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B160" s="73">
         <v>50952</v>
       </c>
@@ -6940,7 +6784,7 @@
         <v>0.20261204301920682</v>
       </c>
     </row>
-    <row r="161" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B161" s="73">
         <v>50983</v>
       </c>
@@ -6954,12 +6798,12 @@
         <v>0.20088005966801797</v>
       </c>
     </row>
-    <row r="162" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B162" s="73">
         <v>51014</v>
       </c>
       <c r="C162" s="79">
-        <v>44241.74544907699</v>
+        <v>44241.745449076989</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>256</v>
@@ -6968,12 +6812,12 @@
         <v>0.20088005966801797</v>
       </c>
     </row>
-    <row r="163" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B163" s="73">
         <v>51044</v>
       </c>
       <c r="C163" s="79">
-        <v>44246.19504777031</v>
+        <v>44246.195047770307</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>257</v>
@@ -6982,12 +6826,12 @@
         <v>0.20088005966801797</v>
       </c>
     </row>
-    <row r="164" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B164" s="73">
         <v>51075</v>
       </c>
       <c r="C164" s="79">
-        <v>44259.96761515437</v>
+        <v>44259.967615154368</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>258</v>
@@ -6996,12 +6840,12 @@
         <v>0.20088005966801797</v>
       </c>
     </row>
-    <row r="165" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B165" s="73">
         <v>51105</v>
       </c>
       <c r="C165" s="79">
-        <v>44281.61022104362</v>
+        <v>44281.610221043622</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>259</v>
@@ -7010,12 +6854,12 @@
         <v>0.19914807631682915</v>
       </c>
     </row>
-    <row r="166" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B166" s="73">
         <v>51136</v>
       </c>
       <c r="C166" s="79">
-        <v>44281.61022104362</v>
+        <v>44281.610221043622</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>260</v>
@@ -7024,12 +6868,12 @@
         <v>0.19914807631682915</v>
       </c>
     </row>
-    <row r="167" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="73">
         <v>51167</v>
       </c>
       <c r="C167" s="79">
-        <v>44289.38644558158</v>
+        <v>44289.386445581578</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>261</v>
@@ -7038,12 +6882,12 @@
         <v>0.19914807631682915</v>
       </c>
     </row>
-    <row r="168" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B168" s="73">
         <v>51196</v>
       </c>
       <c r="C168" s="79">
-        <v>44289.38644558158</v>
+        <v>44289.386445581578</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>262</v>
@@ -7052,12 +6896,12 @@
         <v>0.19914807631682915</v>
       </c>
     </row>
-    <row r="169" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B169" s="73">
         <v>51227</v>
       </c>
       <c r="C169" s="79">
-        <v>44289.38644558158</v>
+        <v>44289.386445581578</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>263</v>
@@ -7066,12 +6910,12 @@
         <v>0.19741686242897075</v>
       </c>
     </row>
-    <row r="170" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B170" s="73">
         <v>51257</v>
       </c>
       <c r="C170" s="79">
-        <v>44293.60695989818</v>
+        <v>44293.606959898178</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>264</v>
@@ -7080,7 +6924,7 @@
         <v>0.19741686242897075</v>
       </c>
     </row>
-    <row r="171" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B171" s="73">
         <v>51288</v>
       </c>
@@ -7094,12 +6938,12 @@
         <v>0.19741686242897075</v>
       </c>
     </row>
-    <row r="172" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B172" s="73">
         <v>51318</v>
       </c>
       <c r="C172" s="79">
-        <v>44377.26773808808</v>
+        <v>44377.267738088078</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>266</v>
@@ -7108,12 +6952,12 @@
         <v>0.19741686242897075</v>
       </c>
     </row>
-    <row r="173" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B173" s="73">
         <v>51349</v>
       </c>
       <c r="C173" s="79">
-        <v>44377.389112356</v>
+        <v>44377.389112356002</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>267</v>
@@ -7122,7 +6966,7 @@
         <v>0.19568487907778193</v>
       </c>
     </row>
-    <row r="174" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B174" s="73">
         <v>51380</v>
       </c>
@@ -7136,7 +6980,7 @@
         <v>0.19568487907778193</v>
       </c>
     </row>
-    <row r="175" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B175" s="73">
         <v>51410</v>
       </c>
@@ -7150,12 +6994,12 @@
         <v>0.19568487907778193</v>
       </c>
     </row>
-    <row r="176" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B176" s="73">
         <v>51441</v>
       </c>
       <c r="C176" s="79">
-        <v>44408.36178590864</v>
+        <v>44408.361785908637</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>270</v>
@@ -7164,12 +7008,12 @@
         <v>0.19568487907778193</v>
       </c>
     </row>
-    <row r="177" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B177" s="73">
         <v>51471</v>
       </c>
       <c r="C177" s="79">
-        <v>44429.39999234956</v>
+        <v>44429.399992349558</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>271</v>
@@ -7178,12 +7022,12 @@
         <v>0.19395289572659308</v>
       </c>
     </row>
-    <row r="178" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B178" s="73">
         <v>51502</v>
       </c>
       <c r="C178" s="79">
-        <v>44429.39999234956</v>
+        <v>44429.399992349558</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>272</v>
@@ -7192,12 +7036,12 @@
         <v>0.19395289572659308</v>
       </c>
     </row>
-    <row r="179" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B179" s="73">
         <v>51533</v>
       </c>
       <c r="C179" s="79">
-        <v>44436.95905515363</v>
+        <v>44436.959055153631</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>273</v>
@@ -7206,12 +7050,12 @@
         <v>0.19395289572659308</v>
       </c>
     </row>
-    <row r="180" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B180" s="73">
         <v>51561</v>
       </c>
       <c r="C180" s="79">
-        <v>44436.95905515363</v>
+        <v>44436.959055153631</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>274</v>
@@ -7220,12 +7064,12 @@
         <v>0.19395289572659308</v>
       </c>
     </row>
-    <row r="181" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B181" s="73">
         <v>51592</v>
       </c>
       <c r="C181" s="79">
-        <v>44436.95905515363</v>
+        <v>44436.959055153631</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>275</v>
@@ -7234,7 +7078,7 @@
         <v>0.1922216818387347</v>
       </c>
     </row>
-    <row r="182" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B182" s="73">
         <v>51622</v>
       </c>
@@ -7248,12 +7092,12 @@
         <v>0.1922216818387347</v>
       </c>
     </row>
-    <row r="183" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B183" s="73">
         <v>51653</v>
       </c>
       <c r="C183" s="79">
-        <v>44475.77677044406</v>
+        <v>44475.776770444063</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>277</v>
@@ -7262,12 +7106,12 @@
         <v>0.1922216818387347</v>
       </c>
     </row>
-    <row r="184" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B184" s="73">
         <v>51683</v>
       </c>
       <c r="C184" s="79">
-        <v>44522.60859563244</v>
+        <v>44522.608595632439</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>278</v>
@@ -7276,7 +7120,7 @@
         <v>0.1922216818387347</v>
       </c>
     </row>
-    <row r="185" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B185" s="73">
         <v>51714</v>
       </c>
@@ -7290,12 +7134,12 @@
         <v>0.1922216818387347</v>
       </c>
     </row>
-    <row r="186" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B186" s="73">
         <v>51745</v>
       </c>
       <c r="C186" s="79">
-        <v>44535.64955092764</v>
+        <v>44535.649550927643</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>280</v>
@@ -7304,7 +7148,7 @@
         <v>0.19048969848754585</v>
       </c>
     </row>
-    <row r="187" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B187" s="73">
         <v>51775</v>
       </c>
@@ -7318,12 +7162,12 @@
         <v>0.19048969848754585</v>
       </c>
     </row>
-    <row r="188" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B188" s="73">
         <v>51806</v>
       </c>
       <c r="C188" s="79">
-        <v>44552.91300777181</v>
+        <v>44552.913007771807</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>282</v>
@@ -7332,7 +7176,7 @@
         <v>0.19048969848754585</v>
       </c>
     </row>
-    <row r="189" ht="14.4" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B189" s="73">
         <v>51836</v>
       </c>
@@ -7346,7 +7190,7 @@
         <v>0.19048969848754585</v>
       </c>
     </row>
-    <row r="190" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G190" s="2" t="s">
         <v>284</v>
       </c>
@@ -7354,7 +7198,7 @@
         <v>0.188757715136357</v>
       </c>
     </row>
-    <row r="191" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G191" s="2" t="s">
         <v>285</v>
       </c>
@@ -7362,7 +7206,7 @@
         <v>0.188757715136357</v>
       </c>
     </row>
-    <row r="192" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G192" s="2" t="s">
         <v>286</v>
       </c>
@@ -7370,7 +7214,7 @@
         <v>0.188757715136357</v>
       </c>
     </row>
-    <row r="193" ht="14.4" customHeight="1" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="7:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G193" s="2" t="s">
         <v>287</v>
       </c>
@@ -7378,615 +7222,776 @@
         <v>0.188757715136357</v>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="B3:H10"/>
+  <sheetFormatPr defaultRowHeight="11.55" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="60" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>289</v>
+      </c>
+      <c r="D3" s="60" t="s">
+        <v>290</v>
+      </c>
+      <c r="E3" s="60" t="s">
+        <v>291</v>
+      </c>
+      <c r="F3" s="60" t="s">
+        <v>292</v>
+      </c>
+      <c r="G3" s="60" t="s">
+        <v>293</v>
+      </c>
+      <c r="H3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="81" t="s">
+        <v>295</v>
+      </c>
+      <c r="C4" s="82">
+        <v>1.6E-2</v>
+      </c>
+      <c r="D4" s="82">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="E4" s="82">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F4" s="83">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="G4" s="81" t="s">
+        <v>296</v>
+      </c>
+      <c r="H4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="81" t="s">
+        <v>298</v>
+      </c>
+      <c r="C5" s="82">
+        <v>0.80600000000000005</v>
+      </c>
+      <c r="D5" s="82">
+        <v>0.80700000000000005</v>
+      </c>
+      <c r="E5" s="82">
+        <v>0.80800000000000005</v>
+      </c>
+      <c r="F5" s="83">
+        <v>0.81</v>
+      </c>
+      <c r="G5" s="81" t="s">
+        <v>299</v>
+      </c>
+      <c r="H5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="81" t="s">
+        <v>300</v>
+      </c>
+      <c r="C6" s="82">
+        <v>0.80700000000000005</v>
+      </c>
+      <c r="D6" s="82">
+        <v>0.80800000000000005</v>
+      </c>
+      <c r="E6" s="82">
+        <v>0.81100000000000005</v>
+      </c>
+      <c r="F6" s="83">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="G6" s="81" t="s">
+        <v>296</v>
+      </c>
+      <c r="H6" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="81" t="s">
+        <v>301</v>
+      </c>
+      <c r="C7" s="81" t="s">
+        <v>302</v>
+      </c>
+      <c r="D7" s="81">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E7" s="81">
+        <v>7.8</v>
+      </c>
+      <c r="F7" s="84">
+        <v>7.3</v>
+      </c>
+      <c r="G7" s="81" t="s">
+        <v>299</v>
+      </c>
+      <c r="H7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="81" t="s">
+        <v>303</v>
+      </c>
+      <c r="C8" s="63">
+        <v>0.84</v>
+      </c>
+      <c r="D8" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="63">
+        <v>0.83</v>
+      </c>
+      <c r="G8" s="81" t="s">
+        <v>299</v>
+      </c>
+      <c r="H8" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="81"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="81"/>
+    </row>
+    <row r="10" spans="2:8" ht="22.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.05" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+    <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="93" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="94" t="s">
         <v>305</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-    </row>
-    <row r="3" ht="34.05" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="87" t="s">
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+    </row>
+    <row r="3" spans="1:7" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="85" t="s">
         <v>306</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="85" t="s">
         <v>307</v>
       </c>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="85" t="s">
         <v>308</v>
       </c>
-      <c r="E3" s="87" t="s">
+      <c r="E3" s="85" t="s">
         <v>309</v>
       </c>
-      <c r="F3" s="87" t="s">
+      <c r="F3" s="85" t="s">
         <v>310</v>
       </c>
-      <c r="G3" s="87" t="s">
+      <c r="G3" s="85" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="4" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="88">
+    <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="86">
         <v>45658</v>
       </c>
-      <c r="B4" s="89">
+      <c r="B4" s="87">
         <v>0.9</v>
       </c>
-      <c r="C4" s="90">
+      <c r="C4" s="88">
         <v>0.46</v>
       </c>
-      <c r="D4" s="90">
+      <c r="D4" s="88">
         <v>0.18</v>
       </c>
-      <c r="E4" s="90">
+      <c r="E4" s="88">
         <v>0.24</v>
       </c>
-      <c r="F4" s="90">
+      <c r="F4" s="88">
         <v>0.12</v>
       </c>
-      <c r="G4" s="90">
+      <c r="G4" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="88">
+    <row r="5" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="86">
         <v>45689</v>
       </c>
-      <c r="B5" s="89">
+      <c r="B5" s="87">
         <v>0.91</v>
       </c>
-      <c r="C5" s="90">
-        <v>0.4567</v>
-      </c>
-      <c r="D5" s="90">
+      <c r="C5" s="88">
+        <v>0.45669999999999999</v>
+      </c>
+      <c r="D5" s="88">
         <v>0.18</v>
       </c>
-      <c r="E5" s="90">
+      <c r="E5" s="88">
         <v>0.24</v>
       </c>
-      <c r="F5" s="90">
-        <v>0.1233</v>
-      </c>
-      <c r="G5" s="90">
+      <c r="F5" s="88">
+        <v>0.12330000000000001</v>
+      </c>
+      <c r="G5" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="88">
+    <row r="6" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="86">
         <v>45717</v>
       </c>
-      <c r="B6" s="89">
+      <c r="B6" s="87">
         <v>0.92</v>
       </c>
-      <c r="C6" s="90">
-        <v>0.4533</v>
-      </c>
-      <c r="D6" s="90">
+      <c r="C6" s="88">
+        <v>0.45329999999999998</v>
+      </c>
+      <c r="D6" s="88">
         <v>0.18</v>
       </c>
-      <c r="E6" s="90">
+      <c r="E6" s="88">
         <v>0.24</v>
       </c>
-      <c r="F6" s="90">
-        <v>0.1267</v>
-      </c>
-      <c r="G6" s="90">
+      <c r="F6" s="88">
+        <v>0.12670000000000001</v>
+      </c>
+      <c r="G6" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="88">
+    <row r="7" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="86">
         <v>45748</v>
       </c>
-      <c r="B7" s="89">
+      <c r="B7" s="87">
         <v>0.93</v>
       </c>
-      <c r="C7" s="90">
+      <c r="C7" s="88">
         <v>0.45</v>
       </c>
-      <c r="D7" s="90">
+      <c r="D7" s="88">
         <v>0.18</v>
       </c>
-      <c r="E7" s="90">
+      <c r="E7" s="88">
         <v>0.24</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="88">
         <v>0.13</v>
       </c>
-      <c r="G7" s="90">
+      <c r="G7" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="88">
+    <row r="8" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="86">
         <v>45778</v>
       </c>
-      <c r="B8" s="89">
+      <c r="B8" s="87">
         <v>0.94</v>
       </c>
-      <c r="C8" s="90">
+      <c r="C8" s="88">
         <v>0.44670000000000004</v>
       </c>
-      <c r="D8" s="90">
+      <c r="D8" s="88">
         <v>0.17670000000000002</v>
       </c>
-      <c r="E8" s="90">
-        <v>0.2433</v>
-      </c>
-      <c r="F8" s="90">
+      <c r="E8" s="88">
+        <v>0.24329999999999999</v>
+      </c>
+      <c r="F8" s="88">
         <v>0.1333</v>
       </c>
-      <c r="G8" s="90">
+      <c r="G8" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="88">
+    <row r="9" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="86">
         <v>45809</v>
       </c>
-      <c r="B9" s="89">
+      <c r="B9" s="87">
         <v>0.95</v>
       </c>
-      <c r="C9" s="90">
+      <c r="C9" s="88">
         <v>0.44329999999999997</v>
       </c>
-      <c r="D9" s="90">
+      <c r="D9" s="88">
         <v>0.17329999999999998</v>
       </c>
-      <c r="E9" s="90">
+      <c r="E9" s="88">
         <v>0.24670000000000003</v>
       </c>
-      <c r="F9" s="90">
-        <v>0.1367</v>
-      </c>
-      <c r="G9" s="90">
+      <c r="F9" s="88">
+        <v>0.13669999999999999</v>
+      </c>
+      <c r="G9" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="88">
+    <row r="10" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="86">
         <v>45839</v>
       </c>
-      <c r="B10" s="89">
+      <c r="B10" s="87">
         <v>0.96</v>
       </c>
-      <c r="C10" s="90">
+      <c r="C10" s="88">
         <v>0.44</v>
       </c>
-      <c r="D10" s="90">
+      <c r="D10" s="88">
         <v>0.17</v>
       </c>
-      <c r="E10" s="90">
+      <c r="E10" s="88">
         <v>0.25</v>
       </c>
-      <c r="F10" s="90">
-        <v>0.14</v>
-      </c>
-      <c r="G10" s="90">
+      <c r="F10" s="88">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G10" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="88">
+    <row r="11" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="86">
         <v>45870</v>
       </c>
-      <c r="B11" s="89">
+      <c r="B11" s="87">
         <v>0.97</v>
       </c>
-      <c r="C11" s="90">
+      <c r="C11" s="88">
         <v>0.43670000000000003</v>
       </c>
-      <c r="D11" s="90">
+      <c r="D11" s="88">
         <v>0.17</v>
       </c>
-      <c r="E11" s="90">
+      <c r="E11" s="88">
         <v>0.25</v>
       </c>
-      <c r="F11" s="90">
-        <v>0.1433</v>
-      </c>
-      <c r="G11" s="90">
+      <c r="F11" s="88">
+        <v>0.14330000000000001</v>
+      </c>
+      <c r="G11" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="88">
+    <row r="12" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="86">
         <v>45901</v>
       </c>
-      <c r="B12" s="89">
+      <c r="B12" s="87">
         <v>0.98</v>
       </c>
-      <c r="C12" s="90">
+      <c r="C12" s="88">
         <v>0.43329999999999996</v>
       </c>
-      <c r="D12" s="90">
+      <c r="D12" s="88">
         <v>0.17</v>
       </c>
-      <c r="E12" s="90">
+      <c r="E12" s="88">
         <v>0.25</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="88">
         <v>0.1467</v>
       </c>
-      <c r="G12" s="90">
+      <c r="G12" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="88">
+    <row r="13" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="86">
         <v>45931</v>
       </c>
-      <c r="B13" s="89">
+      <c r="B13" s="87">
         <v>0.99</v>
       </c>
-      <c r="C13" s="90">
+      <c r="C13" s="88">
         <v>0.43</v>
       </c>
-      <c r="D13" s="90">
+      <c r="D13" s="88">
         <v>0.17</v>
       </c>
-      <c r="E13" s="90">
+      <c r="E13" s="88">
         <v>0.25</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="88">
         <v>0.15</v>
       </c>
-      <c r="G13" s="90">
+      <c r="G13" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="88">
+    <row r="14" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="86">
         <v>45962</v>
       </c>
-      <c r="B14" s="89">
+      <c r="B14" s="87">
         <v>1</v>
       </c>
-      <c r="C14" s="90">
-        <v>0.4267</v>
-      </c>
-      <c r="D14" s="90">
+      <c r="C14" s="88">
+        <v>0.42670000000000002</v>
+      </c>
+      <c r="D14" s="88">
         <v>0.16670000000000001</v>
       </c>
-      <c r="E14" s="90">
+      <c r="E14" s="88">
         <v>0.25329999999999997</v>
       </c>
-      <c r="F14" s="90">
-        <v>0.1533</v>
-      </c>
-      <c r="G14" s="90">
+      <c r="F14" s="88">
+        <v>0.15329999999999999</v>
+      </c>
+      <c r="G14" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="88">
+    <row r="15" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="86">
         <v>45992</v>
       </c>
-      <c r="B15" s="89">
+      <c r="B15" s="87">
         <v>1.01</v>
       </c>
-      <c r="C15" s="90">
-        <v>0.4233</v>
-      </c>
-      <c r="D15" s="90">
+      <c r="C15" s="88">
+        <v>0.42330000000000001</v>
+      </c>
+      <c r="D15" s="88">
         <v>0.16329999999999997</v>
       </c>
-      <c r="E15" s="90">
+      <c r="E15" s="88">
         <v>0.25670000000000004</v>
       </c>
-      <c r="F15" s="90">
-        <v>0.1567</v>
-      </c>
-      <c r="G15" s="90">
+      <c r="F15" s="88">
+        <v>0.15670000000000001</v>
+      </c>
+      <c r="G15" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="88">
+    <row r="16" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="86">
         <v>46023</v>
       </c>
-      <c r="B16" s="89">
+      <c r="B16" s="87">
         <v>1.02</v>
       </c>
-      <c r="C16" s="90">
+      <c r="C16" s="88">
         <v>0.42</v>
       </c>
-      <c r="D16" s="90">
+      <c r="D16" s="88">
         <v>0.16</v>
       </c>
-      <c r="E16" s="90">
+      <c r="E16" s="88">
         <v>0.26</v>
       </c>
-      <c r="F16" s="90">
+      <c r="F16" s="88">
         <v>0.16</v>
       </c>
-      <c r="G16" s="90">
+      <c r="G16" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="88">
+    <row r="17" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="86">
         <v>46054</v>
       </c>
-      <c r="B17" s="89">
+      <c r="B17" s="87">
         <v>1.03</v>
       </c>
-      <c r="C17" s="90">
+      <c r="C17" s="88">
         <v>0.41</v>
       </c>
-      <c r="D17" s="90">
-        <v>0.1567</v>
-      </c>
-      <c r="E17" s="90">
+      <c r="D17" s="88">
+        <v>0.15670000000000001</v>
+      </c>
+      <c r="E17" s="88">
         <v>0.26</v>
       </c>
-      <c r="F17" s="90">
+      <c r="F17" s="88">
         <v>0.16329999999999997</v>
       </c>
-      <c r="G17" s="90">
+      <c r="G17" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="88">
+    <row r="18" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="86">
         <v>46082</v>
       </c>
-      <c r="B18" s="89">
+      <c r="B18" s="87">
         <v>1.04</v>
       </c>
-      <c r="C18" s="90">
+      <c r="C18" s="88">
         <v>0.4</v>
       </c>
-      <c r="D18" s="90">
-        <v>0.1533</v>
-      </c>
-      <c r="E18" s="90">
+      <c r="D18" s="88">
+        <v>0.15329999999999999</v>
+      </c>
+      <c r="E18" s="88">
         <v>0.26</v>
       </c>
-      <c r="F18" s="90">
+      <c r="F18" s="88">
         <v>0.16670000000000001</v>
       </c>
-      <c r="G18" s="90">
+      <c r="G18" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="88">
+    <row r="19" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="86">
         <v>46113</v>
       </c>
-      <c r="B19" s="89">
+      <c r="B19" s="87">
         <v>1.05</v>
       </c>
-      <c r="C19" s="90">
+      <c r="C19" s="88">
         <v>0.39</v>
       </c>
-      <c r="D19" s="90">
+      <c r="D19" s="88">
         <v>0.15</v>
       </c>
-      <c r="E19" s="90">
+      <c r="E19" s="88">
         <v>0.26</v>
       </c>
-      <c r="F19" s="90">
+      <c r="F19" s="88">
         <v>0.17</v>
       </c>
-      <c r="G19" s="90">
+      <c r="G19" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="88">
+    <row r="20" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="86">
         <v>46143</v>
       </c>
-      <c r="B20" s="89">
+      <c r="B20" s="87">
         <v>1.06</v>
       </c>
-      <c r="C20" s="90">
-        <v>0.3833</v>
-      </c>
-      <c r="D20" s="90">
+      <c r="C20" s="88">
+        <v>0.38329999999999997</v>
+      </c>
+      <c r="D20" s="88">
         <v>0.1467</v>
       </c>
-      <c r="E20" s="90">
+      <c r="E20" s="88">
         <v>0.25670000000000004</v>
       </c>
-      <c r="F20" s="90">
+      <c r="F20" s="88">
         <v>0.17</v>
       </c>
-      <c r="G20" s="90">
+      <c r="G20" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="88">
+    <row r="21" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="86">
         <v>46174</v>
       </c>
-      <c r="B21" s="89">
+      <c r="B21" s="87">
         <v>1.07</v>
       </c>
-      <c r="C21" s="90">
-        <v>0.3767</v>
-      </c>
-      <c r="D21" s="90">
-        <v>0.1433</v>
-      </c>
-      <c r="E21" s="90">
+      <c r="C21" s="88">
+        <v>0.37669999999999998</v>
+      </c>
+      <c r="D21" s="88">
+        <v>0.14330000000000001</v>
+      </c>
+      <c r="E21" s="88">
         <v>0.25329999999999997</v>
       </c>
-      <c r="F21" s="90">
+      <c r="F21" s="88">
         <v>0.17</v>
       </c>
-      <c r="G21" s="90">
+      <c r="G21" s="88">
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="88">
+    <row r="22" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="86">
         <v>46204</v>
       </c>
-      <c r="B22" s="89">
+      <c r="B22" s="87">
         <v>1.08</v>
       </c>
-      <c r="C22" s="90">
+      <c r="C22" s="88">
         <v>0.37</v>
       </c>
-      <c r="D22" s="90">
-        <v>0.14</v>
-      </c>
-      <c r="E22" s="90">
+      <c r="D22" s="88">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E22" s="88">
         <v>0.25</v>
       </c>
-      <c r="F22" s="90">
+      <c r="F22" s="88">
         <v>0.17</v>
       </c>
-      <c r="G22" s="90">
-        <v>0.07</v>
-      </c>
-    </row>
-    <row r="23" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="88">
+      <c r="G22" s="88">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="86">
         <v>46235</v>
       </c>
-      <c r="B23" s="89">
-        <v>1.09</v>
-      </c>
-      <c r="C23" s="90">
+      <c r="B23" s="87">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="C23" s="88">
         <v>0.3599</v>
       </c>
-      <c r="D23" s="90">
-        <v>0.1367</v>
-      </c>
-      <c r="E23" s="90">
+      <c r="D23" s="88">
+        <v>0.13669999999999999</v>
+      </c>
+      <c r="E23" s="88">
         <v>0.24670000000000003</v>
       </c>
-      <c r="F23" s="90">
+      <c r="F23" s="88">
         <v>0.17</v>
       </c>
-      <c r="G23" s="90">
-        <v>0.0867</v>
-      </c>
-    </row>
-    <row r="24" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="88">
+      <c r="G23" s="88">
+        <v>8.6699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="86">
         <v>46266</v>
       </c>
-      <c r="B24" s="89">
-        <v>1.1</v>
-      </c>
-      <c r="C24" s="90">
-        <v>0.3501</v>
-      </c>
-      <c r="D24" s="90">
+      <c r="B24" s="87">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C24" s="88">
+        <v>0.35010000000000002</v>
+      </c>
+      <c r="D24" s="88">
         <v>0.1333</v>
       </c>
-      <c r="E24" s="90">
-        <v>0.2433</v>
-      </c>
-      <c r="F24" s="90">
+      <c r="E24" s="88">
+        <v>0.24329999999999999</v>
+      </c>
+      <c r="F24" s="88">
         <v>0.17</v>
       </c>
-      <c r="G24" s="90">
+      <c r="G24" s="88">
         <v>0.1033</v>
       </c>
     </row>
-    <row r="25" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="88">
+    <row r="25" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="86">
         <v>46296</v>
       </c>
-      <c r="B25" s="89">
-        <v>1.11</v>
-      </c>
-      <c r="C25" s="90">
+      <c r="B25" s="87">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C25" s="88">
         <v>0.34</v>
       </c>
-      <c r="D25" s="90">
+      <c r="D25" s="88">
         <v>0.13</v>
       </c>
-      <c r="E25" s="90">
+      <c r="E25" s="88">
         <v>0.24</v>
       </c>
-      <c r="F25" s="90">
+      <c r="F25" s="88">
         <v>0.17</v>
       </c>
-      <c r="G25" s="90">
+      <c r="G25" s="88">
         <v>0.12</v>
       </c>
     </row>
-    <row r="26" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="88">
+    <row r="26" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="86">
         <v>46327</v>
       </c>
-      <c r="B26" s="89">
-        <v>1.11</v>
-      </c>
-      <c r="C26" s="90">
+      <c r="B26" s="87">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C26" s="88">
         <v>0.34</v>
       </c>
-      <c r="D26" s="90">
+      <c r="D26" s="88">
         <v>0.13</v>
       </c>
-      <c r="E26" s="90">
+      <c r="E26" s="88">
         <v>0.24</v>
       </c>
-      <c r="F26" s="90">
+      <c r="F26" s="88">
         <v>0.17</v>
       </c>
-      <c r="G26" s="90">
+      <c r="G26" s="88">
         <v>0.12</v>
       </c>
     </row>
-    <row r="27" ht="19.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="88">
+    <row r="27" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="86">
         <v>46357</v>
       </c>
-      <c r="B27" s="89">
-        <v>1.11</v>
-      </c>
-      <c r="C27" s="90">
+      <c r="B27" s="87">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C27" s="88">
         <v>0.34</v>
       </c>
-      <c r="D27" s="90">
+      <c r="D27" s="88">
         <v>0.13</v>
       </c>
-      <c r="E27" s="90">
+      <c r="E27" s="88">
         <v>0.24</v>
       </c>
-      <c r="F27" s="90">
+      <c r="F27" s="88">
         <v>0.17</v>
       </c>
-      <c r="G27" s="90">
+      <c r="G27" s="88">
         <v>0.12</v>
       </c>
     </row>
@@ -8000,69 +8005,69 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.05" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+    <row r="1" spans="1:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="93" t="s">
         <v>312</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="94" t="s">
         <v>313</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-    </row>
-    <row r="3" ht="34.05" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="87" t="s">
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+    </row>
+    <row r="3" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="85" t="s">
         <v>314</v>
       </c>
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="85" t="s">
         <v>315</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="85" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="4" ht="19.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="91" t="s">
+    <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="89" t="s">
         <v>317</v>
       </c>
-      <c r="B4" s="92">
+      <c r="B4" s="90">
         <v>3200</v>
       </c>
-      <c r="C4" s="93">
-        <v>9.2</v>
-      </c>
-    </row>
-    <row r="5" ht="19.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="91" t="s">
+      <c r="C4" s="91">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="89" t="s">
         <v>318</v>
       </c>
-      <c r="B5" s="92">
+      <c r="B5" s="90">
         <v>2600</v>
       </c>
-      <c r="C5" s="93">
+      <c r="C5" s="91">
         <v>6.1</v>
       </c>
     </row>
-    <row r="6" ht="19.95" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="91" t="s">
+    <row r="6" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="89" t="s">
         <v>319</v>
       </c>
-      <c r="B6" s="92">
+      <c r="B6" s="90">
         <v>900</v>
       </c>
-      <c r="C6" s="93">
+      <c r="C6" s="91">
         <v>3.4</v>
       </c>
     </row>
@@ -8076,125 +8081,125 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.05" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="93" t="s">
         <v>320</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="94" t="s">
         <v>321</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-    </row>
-    <row r="3" ht="34.05" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="87" t="s">
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+    </row>
+    <row r="3" spans="1:4" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="85" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="4" ht="19.95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="88">
+    <row r="4" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="86">
         <v>46204</v>
       </c>
-      <c r="B4" s="94">
+      <c r="B4" s="92">
         <v>0.8</v>
       </c>
-      <c r="C4" s="94">
+      <c r="C4" s="92">
         <v>0.79</v>
       </c>
-      <c r="D4" s="91" t="s">
+      <c r="D4" s="89" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="5" ht="19.95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="88">
+    <row r="5" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="86">
         <v>46235</v>
       </c>
-      <c r="B5" s="94">
+      <c r="B5" s="92">
         <v>0.8</v>
       </c>
-      <c r="C5" s="94">
+      <c r="C5" s="92">
         <v>0.8</v>
       </c>
-      <c r="D5" s="91" t="s">
+      <c r="D5" s="89" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="6" ht="19.95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="88">
+    <row r="6" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="86">
         <v>46266</v>
       </c>
-      <c r="B6" s="94">
+      <c r="B6" s="92">
         <v>0.8</v>
       </c>
-      <c r="C6" s="94">
+      <c r="C6" s="92">
         <v>0.81</v>
       </c>
-      <c r="D6" s="91" t="s">
+      <c r="D6" s="89" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="7" ht="19.95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="88">
+    <row r="7" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="86">
         <v>46296</v>
       </c>
-      <c r="B7" s="94">
+      <c r="B7" s="92">
         <v>0.8</v>
       </c>
-      <c r="C7" s="94">
+      <c r="C7" s="92">
         <v>0.82</v>
       </c>
-      <c r="D7" s="91" t="s">
+      <c r="D7" s="89" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="8" ht="19.95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="88">
+    <row r="8" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="86">
         <v>46327</v>
       </c>
-      <c r="B8" s="94">
+      <c r="B8" s="92">
         <v>0.8</v>
       </c>
-      <c r="C8" s="94">
+      <c r="C8" s="92">
         <v>0.82</v>
       </c>
-      <c r="D8" s="91" t="s">
+      <c r="D8" s="89" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="9" ht="19.95" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="88">
+    <row r="9" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="86">
         <v>46357</v>
       </c>
-      <c r="B9" s="94">
+      <c r="B9" s="92">
         <v>0.8</v>
       </c>
-      <c r="C9" s="94">
+      <c r="C9" s="92">
         <v>0.83</v>
       </c>
-      <c r="D9" s="91" t="s">
+      <c r="D9" s="89" t="s">
         <v>322</v>
       </c>
     </row>
